--- a/Transformed_Tradebook.xlsx
+++ b/Transformed_Tradebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/143b6e31b9e74e02/Desktop/Projects/stockjournal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_C122EE47FBF212BC432BC93226490F8028736916" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{36D8F479-9BDD-4CBA-B340-AA4737EF65C5}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_2FBFAC42D0EA9DE88FE8DD3226490F8018FB7938" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04E0FA7B-EE23-4149-9284-420A6887D25C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3003" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3084" uniqueCount="322">
   <si>
     <t>Unnamed: 0</t>
   </si>
@@ -922,6 +922,9 @@
     <t>Tranch 3</t>
   </si>
   <si>
+    <t>Cap</t>
+  </si>
+  <si>
     <t>Current_Quantity</t>
   </si>
   <si>
@@ -953,6 +956,15 @@
   </si>
   <si>
     <t>Unrealized_PnL</t>
+  </si>
+  <si>
+    <t>Mid Cap</t>
+  </si>
+  <si>
+    <t>Large Cap</t>
+  </si>
+  <si>
+    <t>Small Cap</t>
   </si>
   <si>
     <t>Total_Buy_Quantity</t>
@@ -1324,21 +1336,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N302"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -16487,20 +16484,21 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
-    <col min="6" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16537,1106 +16535,1196 @@
       <c r="L1" t="s">
         <v>309</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>200</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>2936.3</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2642.67</v>
       </c>
-      <c r="E2" s="1">
+      <c r="F2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="G2" s="1">
         <v>2992</v>
       </c>
-      <c r="G2" s="1">
+      <c r="H2" s="1">
         <v>2966.46</v>
       </c>
-      <c r="H2" s="1">
+      <c r="I2" s="1">
         <v>2964.14</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>2961.54</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>2928.94</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>11968</v>
       </c>
-      <c r="L2" s="1">
+      <c r="M2" s="1">
         <v>222.8</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>253</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3">
         <v>45</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>2237.6</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2013.84</v>
       </c>
-      <c r="E3" s="1">
+      <c r="F3" s="1">
         <v>100692</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>2152.8000000000002</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>2183.5300000000002</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <v>2185.14</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>2186.16</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>2173.39</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>96876</v>
       </c>
-      <c r="L3" s="1">
+      <c r="M3" s="1">
         <v>-3816</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>138</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4">
         <v>90</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>292.10000000000002</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>262.89</v>
       </c>
-      <c r="E4" s="1">
+      <c r="F4" s="1">
         <v>26289</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>295.35000000000002</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>306.04000000000002</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <v>306.10000000000002</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <v>306.07</v>
       </c>
-      <c r="J4" s="1">
+      <c r="K4" s="1">
         <v>304.31</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>26581.5</v>
       </c>
-      <c r="L4" s="1">
+      <c r="M4" s="1">
         <v>292.5</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>216</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C5">
         <v>465</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>161.68</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>145.51</v>
       </c>
-      <c r="E5" s="1">
+      <c r="F5" s="1">
         <v>75181.2</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>159.58000000000001</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>167.76</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <v>167.99</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <v>168.13</v>
       </c>
-      <c r="J5" s="1">
+      <c r="K5" s="1">
         <v>167.33</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <v>74204.7</v>
       </c>
-      <c r="L5" s="1">
+      <c r="M5" s="1">
         <v>-976.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>235</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6">
         <v>222</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>453.96</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>408.56</v>
       </c>
-      <c r="E6" s="1">
+      <c r="F6" s="1">
         <v>100779.12</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>468.45</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>450.39</v>
       </c>
-      <c r="H6" s="1">
+      <c r="I6" s="1">
         <v>449.47</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>448.64</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>442.22</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>103995.9</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>3216.78</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>129</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7">
         <v>82</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1">
         <v>367.7</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>330.93</v>
       </c>
-      <c r="E7" s="1">
+      <c r="F7" s="1">
         <v>30151.4</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>352.75</v>
       </c>
-      <c r="G7" s="1">
+      <c r="H7" s="1">
         <v>367.39</v>
       </c>
-      <c r="H7" s="1">
+      <c r="I7" s="1">
         <v>368.05</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>368.58</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>369.89</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>28925.5</v>
       </c>
-      <c r="L7" s="1">
+      <c r="M7" s="1">
         <v>-1225.9000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>77</v>
       </c>
-      <c r="B8">
-        <v>18</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="B8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8">
+        <v>18</v>
+      </c>
+      <c r="D8" s="1">
         <v>2801.6</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>2521.44</v>
       </c>
-      <c r="E8" s="1">
+      <c r="F8" s="1">
         <v>50428.800000000003</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>2751.6</v>
       </c>
-      <c r="G8" s="1">
+      <c r="H8" s="1">
         <v>2738.6</v>
       </c>
-      <c r="H8" s="1">
+      <c r="I8" s="1">
         <v>2743.38</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>2748.12</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>2779.22</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>49528.800000000003</v>
       </c>
-      <c r="L8" s="1">
+      <c r="M8" s="1">
         <v>-900</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C9">
         <v>37</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1">
         <v>743.7</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>669.33</v>
       </c>
-      <c r="E9" s="1">
+      <c r="F9" s="1">
         <v>27516.9</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>715.45</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>707.53</v>
       </c>
-      <c r="H9" s="1">
+      <c r="I9" s="1">
         <v>706.75</v>
       </c>
-      <c r="I9" s="1">
+      <c r="J9" s="1">
         <v>705.78</v>
       </c>
-      <c r="J9" s="1">
+      <c r="K9" s="1">
         <v>691.8</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>26471.65</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <v>-1045.25</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>21</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1">
         <v>1548.9</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>1394.01</v>
       </c>
-      <c r="E10" s="1">
+      <c r="F10" s="1">
         <v>1548.9</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>1321.2</v>
       </c>
-      <c r="G10" s="1">
+      <c r="H10" s="1">
         <v>1333.03</v>
       </c>
-      <c r="H10" s="1">
+      <c r="I10" s="1">
         <v>1333.65</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>1334.23</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>1341.76</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>1321.2</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <v>-227.7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>192</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="s">
+        <v>311</v>
+      </c>
+      <c r="C11">
         <v>205</v>
       </c>
-      <c r="C11" s="1">
+      <c r="D11" s="1">
         <v>423.8</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>381.42</v>
       </c>
-      <c r="E11" s="1">
+      <c r="F11" s="1">
         <v>86879</v>
       </c>
-      <c r="F11" s="1">
+      <c r="G11" s="1">
         <v>80.44</v>
       </c>
-      <c r="G11" s="1">
+      <c r="H11" s="1">
         <v>80.709999999999994</v>
       </c>
-      <c r="H11" s="1">
+      <c r="I11" s="1">
         <v>80.88</v>
       </c>
-      <c r="I11" s="1">
+      <c r="J11" s="1">
         <v>81.040000000000006</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>82.12</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>16490.2</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <v>-70388.800000000003</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>141</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>311</v>
+      </c>
+      <c r="C12">
         <v>1172</v>
       </c>
-      <c r="C12" s="1">
+      <c r="D12" s="1">
         <v>256.22000000000003</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>263.82</v>
       </c>
-      <c r="E12" s="1">
+      <c r="F12" s="1">
         <v>300289.84000000003</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>286.5</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>291.52</v>
       </c>
-      <c r="H12" s="1">
+      <c r="I12" s="1">
         <v>291.57</v>
       </c>
-      <c r="I12" s="1">
+      <c r="J12" s="1">
         <v>291.55</v>
       </c>
-      <c r="J12" s="1">
+      <c r="K12" s="1">
         <v>289.55</v>
       </c>
-      <c r="K12" s="1">
+      <c r="L12" s="1">
         <v>335778</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <v>35488.160000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>189</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13">
         <v>362</v>
       </c>
-      <c r="C13" s="1">
+      <c r="D13" s="1">
         <v>138.75</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>124.88</v>
       </c>
-      <c r="E13" s="1">
+      <c r="F13" s="1">
         <v>50227.5</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>135.75</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>139.38</v>
       </c>
-      <c r="H13" s="1">
+      <c r="I13" s="1">
         <v>139.49</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>139.55000000000001</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>139.16</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>49141.5</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>-1086</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>43</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>313</v>
+      </c>
+      <c r="C14">
         <v>41</v>
       </c>
-      <c r="C14" s="1">
+      <c r="D14" s="1">
         <v>589.89</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>530.9</v>
       </c>
-      <c r="E14" s="1">
+      <c r="F14" s="1">
         <v>24185.49</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>546.85</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>554.23</v>
       </c>
-      <c r="H14" s="1">
+      <c r="I14" s="1">
         <v>555.4</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>556.49</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>563.08000000000004</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>22420.85</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>-1764.64</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>117</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15">
         <v>276</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D15" s="1">
         <v>278.74</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>250.87</v>
       </c>
-      <c r="E15" s="1">
+      <c r="F15" s="1">
         <v>76932.240000000005</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>247.35</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>256.63</v>
       </c>
-      <c r="H15" s="1">
+      <c r="I15" s="1">
         <v>257.2</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>257.67</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>259.11</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>68268.600000000006</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>-8663.64</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>24</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>313</v>
+      </c>
+      <c r="C16">
         <v>226</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1">
         <v>878.42</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>844.15</v>
       </c>
-      <c r="E16" s="1">
+      <c r="F16" s="1">
         <v>198522.92</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>676.9</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>684.33</v>
       </c>
-      <c r="H16" s="1">
+      <c r="I16" s="1">
         <v>687.27</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>690.15</v>
       </c>
-      <c r="J16" s="1">
+      <c r="K16" s="1">
         <v>715</v>
       </c>
-      <c r="K16" s="1">
+      <c r="L16" s="1">
         <v>152979.4</v>
       </c>
-      <c r="L16" s="1">
+      <c r="M16" s="1">
         <v>-45543.519999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>87</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>312</v>
+      </c>
+      <c r="C17">
         <v>253</v>
-      </c>
-      <c r="C17" s="1">
-        <v>843.31</v>
       </c>
       <c r="D17" s="1">
         <v>843.31</v>
       </c>
       <c r="E17" s="1">
+        <v>843.31</v>
+      </c>
+      <c r="F17" s="1">
         <v>213357.43</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>958.9</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>938.87</v>
       </c>
-      <c r="H17" s="1">
+      <c r="I17" s="1">
         <v>938.11</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>937.54</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>935.46</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>242601.7</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>29244.27</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>122</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="s">
+        <v>311</v>
+      </c>
+      <c r="C18">
         <v>205</v>
       </c>
-      <c r="C18" s="1">
+      <c r="D18" s="1">
         <v>483.35</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>435.02</v>
       </c>
-      <c r="E18" s="1">
+      <c r="F18" s="1">
         <v>99086.75</v>
       </c>
-      <c r="F18" s="1">
+      <c r="G18" s="1">
         <v>404.95</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>424.12</v>
       </c>
-      <c r="H18" s="1">
+      <c r="I18" s="1">
         <v>425.57</v>
       </c>
-      <c r="I18" s="1">
+      <c r="J18" s="1">
         <v>426.88</v>
       </c>
-      <c r="J18" s="1">
+      <c r="K18" s="1">
         <v>435.15</v>
       </c>
-      <c r="K18" s="1">
+      <c r="L18" s="1">
         <v>83014.75</v>
       </c>
-      <c r="L18" s="1">
+      <c r="M18" s="1">
         <v>-16072</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19">
         <v>386</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D19" s="1">
         <v>181.83</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>163.65</v>
       </c>
-      <c r="E19" s="1">
+      <c r="F19" s="1">
         <v>70186.38</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>168.68</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>175.51</v>
       </c>
-      <c r="H19" s="1">
+      <c r="I19" s="1">
         <v>175.7</v>
       </c>
-      <c r="I19" s="1">
+      <c r="J19" s="1">
         <v>175.81</v>
       </c>
-      <c r="J19" s="1">
+      <c r="K19" s="1">
         <v>174.93</v>
       </c>
-      <c r="K19" s="1">
+      <c r="L19" s="1">
         <v>65110.48</v>
       </c>
-      <c r="L19" s="1">
+      <c r="M19" s="1">
         <v>-5075.8999999999996</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>219</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C20">
         <v>720</v>
       </c>
-      <c r="C20" s="1">
+      <c r="D20" s="1">
         <v>70.69</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>63.62</v>
       </c>
-      <c r="E20" s="1">
+      <c r="F20" s="1">
         <v>50896.800000000003</v>
       </c>
-      <c r="F20" s="1">
+      <c r="G20" s="1">
         <v>70.13</v>
       </c>
-      <c r="G20" s="1">
+      <c r="H20" s="1">
         <v>70.92</v>
       </c>
-      <c r="H20" s="1">
+      <c r="I20" s="1">
         <v>70.81</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>70.69</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>69.3</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>50493.599999999999</v>
       </c>
-      <c r="L20" s="1">
+      <c r="M20" s="1">
         <v>-403.2</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>284</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C21">
         <v>121</v>
       </c>
-      <c r="C21" s="1">
+      <c r="D21" s="1">
         <v>206.6</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
         <v>185.94</v>
       </c>
-      <c r="E21" s="1">
+      <c r="F21" s="1">
         <v>24998.6</v>
       </c>
-      <c r="F21" s="1">
+      <c r="G21" s="1">
         <v>206.55</v>
       </c>
-      <c r="G21" s="1">
+      <c r="H21" s="1">
         <v>196.16</v>
       </c>
-      <c r="H21" s="1">
+      <c r="I21" s="1">
         <v>195.73</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>195.28</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>190.07</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>24992.55</v>
       </c>
-      <c r="L21" s="1">
+      <c r="M21" s="1">
         <v>-6.05</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>186</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>311</v>
+      </c>
+      <c r="C22">
         <v>300</v>
       </c>
-      <c r="C22" s="1">
+      <c r="D22" s="1">
         <v>84.49</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
         <v>76.040000000000006</v>
       </c>
-      <c r="E22" s="1">
+      <c r="F22" s="1">
         <v>25347</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>79.790000000000006</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>79.849999999999994</v>
       </c>
-      <c r="H22" s="1">
+      <c r="I22" s="1">
         <v>79.91</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>79.959999999999994</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>80.09</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>23937</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <v>-1410</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>14</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23">
         <v>38</v>
-      </c>
-      <c r="C23" s="1">
-        <v>7570.55</v>
       </c>
       <c r="D23" s="1">
         <v>7570.55</v>
       </c>
       <c r="E23" s="1">
+        <v>7570.55</v>
+      </c>
+      <c r="F23" s="1">
         <v>287680.90000000002</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>8552</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>8362.5</v>
       </c>
-      <c r="H23" s="1">
+      <c r="I23" s="1">
         <v>8333.4</v>
       </c>
-      <c r="I23" s="1">
+      <c r="J23" s="1">
         <v>8304.77</v>
       </c>
-      <c r="J23" s="1">
+      <c r="K23" s="1">
         <v>8068.43</v>
       </c>
-      <c r="K23" s="1">
+      <c r="L23" s="1">
         <v>324976</v>
       </c>
-      <c r="L23" s="1">
+      <c r="M23" s="1">
         <v>37295.1</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>80</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24">
         <v>25</v>
       </c>
-      <c r="C24" s="1">
+      <c r="D24" s="1">
         <v>531.34</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <v>478.21</v>
       </c>
-      <c r="E24" s="1">
+      <c r="F24" s="1">
         <v>13283.5</v>
       </c>
-      <c r="F24" s="1">
+      <c r="G24" s="1">
         <v>423.5</v>
       </c>
-      <c r="G24" s="1">
+      <c r="H24" s="1">
         <v>443.76</v>
       </c>
-      <c r="H24" s="1">
+      <c r="I24" s="1">
         <v>445.1</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>446.2</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>450.38</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>10587.5</v>
       </c>
-      <c r="L24" s="1">
+      <c r="M24" s="1">
         <v>-2696</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>135</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>312</v>
+      </c>
+      <c r="C25">
         <v>208</v>
       </c>
-      <c r="C25" s="1">
+      <c r="D25" s="1">
         <v>1121.97</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
         <v>1078</v>
       </c>
-      <c r="E25" s="1">
+      <c r="F25" s="1">
         <v>233369.76</v>
       </c>
-      <c r="F25" s="1">
+      <c r="G25" s="1">
         <v>1143</v>
       </c>
-      <c r="G25" s="1">
+      <c r="H25" s="1">
         <v>1180.6199999999999</v>
       </c>
-      <c r="H25" s="1">
+      <c r="I25" s="1">
         <v>1181.21</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>1181.26</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>1166.47</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>237744</v>
       </c>
-      <c r="L25" s="1">
+      <c r="M25" s="1">
         <v>4374.24</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>238</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>313</v>
+      </c>
+      <c r="C26">
         <v>34</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D26" s="1">
         <v>1348.03</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>1213.23</v>
       </c>
-      <c r="E26" s="1">
+      <c r="F26" s="1">
         <v>45833.02</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>1346</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>1331.94</v>
       </c>
-      <c r="H26" s="1">
+      <c r="I26" s="1">
         <v>1331.11</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>1330.07</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>1309.1400000000001</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <v>45764</v>
       </c>
-      <c r="L26" s="1">
+      <c r="M26" s="1">
         <v>-69.02</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>27</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27">
         <v>4</v>
       </c>
-      <c r="C27" s="1">
+      <c r="D27" s="1">
         <v>4509</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <v>4058.1</v>
       </c>
-      <c r="E27" s="1">
+      <c r="F27" s="1">
         <v>18036</v>
       </c>
-      <c r="F27" s="1">
+      <c r="G27" s="1">
         <v>3947.7</v>
       </c>
-      <c r="G27" s="1">
+      <c r="H27" s="1">
         <v>3941.29</v>
       </c>
-      <c r="H27" s="1">
+      <c r="I27" s="1">
         <v>3937.16</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>3932.32</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>3866.95</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>15790.8</v>
       </c>
-      <c r="L27" s="1">
+      <c r="M27" s="1">
         <v>-2245.1999999999998</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>272</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>313</v>
+      </c>
+      <c r="C28">
         <v>80</v>
       </c>
-      <c r="C28" s="1">
+      <c r="D28" s="1">
         <v>314.7</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
         <v>283.23</v>
       </c>
-      <c r="E28" s="1">
+      <c r="F28" s="1">
         <v>25176</v>
       </c>
-      <c r="F28" s="1">
+      <c r="G28" s="1">
         <v>293.64999999999998</v>
       </c>
-      <c r="G28" s="1">
+      <c r="H28" s="1">
         <v>296.93</v>
       </c>
-      <c r="H28" s="1">
+      <c r="I28" s="1">
         <v>296.52999999999997</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>296.01</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>289.45</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>23492</v>
       </c>
-      <c r="L28" s="1">
+      <c r="M28" s="1">
         <v>-1684</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>257</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29">
         <v>55</v>
       </c>
-      <c r="C29" s="1">
+      <c r="D29" s="1">
         <v>898.15</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
         <v>808.34</v>
       </c>
-      <c r="E29" s="1">
+      <c r="F29" s="1">
         <v>49398.25</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>878.75</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>880.79</v>
       </c>
-      <c r="H29" s="1">
+      <c r="I29" s="1">
         <v>879.35</v>
       </c>
-      <c r="I29" s="1">
+      <c r="J29" s="1">
         <v>877.62</v>
       </c>
-      <c r="J29" s="1">
+      <c r="K29" s="1">
         <v>852.29</v>
       </c>
-      <c r="K29" s="1">
+      <c r="L29" s="1">
         <v>48331.25</v>
       </c>
-      <c r="L29" s="1">
+      <c r="M29" s="1">
         <v>-1067</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>46</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>311</v>
+      </c>
+      <c r="C30">
         <v>37</v>
       </c>
-      <c r="C30" s="1">
+      <c r="D30" s="1">
         <v>1289.2</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <v>1160.28</v>
       </c>
-      <c r="E30" s="1">
+      <c r="F30" s="1">
         <v>47700.4</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>1121.3</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>1157.48</v>
       </c>
-      <c r="H30" s="1">
+      <c r="I30" s="1">
         <v>1160.73</v>
       </c>
-      <c r="I30" s="1">
+      <c r="J30" s="1">
         <v>1163.58</v>
       </c>
-      <c r="J30" s="1">
+      <c r="K30" s="1">
         <v>1180.18</v>
       </c>
-      <c r="K30" s="1">
+      <c r="L30" s="1">
         <v>41488.1</v>
       </c>
-      <c r="L30" s="1">
+      <c r="M30" s="1">
         <v>-6212.3</v>
       </c>
     </row>
@@ -17647,2420 +17735,2574 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O51"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>310</v>
+        <v>299</v>
       </c>
       <c r="C1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="D1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F1" t="s">
+        <v>316</v>
+      </c>
+      <c r="G1" t="s">
+        <v>317</v>
+      </c>
+      <c r="H1" t="s">
+        <v>318</v>
+      </c>
+      <c r="I1" t="s">
         <v>300</v>
-      </c>
-      <c r="E1" t="s">
-        <v>312</v>
-      </c>
-      <c r="F1" t="s">
-        <v>313</v>
-      </c>
-      <c r="G1" t="s">
-        <v>314</v>
-      </c>
-      <c r="H1" t="s">
-        <v>299</v>
-      </c>
-      <c r="I1" t="s">
-        <v>302</v>
       </c>
       <c r="J1" t="s">
         <v>303</v>
       </c>
       <c r="K1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="L1" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="M1" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="N1" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="O1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+        <v>320</v>
+      </c>
+      <c r="P1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>200</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C2">
         <v>4</v>
       </c>
-      <c r="C2" s="1">
+      <c r="D2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="D2" s="1">
+      <c r="E2" s="1">
         <v>2936.3</v>
       </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="1">
+      <c r="F2">
         <v>0</v>
       </c>
       <c r="G2" s="1">
         <v>0</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="1">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>4</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="J2" s="1">
+      <c r="K2" s="1">
         <v>2992</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>11968</v>
       </c>
-      <c r="L2" s="1">
-        <v>0</v>
-      </c>
       <c r="M2" s="1">
-        <v>222.8</v>
+        <v>0</v>
       </c>
       <c r="N2" s="1">
         <v>222.8</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2" s="1">
+        <v>222.8</v>
+      </c>
+      <c r="P2" s="2">
         <v>1.896945135033886E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>253</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C3">
         <v>45</v>
       </c>
-      <c r="C3" s="1">
+      <c r="D3" s="1">
         <v>100692.0045</v>
       </c>
-      <c r="D3" s="1">
+      <c r="E3" s="1">
         <v>2237.6</v>
       </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="1">
+      <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" s="1">
         <v>0</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="1">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>45</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <v>100692</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>2152.8000000000002</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>96876</v>
       </c>
-      <c r="L3" s="1">
-        <v>0</v>
-      </c>
       <c r="M3" s="1">
-        <v>-3816</v>
+        <v>0</v>
       </c>
       <c r="N3" s="1">
         <v>-3816</v>
       </c>
-      <c r="O3" s="2">
+      <c r="O3" s="1">
+        <v>-3816</v>
+      </c>
+      <c r="P3" s="2">
         <v>-3.7897745893021723E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="s">
+        <v>313</v>
+      </c>
+      <c r="C4">
         <v>671</v>
       </c>
-      <c r="C4" s="1">
+      <c r="D4" s="1">
         <v>129693.78</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
         <v>193.28</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>671</v>
       </c>
-      <c r="F4" s="1">
+      <c r="G4" s="1">
         <v>120337.14</v>
       </c>
-      <c r="G4" s="1">
+      <c r="H4" s="1">
         <v>179.34</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" s="1">
+      <c r="I4">
         <v>0</v>
       </c>
       <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
         <v>145.11000000000001</v>
       </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
       <c r="L4" s="1">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
         <v>-9353.74</v>
       </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
       <c r="N4" s="1">
+        <v>0</v>
+      </c>
+      <c r="O4" s="1">
         <v>-9353.74</v>
       </c>
-      <c r="O4" s="2">
+      <c r="P4" s="2">
         <v>-7.2121731666699815E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>97</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="s">
+        <v>312</v>
+      </c>
+      <c r="C5">
         <v>94</v>
       </c>
-      <c r="C5" s="1">
+      <c r="D5" s="1">
         <v>100072.4</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
         <v>1064.5999999999999</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>94</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>84426.099999999991</v>
       </c>
-      <c r="G5" s="1">
+      <c r="H5" s="1">
         <v>898.15</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" s="1">
+      <c r="I5">
         <v>0</v>
       </c>
       <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
         <v>950.2</v>
       </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
       <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
         <v>-15646.3</v>
       </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
       <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1">
         <v>-15646.3</v>
       </c>
-      <c r="O5" s="2">
+      <c r="P5" s="2">
         <v>-0.15634980274281421</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>138</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6">
         <v>260</v>
       </c>
-      <c r="C6" s="1">
+      <c r="D6" s="1">
         <v>75946</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
         <v>292.10000000000002</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>170</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>46165.05</v>
       </c>
-      <c r="G6" s="1">
+      <c r="H6" s="1">
         <v>271.56</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <v>90</v>
       </c>
-      <c r="I6" s="1">
+      <c r="J6" s="1">
         <v>26289</v>
       </c>
-      <c r="J6" s="1">
+      <c r="K6" s="1">
         <v>295.35000000000002</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <v>26581.5</v>
       </c>
-      <c r="L6" s="1">
+      <c r="M6" s="1">
         <v>-3491.95</v>
       </c>
-      <c r="M6" s="1">
+      <c r="N6" s="1">
         <v>292.5</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <v>-3199.45</v>
       </c>
-      <c r="O6" s="2">
+      <c r="P6" s="2">
         <v>-4.2127959339530723E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>216</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7">
         <v>465</v>
       </c>
-      <c r="C7" s="1">
+      <c r="D7" s="1">
         <v>75179.430000000008</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
         <v>161.68</v>
       </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7" s="1">
+      <c r="F7">
         <v>0</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7">
         <v>465</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7" s="1">
         <v>75181.2</v>
       </c>
-      <c r="J7" s="1">
+      <c r="K7" s="1">
         <v>159.58000000000001</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>74204.7</v>
       </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
       <c r="M7" s="1">
-        <v>-976.5</v>
+        <v>0</v>
       </c>
       <c r="N7" s="1">
         <v>-976.5</v>
       </c>
-      <c r="O7" s="2">
+      <c r="O7" s="1">
+        <v>-976.5</v>
+      </c>
+      <c r="P7" s="2">
         <v>-1.2988925295123939E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>235</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C8">
         <v>222</v>
       </c>
-      <c r="C8" s="1">
+      <c r="D8" s="1">
         <v>100778.25</v>
       </c>
-      <c r="D8" s="1">
+      <c r="E8" s="1">
         <v>453.96</v>
       </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" s="1">
+      <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8">
         <v>222</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8" s="1">
         <v>100779.12</v>
       </c>
-      <c r="J8" s="1">
+      <c r="K8" s="1">
         <v>468.45</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>103995.9</v>
       </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
       <c r="M8" s="1">
-        <v>3216.78</v>
+        <v>0</v>
       </c>
       <c r="N8" s="1">
         <v>3216.78</v>
       </c>
-      <c r="O8" s="2">
+      <c r="O8" s="1">
+        <v>3216.78</v>
+      </c>
+      <c r="P8" s="2">
         <v>3.1919387367810019E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>153</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9">
         <v>36</v>
       </c>
-      <c r="C9" s="1">
+      <c r="D9" s="1">
         <v>50176.800000000003</v>
       </c>
-      <c r="D9" s="1">
+      <c r="E9" s="1">
         <v>1393.8</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>36</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>50997.599999999999</v>
       </c>
-      <c r="G9" s="1">
+      <c r="H9" s="1">
         <v>1416.6</v>
       </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>0</v>
       </c>
       <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
         <v>1923.9</v>
       </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
       <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
         <v>820.8</v>
       </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
       <c r="N9" s="1">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1">
         <v>820.8</v>
       </c>
-      <c r="O9" s="2">
+      <c r="P9" s="2">
         <v>1.635815755488592E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>129</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="s">
+        <v>312</v>
+      </c>
+      <c r="C10">
         <v>82</v>
       </c>
-      <c r="C10" s="1">
+      <c r="D10" s="1">
         <v>30151.4</v>
       </c>
-      <c r="D10" s="1">
+      <c r="E10" s="1">
         <v>367.7</v>
       </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10" s="1">
+      <c r="F10">
         <v>0</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10">
         <v>82</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10" s="1">
         <v>30151.4</v>
       </c>
-      <c r="J10" s="1">
+      <c r="K10" s="1">
         <v>352.75</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>28925.5</v>
       </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
       <c r="M10" s="1">
-        <v>-1225.9000000000001</v>
+        <v>0</v>
       </c>
       <c r="N10" s="1">
         <v>-1225.9000000000001</v>
       </c>
-      <c r="O10" s="2">
+      <c r="O10" s="1">
+        <v>-1225.9000000000001</v>
+      </c>
+      <c r="P10" s="2">
         <v>-4.0658145227087307E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>77</v>
       </c>
-      <c r="B11">
-        <v>18</v>
-      </c>
-      <c r="C11" s="1">
+      <c r="B11" t="s">
+        <v>312</v>
+      </c>
+      <c r="C11">
+        <v>18</v>
+      </c>
+      <c r="D11" s="1">
         <v>50428.801800000001</v>
       </c>
-      <c r="D11" s="1">
+      <c r="E11" s="1">
         <v>2801.6</v>
       </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1">
+      <c r="F11">
         <v>0</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
       </c>
-      <c r="H11">
-        <v>18</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>18</v>
+      </c>
+      <c r="J11" s="1">
         <v>50428.800000000003</v>
       </c>
-      <c r="J11" s="1">
+      <c r="K11" s="1">
         <v>2751.6</v>
       </c>
-      <c r="K11" s="1">
+      <c r="L11" s="1">
         <v>49528.800000000003</v>
       </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
       <c r="M11" s="1">
-        <v>-900</v>
+        <v>0</v>
       </c>
       <c r="N11" s="1">
         <v>-900</v>
       </c>
-      <c r="O11" s="2">
+      <c r="O11" s="1">
+        <v>-900</v>
+      </c>
+      <c r="P11" s="2">
         <v>-1.784694396605711E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>167</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="s">
+        <v>313</v>
+      </c>
+      <c r="C12">
         <v>228</v>
       </c>
-      <c r="C12" s="1">
+      <c r="D12" s="1">
         <v>99912.15</v>
       </c>
-      <c r="D12" s="1">
+      <c r="E12" s="1">
         <v>438.21</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>228</v>
       </c>
-      <c r="F12" s="1">
+      <c r="G12" s="1">
         <v>90155.400000000009</v>
       </c>
-      <c r="G12" s="1">
+      <c r="H12" s="1">
         <v>395.42</v>
       </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12" s="1">
+      <c r="I12">
         <v>0</v>
       </c>
       <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
         <v>371.2</v>
       </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
       <c r="L12" s="1">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
         <v>-9756.48</v>
       </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
       <c r="N12" s="1">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1">
         <v>-9756.48</v>
       </c>
-      <c r="O12" s="2">
+      <c r="P12" s="2">
         <v>-9.7650586039835993E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>60</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="s">
+        <v>312</v>
+      </c>
+      <c r="C13">
         <v>2062</v>
       </c>
-      <c r="C13" s="1">
+      <c r="D13" s="1">
         <v>269285.90000000002</v>
       </c>
-      <c r="D13" s="1">
+      <c r="E13" s="1">
         <v>130.59</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>2078</v>
       </c>
-      <c r="F13" s="1">
+      <c r="G13" s="1">
         <v>267524.40000000002</v>
       </c>
-      <c r="G13" s="1">
+      <c r="H13" s="1">
         <v>128.74</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>-16</v>
       </c>
-      <c r="I13" s="1">
+      <c r="J13" s="1">
         <v>-2089.44</v>
       </c>
-      <c r="J13" s="1">
+      <c r="K13" s="1">
         <v>145.97</v>
       </c>
-      <c r="K13" s="1">
+      <c r="L13" s="1">
         <v>-2335.52</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <v>-3841.62</v>
       </c>
-      <c r="M13" s="1">
+      <c r="N13" s="1">
         <v>-246.08</v>
       </c>
-      <c r="N13" s="1">
+      <c r="O13" s="1">
         <v>-4087.7</v>
       </c>
-      <c r="O13" s="2">
+      <c r="P13" s="2">
         <v>-1.5179777329596531E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="s">
+        <v>312</v>
+      </c>
+      <c r="C14">
         <v>70</v>
       </c>
-      <c r="C14" s="1">
+      <c r="D14" s="1">
         <v>52058.85</v>
       </c>
-      <c r="D14" s="1">
+      <c r="E14" s="1">
         <v>743.7</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>33</v>
       </c>
-      <c r="F14" s="1">
+      <c r="G14" s="1">
         <v>25000.799999999999</v>
       </c>
-      <c r="G14" s="1">
+      <c r="H14" s="1">
         <v>757.6</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>37</v>
       </c>
-      <c r="I14" s="1">
+      <c r="J14" s="1">
         <v>27516.9</v>
       </c>
-      <c r="J14" s="1">
+      <c r="K14" s="1">
         <v>715.45</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>26471.65</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <v>458.7</v>
       </c>
-      <c r="M14" s="1">
+      <c r="N14" s="1">
         <v>-1045.25</v>
       </c>
-      <c r="N14" s="1">
+      <c r="O14" s="1">
         <v>-586.54999999999995</v>
       </c>
-      <c r="O14" s="2">
+      <c r="P14" s="2">
         <v>-1.126705641788092E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>126</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="s">
+        <v>313</v>
+      </c>
+      <c r="C15">
         <v>42</v>
       </c>
-      <c r="C15" s="1">
+      <c r="D15" s="1">
         <v>40147.050000000003</v>
       </c>
-      <c r="D15" s="1">
+      <c r="E15" s="1">
         <v>955.88</v>
       </c>
-      <c r="E15">
+      <c r="F15">
         <v>52</v>
       </c>
-      <c r="F15" s="1">
+      <c r="G15" s="1">
         <v>42377.3</v>
       </c>
-      <c r="G15" s="1">
+      <c r="H15" s="1">
         <v>814.95</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <v>-10</v>
       </c>
-      <c r="I15" s="1">
+      <c r="J15" s="1">
         <v>-9558.7999999999993</v>
       </c>
-      <c r="J15" s="1">
+      <c r="K15" s="1">
         <v>1007.5</v>
       </c>
-      <c r="K15" s="1">
+      <c r="L15" s="1">
         <v>-10075</v>
       </c>
-      <c r="L15" s="1">
+      <c r="M15" s="1">
         <v>-7328.46</v>
       </c>
-      <c r="M15" s="1">
+      <c r="N15" s="1">
         <v>-516.20000000000005</v>
       </c>
-      <c r="N15" s="1">
+      <c r="O15" s="1">
         <v>-7844.66</v>
       </c>
-      <c r="O15" s="2">
+      <c r="P15" s="2">
         <v>-0.19539816748677671</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="s">
+        <v>312</v>
+      </c>
+      <c r="C16">
         <v>64</v>
       </c>
-      <c r="C16" s="1">
+      <c r="D16" s="1">
         <v>99129.600000000006</v>
       </c>
-      <c r="D16" s="1">
+      <c r="E16" s="1">
         <v>1548.9</v>
       </c>
-      <c r="E16">
+      <c r="F16">
         <v>63</v>
       </c>
-      <c r="F16" s="1">
+      <c r="G16" s="1">
         <v>81862.200000000012</v>
       </c>
-      <c r="G16" s="1">
+      <c r="H16" s="1">
         <v>1299.4000000000001</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <v>1</v>
       </c>
-      <c r="I16" s="1">
+      <c r="J16" s="1">
         <v>1548.9</v>
-      </c>
-      <c r="J16" s="1">
-        <v>1321.2</v>
       </c>
       <c r="K16" s="1">
         <v>1321.2</v>
       </c>
       <c r="L16" s="1">
+        <v>1321.2</v>
+      </c>
+      <c r="M16" s="1">
         <v>-15718.5</v>
       </c>
-      <c r="M16" s="1">
+      <c r="N16" s="1">
         <v>-227.7</v>
       </c>
-      <c r="N16" s="1">
+      <c r="O16" s="1">
         <v>-15946.2</v>
       </c>
-      <c r="O16" s="2">
+      <c r="P16" s="2">
         <v>-0.1608621441022661</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>192</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="s">
+        <v>311</v>
+      </c>
+      <c r="C17">
         <v>338</v>
       </c>
-      <c r="C17" s="1">
+      <c r="D17" s="1">
         <v>143246</v>
       </c>
-      <c r="D17" s="1">
+      <c r="E17" s="1">
         <v>423.8</v>
       </c>
-      <c r="E17">
+      <c r="F17">
         <v>133</v>
       </c>
-      <c r="F17" s="1">
+      <c r="G17" s="1">
         <v>48531.7</v>
       </c>
-      <c r="G17" s="1">
+      <c r="H17" s="1">
         <v>364.9</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <v>205</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17" s="1">
         <v>86879</v>
       </c>
-      <c r="J17" s="1">
+      <c r="K17" s="1">
         <v>80.44</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>16490.2</v>
       </c>
-      <c r="L17" s="1">
+      <c r="M17" s="1">
         <v>-7833.7</v>
       </c>
-      <c r="M17" s="1">
+      <c r="N17" s="1">
         <v>-70388.800000000003</v>
       </c>
-      <c r="N17" s="1">
+      <c r="O17" s="1">
         <v>-78222.5</v>
       </c>
-      <c r="O17" s="2">
+      <c r="P17" s="2">
         <v>-0.54607109448082325</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18">
-        <v>19</v>
-      </c>
-      <c r="C18" s="1">
+      <c r="B18" t="s">
+        <v>312</v>
+      </c>
+      <c r="C18">
+        <v>19</v>
+      </c>
+      <c r="D18" s="1">
         <v>89756.600600000005</v>
       </c>
-      <c r="D18" s="1">
+      <c r="E18" s="1">
         <v>4724.03</v>
       </c>
-      <c r="E18">
-        <v>19</v>
-      </c>
-      <c r="F18" s="1">
+      <c r="F18">
+        <v>19</v>
+      </c>
+      <c r="G18" s="1">
         <v>77079.199999999997</v>
       </c>
-      <c r="G18" s="1">
+      <c r="H18" s="1">
         <v>4056.8</v>
       </c>
-      <c r="H18">
-        <v>0</v>
-      </c>
-      <c r="I18" s="1">
+      <c r="I18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
         <v>3875.8</v>
       </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
       <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
         <v>-12677.37</v>
       </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
       <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
         <v>-12677.37</v>
       </c>
-      <c r="O18" s="2">
+      <c r="P18" s="2">
         <v>-0.14124164590966029</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>107</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="s">
+        <v>312</v>
+      </c>
+      <c r="C19">
         <v>75</v>
       </c>
-      <c r="C19" s="1">
+      <c r="D19" s="1">
         <v>25440</v>
       </c>
-      <c r="D19" s="1">
+      <c r="E19" s="1">
         <v>339.2</v>
       </c>
-      <c r="E19">
+      <c r="F19">
         <v>75</v>
       </c>
-      <c r="F19" s="1">
+      <c r="G19" s="1">
         <v>22856.25</v>
       </c>
-      <c r="G19" s="1">
+      <c r="H19" s="1">
         <v>304.75</v>
       </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1">
+      <c r="I19">
         <v>0</v>
       </c>
       <c r="J19" s="1">
+        <v>0</v>
+      </c>
+      <c r="K19" s="1">
         <v>232.57</v>
       </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
       <c r="L19" s="1">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
         <v>-2583.75</v>
       </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
       <c r="N19" s="1">
+        <v>0</v>
+      </c>
+      <c r="O19" s="1">
         <v>-2583.75</v>
       </c>
-      <c r="O19" s="2">
+      <c r="P19" s="2">
         <v>-0.1015625</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>141</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="s">
+        <v>311</v>
+      </c>
+      <c r="C20">
         <v>1172</v>
       </c>
-      <c r="C20" s="1">
+      <c r="D20" s="1">
         <v>300285.28000000003</v>
       </c>
-      <c r="D20" s="1">
+      <c r="E20" s="1">
         <v>256.22000000000003</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20" s="1">
+      <c r="F20">
         <v>0</v>
       </c>
       <c r="G20" s="1">
         <v>0</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="1">
+        <v>0</v>
+      </c>
+      <c r="I20">
         <v>1172</v>
       </c>
-      <c r="I20" s="1">
+      <c r="J20" s="1">
         <v>300289.84000000003</v>
       </c>
-      <c r="J20" s="1">
+      <c r="K20" s="1">
         <v>286.5</v>
       </c>
-      <c r="K20" s="1">
+      <c r="L20" s="1">
         <v>335778</v>
       </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
       <c r="M20" s="1">
-        <v>35488.160000000003</v>
+        <v>0</v>
       </c>
       <c r="N20" s="1">
         <v>35488.160000000003</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20" s="1">
+        <v>35488.160000000003</v>
+      </c>
+      <c r="P20" s="2">
         <v>0.1181814839541918</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>189</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C21">
         <v>362</v>
       </c>
-      <c r="C21" s="1">
+      <c r="D21" s="1">
         <v>50229.29</v>
       </c>
-      <c r="D21" s="1">
+      <c r="E21" s="1">
         <v>138.75</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21" s="1">
+      <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" s="1">
         <v>0</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="1">
+        <v>0</v>
+      </c>
+      <c r="I21">
         <v>362</v>
       </c>
-      <c r="I21" s="1">
+      <c r="J21" s="1">
         <v>50227.5</v>
       </c>
-      <c r="J21" s="1">
+      <c r="K21" s="1">
         <v>135.75</v>
       </c>
-      <c r="K21" s="1">
+      <c r="L21" s="1">
         <v>49141.5</v>
       </c>
-      <c r="L21" s="1">
-        <v>0</v>
-      </c>
       <c r="M21" s="1">
-        <v>-1086</v>
+        <v>0</v>
       </c>
       <c r="N21" s="1">
         <v>-1086</v>
       </c>
-      <c r="O21" s="2">
+      <c r="O21" s="1">
+        <v>-1086</v>
+      </c>
+      <c r="P21" s="2">
         <v>-2.1620851101020942E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="s">
+        <v>313</v>
+      </c>
+      <c r="C22">
         <v>339</v>
       </c>
-      <c r="C22" s="1">
+      <c r="D22" s="1">
         <v>199971.65</v>
       </c>
-      <c r="D22" s="1">
+      <c r="E22" s="1">
         <v>589.89</v>
       </c>
-      <c r="E22">
+      <c r="F22">
         <v>298</v>
       </c>
-      <c r="F22" s="1">
+      <c r="G22" s="1">
         <v>175804.15</v>
       </c>
-      <c r="G22" s="1">
+      <c r="H22" s="1">
         <v>589.95000000000005</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <v>41</v>
       </c>
-      <c r="I22" s="1">
+      <c r="J22" s="1">
         <v>24185.49</v>
       </c>
-      <c r="J22" s="1">
+      <c r="K22" s="1">
         <v>546.85</v>
       </c>
-      <c r="K22" s="1">
+      <c r="L22" s="1">
         <v>22420.85</v>
       </c>
-      <c r="L22" s="1">
+      <c r="M22" s="1">
         <v>16.93</v>
       </c>
-      <c r="M22" s="1">
+      <c r="N22" s="1">
         <v>-1764.64</v>
       </c>
-      <c r="N22" s="1">
+      <c r="O22" s="1">
         <v>-1747.71</v>
       </c>
-      <c r="O22" s="2">
+      <c r="P22" s="2">
         <v>-8.7397888650716238E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>164</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23">
         <v>920</v>
       </c>
-      <c r="C23" s="1">
+      <c r="D23" s="1">
         <v>99801.600000000006</v>
       </c>
-      <c r="D23" s="1">
+      <c r="E23" s="1">
         <v>108.48</v>
       </c>
-      <c r="E23">
+      <c r="F23">
         <v>920</v>
       </c>
-      <c r="F23" s="1">
+      <c r="G23" s="1">
         <v>82570</v>
       </c>
-      <c r="G23" s="1">
+      <c r="H23" s="1">
         <v>89.75</v>
       </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23" s="1">
+      <c r="I23">
         <v>0</v>
       </c>
       <c r="J23" s="1">
+        <v>0</v>
+      </c>
+      <c r="K23" s="1">
         <v>95.06</v>
       </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
       <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
         <v>-17231.599999999999</v>
       </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
       <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
         <v>-17231.599999999999</v>
       </c>
-      <c r="O23" s="2">
+      <c r="P23" s="2">
         <v>-0.17265855457227139</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>117</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24">
         <v>276</v>
       </c>
-      <c r="C24" s="1">
+      <c r="D24" s="1">
         <v>76932.53</v>
       </c>
-      <c r="D24" s="1">
+      <c r="E24" s="1">
         <v>278.74</v>
       </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-      <c r="F24" s="1">
+      <c r="F24">
         <v>0</v>
       </c>
       <c r="G24" s="1">
         <v>0</v>
       </c>
-      <c r="H24">
+      <c r="H24" s="1">
+        <v>0</v>
+      </c>
+      <c r="I24">
         <v>276</v>
       </c>
-      <c r="I24" s="1">
+      <c r="J24" s="1">
         <v>76932.240000000005</v>
       </c>
-      <c r="J24" s="1">
+      <c r="K24" s="1">
         <v>247.35</v>
       </c>
-      <c r="K24" s="1">
+      <c r="L24" s="1">
         <v>68268.600000000006</v>
       </c>
-      <c r="L24" s="1">
-        <v>0</v>
-      </c>
       <c r="M24" s="1">
-        <v>-8663.64</v>
+        <v>0</v>
       </c>
       <c r="N24" s="1">
         <v>-8663.64</v>
       </c>
-      <c r="O24" s="2">
+      <c r="O24" s="1">
+        <v>-8663.64</v>
+      </c>
+      <c r="P24" s="2">
         <v>-0.1126134809293286</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="s">
+        <v>313</v>
+      </c>
+      <c r="C25">
         <v>226</v>
       </c>
-      <c r="C25" s="1">
+      <c r="D25" s="1">
         <v>198521.9</v>
       </c>
-      <c r="D25" s="1">
+      <c r="E25" s="1">
         <v>878.42</v>
       </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-      <c r="F25" s="1">
+      <c r="F25">
         <v>0</v>
       </c>
       <c r="G25" s="1">
         <v>0</v>
       </c>
-      <c r="H25">
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25">
         <v>226</v>
       </c>
-      <c r="I25" s="1">
+      <c r="J25" s="1">
         <v>198522.92</v>
       </c>
-      <c r="J25" s="1">
+      <c r="K25" s="1">
         <v>676.9</v>
       </c>
-      <c r="K25" s="1">
+      <c r="L25" s="1">
         <v>152979.4</v>
       </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
       <c r="M25" s="1">
-        <v>-45543.519999999997</v>
+        <v>0</v>
       </c>
       <c r="N25" s="1">
         <v>-45543.519999999997</v>
       </c>
-      <c r="O25" s="2">
+      <c r="O25" s="1">
+        <v>-45543.519999999997</v>
+      </c>
+      <c r="P25" s="2">
         <v>-0.2294130773481414</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>87</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="s">
+        <v>312</v>
+      </c>
+      <c r="C26">
         <v>356</v>
       </c>
-      <c r="C26" s="1">
+      <c r="D26" s="1">
         <v>300219.3</v>
       </c>
-      <c r="D26" s="1">
+      <c r="E26" s="1">
         <v>843.31</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>103</v>
       </c>
-      <c r="F26" s="1">
+      <c r="G26" s="1">
         <v>99714.349999999991</v>
       </c>
-      <c r="G26" s="1">
+      <c r="H26" s="1">
         <v>968.1</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <v>253</v>
       </c>
-      <c r="I26" s="1">
+      <c r="J26" s="1">
         <v>213357.43</v>
       </c>
-      <c r="J26" s="1">
+      <c r="K26" s="1">
         <v>958.9</v>
       </c>
-      <c r="K26" s="1">
+      <c r="L26" s="1">
         <v>242601.7</v>
       </c>
-      <c r="L26" s="1">
+      <c r="M26" s="1">
         <v>12853.42</v>
       </c>
-      <c r="M26" s="1">
+      <c r="N26" s="1">
         <v>29244.27</v>
       </c>
-      <c r="N26" s="1">
+      <c r="O26" s="1">
         <v>42097.69</v>
       </c>
-      <c r="O26" s="2">
+      <c r="P26" s="2">
         <v>0.14022313022513869</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>122</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="s">
+        <v>311</v>
+      </c>
+      <c r="C27">
         <v>205</v>
       </c>
-      <c r="C27" s="1">
+      <c r="D27" s="1">
         <v>99086.75</v>
       </c>
-      <c r="D27" s="1">
+      <c r="E27" s="1">
         <v>483.35</v>
       </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-      <c r="F27" s="1">
+      <c r="F27">
         <v>0</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
-      <c r="H27">
+      <c r="H27" s="1">
+        <v>0</v>
+      </c>
+      <c r="I27">
         <v>205</v>
       </c>
-      <c r="I27" s="1">
+      <c r="J27" s="1">
         <v>99086.75</v>
       </c>
-      <c r="J27" s="1">
+      <c r="K27" s="1">
         <v>404.95</v>
       </c>
-      <c r="K27" s="1">
+      <c r="L27" s="1">
         <v>83014.75</v>
       </c>
-      <c r="L27" s="1">
-        <v>0</v>
-      </c>
       <c r="M27" s="1">
-        <v>-16072</v>
+        <v>0</v>
       </c>
       <c r="N27" s="1">
         <v>-16072</v>
       </c>
-      <c r="O27" s="2">
+      <c r="O27" s="1">
+        <v>-16072</v>
+      </c>
+      <c r="P27" s="2">
         <v>-0.16220130340333089</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>132</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C28">
         <v>386</v>
       </c>
-      <c r="C28" s="1">
+      <c r="D28" s="1">
         <v>70186.3</v>
       </c>
-      <c r="D28" s="1">
+      <c r="E28" s="1">
         <v>181.83</v>
       </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-      <c r="F28" s="1">
+      <c r="F28">
         <v>0</v>
       </c>
       <c r="G28" s="1">
         <v>0</v>
       </c>
-      <c r="H28">
+      <c r="H28" s="1">
+        <v>0</v>
+      </c>
+      <c r="I28">
         <v>386</v>
       </c>
-      <c r="I28" s="1">
+      <c r="J28" s="1">
         <v>70186.38</v>
       </c>
-      <c r="J28" s="1">
+      <c r="K28" s="1">
         <v>168.68</v>
       </c>
-      <c r="K28" s="1">
+      <c r="L28" s="1">
         <v>65110.48</v>
       </c>
-      <c r="L28" s="1">
-        <v>0</v>
-      </c>
       <c r="M28" s="1">
-        <v>-5075.8999999999996</v>
+        <v>0</v>
       </c>
       <c r="N28" s="1">
         <v>-5075.8999999999996</v>
       </c>
-      <c r="O28" s="2">
+      <c r="O28" s="1">
+        <v>-5075.8999999999996</v>
+      </c>
+      <c r="P28" s="2">
         <v>-7.2320381612935844E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>56</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="s">
+        <v>313</v>
+      </c>
+      <c r="C29">
         <v>35</v>
       </c>
-      <c r="C29" s="1">
+      <c r="D29" s="1">
         <v>25089.75</v>
       </c>
-      <c r="D29" s="1">
+      <c r="E29" s="1">
         <v>716.85</v>
       </c>
-      <c r="E29">
+      <c r="F29">
         <v>35</v>
       </c>
-      <c r="F29" s="1">
+      <c r="G29" s="1">
         <v>22651.75</v>
       </c>
-      <c r="G29" s="1">
+      <c r="H29" s="1">
         <v>647.19000000000005</v>
       </c>
-      <c r="H29">
-        <v>0</v>
-      </c>
-      <c r="I29" s="1">
+      <c r="I29">
         <v>0</v>
       </c>
       <c r="J29" s="1">
+        <v>0</v>
+      </c>
+      <c r="K29" s="1">
         <v>521.9</v>
       </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
       <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
         <v>-2438</v>
       </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
       <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
         <v>-2438</v>
       </c>
-      <c r="O29" s="2">
+      <c r="P29" s="2">
         <v>-9.7171155551569868E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>173</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="s">
+        <v>313</v>
+      </c>
+      <c r="C30">
         <v>196</v>
       </c>
-      <c r="C30" s="1">
+      <c r="D30" s="1">
         <v>100079.5</v>
       </c>
-      <c r="D30" s="1">
+      <c r="E30" s="1">
         <v>510.61</v>
       </c>
-      <c r="E30">
+      <c r="F30">
         <v>196</v>
       </c>
-      <c r="F30" s="1">
+      <c r="G30" s="1">
         <v>82398.399999999994</v>
       </c>
-      <c r="G30" s="1">
+      <c r="H30" s="1">
         <v>420.4</v>
       </c>
-      <c r="H30">
-        <v>0</v>
-      </c>
-      <c r="I30" s="1">
+      <c r="I30">
         <v>0</v>
       </c>
       <c r="J30" s="1">
+        <v>0</v>
+      </c>
+      <c r="K30" s="1">
         <v>452.55</v>
       </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
       <c r="L30" s="1">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
         <v>-17681.16</v>
       </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
       <c r="N30" s="1">
+        <v>0</v>
+      </c>
+      <c r="O30" s="1">
         <v>-17681.16</v>
       </c>
-      <c r="O30" s="2">
+      <c r="P30" s="2">
         <v>-0.17667114643858131</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>178</v>
       </c>
-      <c r="B31">
-        <v>19</v>
-      </c>
-      <c r="C31" s="1">
+      <c r="B31" t="s">
+        <v>313</v>
+      </c>
+      <c r="C31">
+        <v>19</v>
+      </c>
+      <c r="D31" s="1">
         <v>24977.4</v>
       </c>
-      <c r="D31" s="1">
+      <c r="E31" s="1">
         <v>1314.6</v>
       </c>
-      <c r="E31">
-        <v>19</v>
-      </c>
-      <c r="F31" s="1">
+      <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31" s="1">
         <v>21475.7</v>
       </c>
-      <c r="G31" s="1">
+      <c r="H31" s="1">
         <v>1130.3</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31" s="1">
+      <c r="I31">
         <v>0</v>
       </c>
       <c r="J31" s="1">
+        <v>0</v>
+      </c>
+      <c r="K31" s="1">
         <v>1510.5</v>
       </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
       <c r="L31" s="1">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
         <v>-3501.7</v>
       </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
       <c r="N31" s="1">
+        <v>0</v>
+      </c>
+      <c r="O31" s="1">
         <v>-3501.7</v>
       </c>
-      <c r="O31" s="2">
+      <c r="P31" s="2">
         <v>-0.14019473604138141</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>219</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="s">
+        <v>311</v>
+      </c>
+      <c r="C32">
         <v>720</v>
       </c>
-      <c r="C32" s="1">
+      <c r="D32" s="1">
         <v>50899.69</v>
       </c>
-      <c r="D32" s="1">
+      <c r="E32" s="1">
         <v>70.69</v>
       </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32" s="1">
+      <c r="F32">
         <v>0</v>
       </c>
       <c r="G32" s="1">
         <v>0</v>
       </c>
-      <c r="H32">
+      <c r="H32" s="1">
+        <v>0</v>
+      </c>
+      <c r="I32">
         <v>720</v>
       </c>
-      <c r="I32" s="1">
+      <c r="J32" s="1">
         <v>50896.800000000003</v>
       </c>
-      <c r="J32" s="1">
+      <c r="K32" s="1">
         <v>70.13</v>
       </c>
-      <c r="K32" s="1">
+      <c r="L32" s="1">
         <v>50493.599999999999</v>
       </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
       <c r="M32" s="1">
-        <v>-403.2</v>
+        <v>0</v>
       </c>
       <c r="N32" s="1">
         <v>-403.2</v>
       </c>
-      <c r="O32" s="2">
+      <c r="O32" s="1">
+        <v>-403.2</v>
+      </c>
+      <c r="P32" s="2">
         <v>-7.9214627829756919E-3</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>36</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="s">
+        <v>313</v>
+      </c>
+      <c r="C33">
         <v>42</v>
       </c>
-      <c r="C33" s="1">
+      <c r="D33" s="1">
         <v>91224</v>
       </c>
-      <c r="D33" s="1">
+      <c r="E33" s="1">
         <v>2172</v>
       </c>
-      <c r="E33">
+      <c r="F33">
         <v>42</v>
       </c>
-      <c r="F33" s="1">
+      <c r="G33" s="1">
         <v>81102.5</v>
       </c>
-      <c r="G33" s="1">
+      <c r="H33" s="1">
         <v>1931.01</v>
       </c>
-      <c r="H33">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1">
+      <c r="I33">
         <v>0</v>
       </c>
       <c r="J33" s="1">
+        <v>0</v>
+      </c>
+      <c r="K33" s="1">
         <v>1790.2</v>
       </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
       <c r="L33" s="1">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
         <v>-10121.5</v>
       </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
       <c r="N33" s="1">
+        <v>0</v>
+      </c>
+      <c r="O33" s="1">
         <v>-10121.5</v>
       </c>
-      <c r="O33" s="2">
+      <c r="P33" s="2">
         <v>-0.1109521617118302</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>284</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C34">
         <v>121</v>
       </c>
-      <c r="C34" s="1">
+      <c r="D34" s="1">
         <v>24998.6</v>
       </c>
-      <c r="D34" s="1">
+      <c r="E34" s="1">
         <v>206.6</v>
       </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1">
+      <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" s="1">
         <v>0</v>
       </c>
-      <c r="H34">
+      <c r="H34" s="1">
+        <v>0</v>
+      </c>
+      <c r="I34">
         <v>121</v>
       </c>
-      <c r="I34" s="1">
+      <c r="J34" s="1">
         <v>24998.6</v>
       </c>
-      <c r="J34" s="1">
+      <c r="K34" s="1">
         <v>206.55</v>
       </c>
-      <c r="K34" s="1">
+      <c r="L34" s="1">
         <v>24992.55</v>
       </c>
-      <c r="L34" s="1">
-        <v>0</v>
-      </c>
       <c r="M34" s="1">
-        <v>-6.05</v>
+        <v>0</v>
       </c>
       <c r="N34" s="1">
         <v>-6.05</v>
       </c>
-      <c r="O34" s="2">
+      <c r="O34" s="1">
+        <v>-6.05</v>
+      </c>
+      <c r="P34" s="2">
         <v>-2.4201355275895451E-4</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>186</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35">
         <v>300</v>
       </c>
-      <c r="C35" s="1">
+      <c r="D35" s="1">
         <v>25347</v>
       </c>
-      <c r="D35" s="1">
+      <c r="E35" s="1">
         <v>84.49</v>
       </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1">
+      <c r="F35">
         <v>0</v>
       </c>
       <c r="G35" s="1">
         <v>0</v>
       </c>
-      <c r="H35">
+      <c r="H35" s="1">
+        <v>0</v>
+      </c>
+      <c r="I35">
         <v>300</v>
       </c>
-      <c r="I35" s="1">
+      <c r="J35" s="1">
         <v>25347</v>
       </c>
-      <c r="J35" s="1">
+      <c r="K35" s="1">
         <v>79.790000000000006</v>
       </c>
-      <c r="K35" s="1">
+      <c r="L35" s="1">
         <v>23937</v>
       </c>
-      <c r="L35" s="1">
-        <v>0</v>
-      </c>
       <c r="M35" s="1">
-        <v>-1410</v>
+        <v>0</v>
       </c>
       <c r="N35" s="1">
         <v>-1410</v>
       </c>
-      <c r="O35" s="2">
+      <c r="O35" s="1">
+        <v>-1410</v>
+      </c>
+      <c r="P35" s="2">
         <v>-5.5627884956799621E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>49</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="s">
+        <v>312</v>
+      </c>
+      <c r="C36">
         <v>30</v>
       </c>
-      <c r="C36" s="1">
+      <c r="D36" s="1">
         <v>93744</v>
       </c>
-      <c r="D36" s="1">
+      <c r="E36" s="1">
         <v>3124.8</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>52</v>
       </c>
-      <c r="F36" s="1">
+      <c r="G36" s="1">
         <v>76804.7</v>
       </c>
-      <c r="G36" s="1">
+      <c r="H36" s="1">
         <v>1477.01</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <v>-22</v>
       </c>
-      <c r="I36" s="1">
+      <c r="J36" s="1">
         <v>-68745.600000000006</v>
       </c>
-      <c r="J36" s="1">
+      <c r="K36" s="1">
         <v>1433.8</v>
       </c>
-      <c r="K36" s="1">
+      <c r="L36" s="1">
         <v>-31543.599999999999</v>
       </c>
-      <c r="L36" s="1">
+      <c r="M36" s="1">
         <v>-85684.9</v>
       </c>
-      <c r="M36" s="1">
+      <c r="N36" s="1">
         <v>37202</v>
       </c>
-      <c r="N36" s="1">
+      <c r="O36" s="1">
         <v>-48482.9</v>
       </c>
-      <c r="O36" s="2">
+      <c r="P36" s="2">
         <v>-0.51718403311145245</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>213</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="s">
+        <v>312</v>
+      </c>
+      <c r="C37">
         <v>200</v>
       </c>
-      <c r="C37" s="1">
+      <c r="D37" s="1">
         <v>25540.1</v>
       </c>
-      <c r="D37" s="1">
+      <c r="E37" s="1">
         <v>127.7</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>200</v>
       </c>
-      <c r="F37" s="1">
+      <c r="G37" s="1">
         <v>23912</v>
       </c>
-      <c r="G37" s="1">
+      <c r="H37" s="1">
         <v>119.56</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37" s="1">
+      <c r="I37">
         <v>0</v>
       </c>
       <c r="J37" s="1">
+        <v>0</v>
+      </c>
+      <c r="K37" s="1">
         <v>119.31</v>
       </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
       <c r="L37" s="1">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
         <v>-1628</v>
       </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
       <c r="N37" s="1">
+        <v>0</v>
+      </c>
+      <c r="O37" s="1">
         <v>-1628</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="2">
         <v>-6.3742898422480723E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>14</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="s">
+        <v>312</v>
+      </c>
+      <c r="C38">
         <v>38</v>
       </c>
-      <c r="C38" s="1">
+      <c r="D38" s="1">
         <v>287681</v>
       </c>
-      <c r="D38" s="1">
+      <c r="E38" s="1">
         <v>7570.55</v>
       </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38" s="1">
+      <c r="F38">
         <v>0</v>
       </c>
       <c r="G38" s="1">
         <v>0</v>
       </c>
-      <c r="H38">
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
+      <c r="I38">
         <v>38</v>
       </c>
-      <c r="I38" s="1">
+      <c r="J38" s="1">
         <v>287680.90000000002</v>
       </c>
-      <c r="J38" s="1">
+      <c r="K38" s="1">
         <v>8552</v>
       </c>
-      <c r="K38" s="1">
+      <c r="L38" s="1">
         <v>324976</v>
       </c>
-      <c r="L38" s="1">
-        <v>0</v>
-      </c>
       <c r="M38" s="1">
-        <v>37295.1</v>
+        <v>0</v>
       </c>
       <c r="N38" s="1">
         <v>37295.1</v>
       </c>
-      <c r="O38" s="2">
+      <c r="O38" s="1">
+        <v>37295.1</v>
+      </c>
+      <c r="P38" s="2">
         <v>0.12964046982595301</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>80</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="s">
+        <v>313</v>
+      </c>
+      <c r="C39">
         <v>188</v>
       </c>
-      <c r="C39" s="1">
+      <c r="D39" s="1">
         <v>99892.650000000009</v>
       </c>
-      <c r="D39" s="1">
+      <c r="E39" s="1">
         <v>531.34</v>
       </c>
-      <c r="E39">
+      <c r="F39">
         <v>163</v>
       </c>
-      <c r="F39" s="1">
+      <c r="G39" s="1">
         <v>78567.95</v>
       </c>
-      <c r="G39" s="1">
+      <c r="H39" s="1">
         <v>482.01</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <v>25</v>
       </c>
-      <c r="I39" s="1">
+      <c r="J39" s="1">
         <v>13283.5</v>
       </c>
-      <c r="J39" s="1">
+      <c r="K39" s="1">
         <v>423.5</v>
       </c>
-      <c r="K39" s="1">
+      <c r="L39" s="1">
         <v>10587.5</v>
       </c>
-      <c r="L39" s="1">
+      <c r="M39" s="1">
         <v>-8040.47</v>
       </c>
-      <c r="M39" s="1">
+      <c r="N39" s="1">
         <v>-2696</v>
       </c>
-      <c r="N39" s="1">
+      <c r="O39" s="1">
         <v>-10736.47</v>
       </c>
-      <c r="O39" s="2">
+      <c r="P39" s="2">
         <v>-0.10748007986573591</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>83</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="s">
+        <v>313</v>
+      </c>
+      <c r="C40">
         <v>204</v>
       </c>
-      <c r="C40" s="1">
+      <c r="D40" s="1">
         <v>48757.69</v>
       </c>
-      <c r="D40" s="1">
+      <c r="E40" s="1">
         <v>239.01</v>
       </c>
-      <c r="E40">
+      <c r="F40">
         <v>220</v>
       </c>
-      <c r="F40" s="1">
+      <c r="G40" s="1">
         <v>54098</v>
       </c>
-      <c r="G40" s="1">
+      <c r="H40" s="1">
         <v>245.9</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <v>-16</v>
       </c>
-      <c r="I40" s="1">
+      <c r="J40" s="1">
         <v>-3824.16</v>
       </c>
-      <c r="J40" s="1">
+      <c r="K40" s="1">
         <v>333.45</v>
       </c>
-      <c r="K40" s="1">
+      <c r="L40" s="1">
         <v>-5335.2</v>
       </c>
-      <c r="L40" s="1">
+      <c r="M40" s="1">
         <v>1515.8</v>
       </c>
-      <c r="M40" s="1">
+      <c r="N40" s="1">
         <v>-1511.04</v>
       </c>
-      <c r="N40" s="1">
+      <c r="O40" s="1">
         <v>4.76</v>
       </c>
-      <c r="O40" s="2">
+      <c r="P40" s="2">
         <v>9.7625625824357127E-5</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>262</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="s">
+        <v>313</v>
+      </c>
+      <c r="C41">
         <v>10</v>
       </c>
-      <c r="C41" s="1">
+      <c r="D41" s="1">
         <v>4835.5</v>
       </c>
-      <c r="D41" s="1">
+      <c r="E41" s="1">
         <v>483.55</v>
       </c>
-      <c r="E41">
+      <c r="F41">
         <v>10</v>
       </c>
-      <c r="F41" s="1">
+      <c r="G41" s="1">
         <v>4193</v>
       </c>
-      <c r="G41" s="1">
+      <c r="H41" s="1">
         <v>419.3</v>
       </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41" s="1">
+      <c r="I41">
         <v>0</v>
       </c>
       <c r="J41" s="1">
+        <v>0</v>
+      </c>
+      <c r="K41" s="1">
         <v>395.8</v>
       </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
       <c r="L41" s="1">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
         <v>-642.5</v>
       </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
       <c r="N41" s="1">
+        <v>0</v>
+      </c>
+      <c r="O41" s="1">
         <v>-642.5</v>
       </c>
-      <c r="O41" s="2">
+      <c r="P41" s="2">
         <v>-0.1328714714093682</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>135</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="s">
+        <v>312</v>
+      </c>
+      <c r="C42">
         <v>208</v>
       </c>
-      <c r="C42" s="1">
+      <c r="D42" s="1">
         <v>233369.9</v>
       </c>
-      <c r="D42" s="1">
+      <c r="E42" s="1">
         <v>1121.97</v>
       </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42" s="1">
+      <c r="F42">
         <v>0</v>
       </c>
       <c r="G42" s="1">
         <v>0</v>
       </c>
-      <c r="H42">
+      <c r="H42" s="1">
+        <v>0</v>
+      </c>
+      <c r="I42">
         <v>208</v>
       </c>
-      <c r="I42" s="1">
+      <c r="J42" s="1">
         <v>233369.76</v>
       </c>
-      <c r="J42" s="1">
+      <c r="K42" s="1">
         <v>1143</v>
       </c>
-      <c r="K42" s="1">
+      <c r="L42" s="1">
         <v>237744</v>
       </c>
-      <c r="L42" s="1">
-        <v>0</v>
-      </c>
       <c r="M42" s="1">
-        <v>4374.24</v>
+        <v>0</v>
       </c>
       <c r="N42" s="1">
         <v>4374.24</v>
       </c>
-      <c r="O42" s="2">
+      <c r="O42" s="1">
+        <v>4374.24</v>
+      </c>
+      <c r="P42" s="2">
         <v>1.874380543506253E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>238</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="s">
+        <v>313</v>
+      </c>
+      <c r="C43">
         <v>34</v>
       </c>
-      <c r="C43" s="1">
+      <c r="D43" s="1">
         <v>45832.9</v>
       </c>
-      <c r="D43" s="1">
+      <c r="E43" s="1">
         <v>1348.03</v>
       </c>
-      <c r="E43">
-        <v>0</v>
-      </c>
-      <c r="F43" s="1">
+      <c r="F43">
         <v>0</v>
       </c>
       <c r="G43" s="1">
         <v>0</v>
       </c>
-      <c r="H43">
+      <c r="H43" s="1">
+        <v>0</v>
+      </c>
+      <c r="I43">
         <v>34</v>
       </c>
-      <c r="I43" s="1">
+      <c r="J43" s="1">
         <v>45833.02</v>
       </c>
-      <c r="J43" s="1">
+      <c r="K43" s="1">
         <v>1346</v>
       </c>
-      <c r="K43" s="1">
+      <c r="L43" s="1">
         <v>45764</v>
       </c>
-      <c r="L43" s="1">
-        <v>0</v>
-      </c>
       <c r="M43" s="1">
-        <v>-69.02</v>
+        <v>0</v>
       </c>
       <c r="N43" s="1">
         <v>-69.02</v>
       </c>
-      <c r="O43" s="2">
+      <c r="O43" s="1">
+        <v>-69.02</v>
+      </c>
+      <c r="P43" s="2">
         <v>-1.5059051467395689E-3</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>210</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="s">
+        <v>313</v>
+      </c>
+      <c r="C44">
         <v>600</v>
       </c>
-      <c r="C44" s="1">
+      <c r="D44" s="1">
         <v>26682</v>
       </c>
-      <c r="D44" s="1">
+      <c r="E44" s="1">
         <v>44.47</v>
       </c>
-      <c r="E44">
+      <c r="F44">
         <v>600</v>
       </c>
-      <c r="F44" s="1">
+      <c r="G44" s="1">
         <v>22532.01</v>
       </c>
-      <c r="G44" s="1">
+      <c r="H44" s="1">
         <v>37.549999999999997</v>
       </c>
-      <c r="H44">
-        <v>0</v>
-      </c>
-      <c r="I44" s="1">
+      <c r="I44">
         <v>0</v>
       </c>
       <c r="J44" s="1">
+        <v>0</v>
+      </c>
+      <c r="K44" s="1">
         <v>39.81</v>
       </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
       <c r="L44" s="1">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
         <v>-4149.99</v>
       </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
       <c r="N44" s="1">
+        <v>0</v>
+      </c>
+      <c r="O44" s="1">
         <v>-4149.99</v>
       </c>
-      <c r="O44" s="2">
+      <c r="P44" s="2">
         <v>-0.1555351922644479</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>66</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="s">
+        <v>313</v>
+      </c>
+      <c r="C45">
         <v>57</v>
       </c>
-      <c r="C45" s="1">
+      <c r="D45" s="1">
         <v>50160</v>
       </c>
-      <c r="D45" s="1">
+      <c r="E45" s="1">
         <v>880</v>
       </c>
-      <c r="E45">
+      <c r="F45">
         <v>57</v>
       </c>
-      <c r="F45" s="1">
+      <c r="G45" s="1">
         <v>44850.6</v>
       </c>
-      <c r="G45" s="1">
+      <c r="H45" s="1">
         <v>786.85</v>
       </c>
-      <c r="H45">
-        <v>0</v>
-      </c>
-      <c r="I45" s="1">
+      <c r="I45">
         <v>0</v>
       </c>
       <c r="J45" s="1">
+        <v>0</v>
+      </c>
+      <c r="K45" s="1">
         <v>669.2</v>
       </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
       <c r="L45" s="1">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
         <v>-5309.4</v>
       </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
       <c r="N45" s="1">
+        <v>0</v>
+      </c>
+      <c r="O45" s="1">
         <v>-5309.4</v>
       </c>
-      <c r="O45" s="2">
+      <c r="P45" s="2">
         <v>-0.10584928229665071</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>27</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46">
         <v>20</v>
       </c>
-      <c r="C46" s="1">
+      <c r="D46" s="1">
         <v>90180</v>
       </c>
-      <c r="D46" s="1">
+      <c r="E46" s="1">
         <v>4509</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>16</v>
       </c>
-      <c r="F46" s="1">
+      <c r="G46" s="1">
         <v>66882.099600000001</v>
       </c>
-      <c r="G46" s="1">
+      <c r="H46" s="1">
         <v>4180.13</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <v>4</v>
       </c>
-      <c r="I46" s="1">
+      <c r="J46" s="1">
         <v>18036</v>
       </c>
-      <c r="J46" s="1">
+      <c r="K46" s="1">
         <v>3947.7</v>
       </c>
-      <c r="K46" s="1">
+      <c r="L46" s="1">
         <v>15790.8</v>
       </c>
-      <c r="L46" s="1">
+      <c r="M46" s="1">
         <v>-5261.9</v>
       </c>
-      <c r="M46" s="1">
+      <c r="N46" s="1">
         <v>-2245.1999999999998</v>
       </c>
-      <c r="N46" s="1">
+      <c r="O46" s="1">
         <v>-7507.1</v>
       </c>
-      <c r="O46" s="2">
+      <c r="P46" s="2">
         <v>-8.3245730760700826E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>272</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="s">
+        <v>313</v>
+      </c>
+      <c r="C47">
         <v>80</v>
       </c>
-      <c r="C47" s="1">
+      <c r="D47" s="1">
         <v>25175.98</v>
       </c>
-      <c r="D47" s="1">
+      <c r="E47" s="1">
         <v>314.7</v>
       </c>
-      <c r="E47">
-        <v>0</v>
-      </c>
-      <c r="F47" s="1">
+      <c r="F47">
         <v>0</v>
       </c>
       <c r="G47" s="1">
         <v>0</v>
       </c>
-      <c r="H47">
+      <c r="H47" s="1">
+        <v>0</v>
+      </c>
+      <c r="I47">
         <v>80</v>
       </c>
-      <c r="I47" s="1">
+      <c r="J47" s="1">
         <v>25176</v>
       </c>
-      <c r="J47" s="1">
+      <c r="K47" s="1">
         <v>293.64999999999998</v>
       </c>
-      <c r="K47" s="1">
+      <c r="L47" s="1">
         <v>23492</v>
       </c>
-      <c r="L47" s="1">
-        <v>0</v>
-      </c>
       <c r="M47" s="1">
-        <v>-1684</v>
+        <v>0</v>
       </c>
       <c r="N47" s="1">
         <v>-1684</v>
       </c>
-      <c r="O47" s="2">
+      <c r="O47" s="1">
+        <v>-1684</v>
+      </c>
+      <c r="P47" s="2">
         <v>-6.688915386809173E-2</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>257</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="s">
+        <v>313</v>
+      </c>
+      <c r="C48">
         <v>55</v>
       </c>
-      <c r="C48" s="1">
+      <c r="D48" s="1">
         <v>49398.5</v>
       </c>
-      <c r="D48" s="1">
+      <c r="E48" s="1">
         <v>898.15</v>
       </c>
-      <c r="E48">
-        <v>0</v>
-      </c>
-      <c r="F48" s="1">
+      <c r="F48">
         <v>0</v>
       </c>
       <c r="G48" s="1">
         <v>0</v>
       </c>
-      <c r="H48">
+      <c r="H48" s="1">
+        <v>0</v>
+      </c>
+      <c r="I48">
         <v>55</v>
       </c>
-      <c r="I48" s="1">
+      <c r="J48" s="1">
         <v>49398.25</v>
       </c>
-      <c r="J48" s="1">
+      <c r="K48" s="1">
         <v>878.75</v>
       </c>
-      <c r="K48" s="1">
+      <c r="L48" s="1">
         <v>48331.25</v>
       </c>
-      <c r="L48" s="1">
-        <v>0</v>
-      </c>
       <c r="M48" s="1">
-        <v>-1067</v>
+        <v>0</v>
       </c>
       <c r="N48" s="1">
         <v>-1067</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O48" s="1">
+        <v>-1067</v>
+      </c>
+      <c r="P48" s="2">
         <v>-2.1599846149174571E-2</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>30</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="s">
+        <v>312</v>
+      </c>
+      <c r="C49">
         <v>25</v>
       </c>
-      <c r="C49" s="1">
+      <c r="D49" s="1">
         <v>91567.5</v>
       </c>
-      <c r="D49" s="1">
+      <c r="E49" s="1">
         <v>3662.7</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>25</v>
       </c>
-      <c r="F49" s="1">
+      <c r="G49" s="1">
         <v>84762.5</v>
       </c>
-      <c r="G49" s="1">
+      <c r="H49" s="1">
         <v>3390.5</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49" s="1">
+      <c r="I49">
         <v>0</v>
       </c>
       <c r="J49" s="1">
+        <v>0</v>
+      </c>
+      <c r="K49" s="1">
         <v>4244.6000000000004</v>
       </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
       <c r="L49" s="1">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
         <v>-6805</v>
       </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
       <c r="N49" s="1">
+        <v>0</v>
+      </c>
+      <c r="O49" s="1">
         <v>-6805</v>
       </c>
-      <c r="O49" s="2">
+      <c r="P49" s="2">
         <v>-7.431676085947525E-2</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>156</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="s">
+        <v>313</v>
+      </c>
+      <c r="C50">
         <v>22</v>
       </c>
-      <c r="C50" s="1">
+      <c r="D50" s="1">
         <v>101483.5</v>
       </c>
-      <c r="D50" s="1">
+      <c r="E50" s="1">
         <v>4612.8900000000003</v>
       </c>
-      <c r="E50">
+      <c r="F50">
         <v>22</v>
       </c>
-      <c r="F50" s="1">
+      <c r="G50" s="1">
         <v>88669.197999999989</v>
       </c>
-      <c r="G50" s="1">
+      <c r="H50" s="1">
         <v>4030.42</v>
       </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50" s="1">
+      <c r="I50">
         <v>0</v>
       </c>
       <c r="J50" s="1">
+        <v>0</v>
+      </c>
+      <c r="K50" s="1">
         <v>3700.9</v>
       </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
       <c r="L50" s="1">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
         <v>-12814.38</v>
       </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
       <c r="N50" s="1">
+        <v>0</v>
+      </c>
+      <c r="O50" s="1">
         <v>-12814.38</v>
       </c>
-      <c r="O50" s="2">
+      <c r="P50" s="2">
         <v>-0.1262705760049663</v>
       </c>
     </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="s">
+        <v>311</v>
+      </c>
+      <c r="C51">
         <v>37</v>
       </c>
-      <c r="C51" s="1">
+      <c r="D51" s="1">
         <v>47700.4</v>
       </c>
-      <c r="D51" s="1">
+      <c r="E51" s="1">
         <v>1289.2</v>
       </c>
-      <c r="E51">
-        <v>0</v>
-      </c>
-      <c r="F51" s="1">
+      <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
       </c>
-      <c r="H51">
+      <c r="H51" s="1">
+        <v>0</v>
+      </c>
+      <c r="I51">
         <v>37</v>
       </c>
-      <c r="I51" s="1">
+      <c r="J51" s="1">
         <v>47700.4</v>
       </c>
-      <c r="J51" s="1">
+      <c r="K51" s="1">
         <v>1121.3</v>
       </c>
-      <c r="K51" s="1">
+      <c r="L51" s="1">
         <v>41488.1</v>
       </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
       <c r="M51" s="1">
-        <v>-6212.3</v>
+        <v>0</v>
       </c>
       <c r="N51" s="1">
         <v>-6212.3</v>
       </c>
-      <c r="O51" s="2">
+      <c r="O51" s="1">
+        <v>-6212.3</v>
+      </c>
+      <c r="P51" s="2">
         <v>-0.13023580515048089</v>
       </c>
     </row>

--- a/Transformed_Tradebook.xlsx
+++ b/Transformed_Tradebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/143b6e31b9e74e02/Desktop/Projects/stockjournal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_28C34E415CEA97DD4F394E7496E91191A07EBC32" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC48A90F-05EC-4098-83A6-E159AB3B9B60}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_AA78CF5F257A5AA813B84D7496E91191C0FEF95A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E54A671-1C06-44B9-8AD3-AE781D2692B1}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Tradebook" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3194" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="327">
   <si>
     <t>Unnamed: 0.1</t>
   </si>
@@ -968,6 +968,9 @@
   </si>
   <si>
     <t>Unrealized_PnL</t>
+  </si>
+  <si>
+    <t>Holding_Period</t>
   </si>
   <si>
     <t>Mid Cap</t>
@@ -1349,8 +1352,20 @@
   <dimension ref="A1:O306"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="10" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -16667,7 +16682,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:Q28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -16680,10 +16695,10 @@
     <col min="8" max="9" width="15" bestFit="1" customWidth="1"/>
     <col min="10" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16732,13 +16747,16 @@
       <c r="P1" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C2" t="s">
         <v>293</v>
@@ -16782,13 +16800,16 @@
       <c r="P2" s="1">
         <v>222.8</v>
       </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>254</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
         <v>292</v>
@@ -16832,13 +16853,16 @@
       <c r="P3" s="1">
         <v>-3816</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C4" t="s">
         <v>292</v>
@@ -16882,13 +16906,16 @@
       <c r="P4" s="1">
         <v>292.5</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C5" t="s">
         <v>294</v>
@@ -16932,13 +16959,16 @@
       <c r="P5" s="1">
         <v>-976.5</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>236</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
         <v>292</v>
@@ -16982,13 +17012,16 @@
       <c r="P6" s="1">
         <v>3216.78</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C7" t="s">
         <v>293</v>
@@ -17032,13 +17065,16 @@
       <c r="P7" s="1">
         <v>-1225.9000000000001</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q7">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
         <v>293</v>
@@ -17082,13 +17118,16 @@
       <c r="P8" s="1">
         <v>-900</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q8">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C9" t="s">
         <v>296</v>
@@ -17132,13 +17171,16 @@
       <c r="P9" s="1">
         <v>-1045.25</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q9">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C10" t="s">
         <v>296</v>
@@ -17182,13 +17224,16 @@
       <c r="P10" s="1">
         <v>-70388.800000000003</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q10">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C11" t="s">
         <v>299</v>
@@ -17232,13 +17277,16 @@
       <c r="P11" s="1">
         <v>35488.160000000003</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q11">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C12" t="s">
         <v>294</v>
@@ -17282,13 +17330,16 @@
       <c r="P12" s="1">
         <v>-1086</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q12">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C13" t="s">
         <v>296</v>
@@ -17332,13 +17383,16 @@
       <c r="P13" s="1">
         <v>-1764.64</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q13">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C14" t="s">
         <v>294</v>
@@ -17382,13 +17436,16 @@
       <c r="P14" s="1">
         <v>-8663.64</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q14">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C15" t="s">
         <v>297</v>
@@ -17432,13 +17489,16 @@
       <c r="P15" s="1">
         <v>-45543.519999999997</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q15">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C16" t="s">
         <v>299</v>
@@ -17482,13 +17542,16 @@
       <c r="P16" s="1">
         <v>29244.27</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q16">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C17" t="s">
         <v>292</v>
@@ -17532,13 +17595,16 @@
       <c r="P17" s="1">
         <v>-16072</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q17">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C18" t="s">
         <v>294</v>
@@ -17582,13 +17648,16 @@
       <c r="P18" s="1">
         <v>-5075.8999999999996</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q18">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>220</v>
       </c>
       <c r="B19" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C19" t="s">
         <v>296</v>
@@ -17632,13 +17701,16 @@
       <c r="P19" s="1">
         <v>-403.2</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q19">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>285</v>
       </c>
       <c r="B20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
         <v>293</v>
@@ -17682,13 +17754,16 @@
       <c r="P20" s="1">
         <v>-6.05</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q20">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C21" t="s">
         <v>293</v>
@@ -17732,13 +17807,16 @@
       <c r="P21" s="1">
         <v>-1410</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C22" t="s">
         <v>299</v>
@@ -17782,13 +17860,16 @@
       <c r="P22" s="1">
         <v>37295.1</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q22">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C23" t="s">
         <v>292</v>
@@ -17832,13 +17913,16 @@
       <c r="P23" s="1">
         <v>-2696</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q23">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C24" t="s">
         <v>297</v>
@@ -17882,13 +17966,16 @@
       <c r="P24" s="1">
         <v>4374.24</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q24">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C25" t="s">
         <v>296</v>
@@ -17932,13 +18019,16 @@
       <c r="P25" s="1">
         <v>-69.02</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>273</v>
       </c>
       <c r="B26" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C26" t="s">
         <v>293</v>
@@ -17982,13 +18072,16 @@
       <c r="P26" s="1">
         <v>-1684</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C27" t="s">
         <v>294</v>
@@ -18032,13 +18125,16 @@
       <c r="P27" s="1">
         <v>-1067</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q27">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s">
         <v>293</v>
@@ -18081,6 +18177,9 @@
       </c>
       <c r="P28" s="1">
         <v>-6212.3</v>
+      </c>
+      <c r="Q28">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -18090,7 +18189,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q51"/>
+  <dimension ref="A1:R51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
@@ -18110,9 +18209,10 @@
     <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -18123,22 +18223,22 @@
         <v>301</v>
       </c>
       <c r="D1" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E1" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F1" t="s">
         <v>303</v>
       </c>
       <c r="G1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="I1" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="J1" t="s">
         <v>302</v>
@@ -18153,24 +18253,27 @@
         <v>313</v>
       </c>
       <c r="N1" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="O1" t="s">
         <v>314</v>
       </c>
       <c r="P1" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q1" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+      <c r="R1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C2" t="s">
         <v>293</v>
@@ -18217,13 +18320,16 @@
       <c r="Q2" s="2">
         <v>1.896945135033886E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>254</v>
       </c>
       <c r="B3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C3" t="s">
         <v>292</v>
@@ -18270,13 +18376,16 @@
       <c r="Q3" s="2">
         <v>-3.7897745893021723E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C4" t="s">
         <v>298</v>
@@ -18323,13 +18432,16 @@
       <c r="Q4" s="2">
         <v>-7.2121731666699815E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C5" t="s">
         <v>292</v>
@@ -18376,13 +18488,16 @@
       <c r="Q5" s="2">
         <v>-0.15634980274281421</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R5">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C6" t="s">
         <v>292</v>
@@ -18429,13 +18544,16 @@
       <c r="Q6" s="2">
         <v>-4.2127959339530723E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R6">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C7" t="s">
         <v>294</v>
@@ -18482,13 +18600,16 @@
       <c r="Q7" s="2">
         <v>-1.2988925295123939E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R7">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C8" t="s">
         <v>292</v>
@@ -18535,13 +18656,16 @@
       <c r="Q8" s="2">
         <v>3.1919387367810019E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R8">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>154</v>
       </c>
       <c r="B9" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C9" t="s">
         <v>293</v>
@@ -18588,13 +18712,16 @@
       <c r="Q9" s="2">
         <v>1.635815755488592E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R9">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C10" t="s">
         <v>293</v>
@@ -18641,13 +18768,16 @@
       <c r="Q10" s="2">
         <v>-4.0658145227087307E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R10">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C11" t="s">
         <v>293</v>
@@ -18694,13 +18824,16 @@
       <c r="Q11" s="2">
         <v>-1.784694396605711E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R11">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C12" t="s">
         <v>294</v>
@@ -18747,13 +18880,16 @@
       <c r="Q12" s="2">
         <v>-9.7650586039835993E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R12">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C13" t="s">
         <v>297</v>
@@ -18800,13 +18936,16 @@
       <c r="Q13" s="2">
         <v>-1.5179777329596531E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R13">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C14" t="s">
         <v>296</v>
@@ -18853,13 +18992,16 @@
       <c r="Q14" s="2">
         <v>-1.126705641788092E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R14">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C15" t="s">
         <v>293</v>
@@ -18906,13 +19048,16 @@
       <c r="Q15" s="2">
         <v>-0.19539816748677671</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R15">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C16" t="s">
         <v>292</v>
@@ -18959,13 +19104,16 @@
       <c r="Q16" s="2">
         <v>-0.16108205823487631</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>193</v>
       </c>
       <c r="B17" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C17" t="s">
         <v>296</v>
@@ -19012,13 +19160,16 @@
       <c r="Q17" s="2">
         <v>-0.54607109448082325</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C18" t="s">
         <v>292</v>
@@ -19065,13 +19216,16 @@
       <c r="Q18" s="2">
         <v>-0.14124164590966029</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C19" t="s">
         <v>293</v>
@@ -19118,13 +19272,16 @@
       <c r="Q19" s="2">
         <v>-0.1015625</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>142</v>
       </c>
       <c r="B20" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C20" t="s">
         <v>299</v>
@@ -19171,13 +19328,16 @@
       <c r="Q20" s="2">
         <v>0.1181814839541918</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R20">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C21" t="s">
         <v>294</v>
@@ -19224,13 +19384,16 @@
       <c r="Q21" s="2">
         <v>-2.1620851101020942E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R21">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C22" t="s">
         <v>296</v>
@@ -19277,13 +19440,16 @@
       <c r="Q22" s="2">
         <v>-8.7397888650716238E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C23" t="s">
         <v>292</v>
@@ -19330,13 +19496,16 @@
       <c r="Q23" s="2">
         <v>-0.17265855457227139</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
         <v>294</v>
@@ -19383,13 +19552,16 @@
       <c r="Q24" s="2">
         <v>-0.1126134809293286</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C25" t="s">
         <v>297</v>
@@ -19436,13 +19608,16 @@
       <c r="Q25" s="2">
         <v>-0.2294130773481414</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C26" t="s">
         <v>299</v>
@@ -19489,13 +19664,16 @@
       <c r="Q26" s="2">
         <v>0.14022313022513869</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C27" t="s">
         <v>292</v>
@@ -19542,13 +19720,16 @@
       <c r="Q27" s="2">
         <v>-0.16220130340333089</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C28" t="s">
         <v>294</v>
@@ -19595,13 +19776,16 @@
       <c r="Q28" s="2">
         <v>-7.2320381612935844E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C29" t="s">
         <v>293</v>
@@ -19648,13 +19832,16 @@
       <c r="Q29" s="2">
         <v>-9.7171155551569868E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C30" t="s">
         <v>294</v>
@@ -19701,13 +19888,16 @@
       <c r="Q30" s="2">
         <v>-0.17667114643858131</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C31" t="s">
         <v>293</v>
@@ -19754,13 +19944,16 @@
       <c r="Q31" s="2">
         <v>-0.14019473604138141</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C32" t="s">
         <v>296</v>
@@ -19807,13 +20000,16 @@
       <c r="Q32" s="2">
         <v>-7.9214627829756919E-3</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" t="s">
         <v>292</v>
@@ -19860,13 +20056,16 @@
       <c r="Q33" s="2">
         <v>-0.1109521617118302</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>285</v>
       </c>
       <c r="B34" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C34" t="s">
         <v>293</v>
@@ -19913,13 +20112,16 @@
       <c r="Q34" s="2">
         <v>-2.4201355275895451E-4</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C35" t="s">
         <v>293</v>
@@ -19966,13 +20168,16 @@
       <c r="Q35" s="2">
         <v>-5.5627884956799621E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" t="s">
         <v>292</v>
@@ -20019,13 +20224,16 @@
       <c r="Q36" s="2">
         <v>-0.51718403311145245</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C37" t="s">
         <v>294</v>
@@ -20072,13 +20280,16 @@
       <c r="Q37" s="2">
         <v>-6.3742898422480723E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R37">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C38" t="s">
         <v>299</v>
@@ -20125,13 +20336,16 @@
       <c r="Q38" s="2">
         <v>0.12964046982595301</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R38">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C39" t="s">
         <v>292</v>
@@ -20178,13 +20392,16 @@
       <c r="Q39" s="2">
         <v>-0.10748007986573591</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R39">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C40" t="s">
         <v>294</v>
@@ -20231,13 +20448,16 @@
       <c r="Q40" s="2">
         <v>9.7625625824357127E-5</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R40">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>263</v>
       </c>
       <c r="B41" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C41" t="s">
         <v>293</v>
@@ -20284,13 +20504,16 @@
       <c r="Q41" s="2">
         <v>-0.1328714714093682</v>
       </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R41">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C42" t="s">
         <v>297</v>
@@ -20337,13 +20560,16 @@
       <c r="Q42" s="2">
         <v>1.874380543506253E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R42">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>239</v>
       </c>
       <c r="B43" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C43" t="s">
         <v>296</v>
@@ -20390,13 +20616,16 @@
       <c r="Q43" s="2">
         <v>-1.5059051467395689E-3</v>
       </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R43">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>211</v>
       </c>
       <c r="B44" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C44" t="s">
         <v>293</v>
@@ -20443,13 +20672,16 @@
       <c r="Q44" s="2">
         <v>-0.1555351922644479</v>
       </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R44">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" t="s">
         <v>293</v>
@@ -20496,13 +20728,16 @@
       <c r="Q45" s="2">
         <v>-0.10584928229665071</v>
       </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C46" t="s">
         <v>292</v>
@@ -20549,13 +20784,16 @@
       <c r="Q46" s="2">
         <v>-7.2933022843202494E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R46">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>273</v>
       </c>
       <c r="B47" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C47" t="s">
         <v>293</v>
@@ -20602,13 +20840,16 @@
       <c r="Q47" s="2">
         <v>-6.688915386809173E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R47">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C48" t="s">
         <v>294</v>
@@ -20655,13 +20896,16 @@
       <c r="Q48" s="2">
         <v>-2.1599846149174571E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R48">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C49" t="s">
         <v>292</v>
@@ -20708,13 +20952,16 @@
       <c r="Q49" s="2">
         <v>-7.431676085947525E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>157</v>
       </c>
       <c r="B50" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C50" t="s">
         <v>294</v>
@@ -20761,13 +21008,16 @@
       <c r="Q50" s="2">
         <v>-0.1262705760049663</v>
       </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R50">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C51" t="s">
         <v>293</v>
@@ -20813,6 +21063,9 @@
       </c>
       <c r="Q51" s="2">
         <v>-0.13023580515048089</v>
+      </c>
+      <c r="R51">
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/Transformed_Tradebook.xlsx
+++ b/Transformed_Tradebook.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/143b6e31b9e74e02/Desktop/Projects/stockjournal/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_AA78CF5F257A5AA813B84D7496E91191C0FEF95A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E54A671-1C06-44B9-8AD3-AE781D2692B1}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_C42ECD4441221180310B4631DE6A1D9190F7FE4A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E64D2120-31D8-498A-B1E6-9AEA8446E864}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Raw_Tradebook" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3200" uniqueCount="329">
   <si>
     <t>Unnamed: 0.1</t>
   </si>
@@ -926,6 +926,12 @@
   </si>
   <si>
     <t>Cap</t>
+  </si>
+  <si>
+    <t>TF_Sector</t>
+  </si>
+  <si>
+    <t>TF_Classification</t>
   </si>
   <si>
     <t>Latest_Tranche</t>
@@ -1351,22 +1357,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:O306"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.5703125" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -13905,15 +13895,6 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G120"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -16682,23 +16663,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:S28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -16750,1435 +16722,1441 @@
       <c r="Q1" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R1" t="s">
+        <v>316</v>
+      </c>
+      <c r="S1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E2" t="s">
         <v>293</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>4</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>2936.3</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>2642.67</v>
       </c>
-      <c r="G2" s="1">
+      <c r="I2" s="1">
         <v>349.33</v>
       </c>
-      <c r="H2" s="2">
+      <c r="J2" s="2">
         <v>0.116754679144385</v>
       </c>
-      <c r="I2" s="1">
+      <c r="K2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="J2" s="1">
+      <c r="L2" s="1">
         <v>2992</v>
       </c>
-      <c r="K2" s="1">
+      <c r="M2" s="1">
         <v>2966.46</v>
       </c>
-      <c r="L2" s="1">
+      <c r="N2" s="1">
         <v>2964.14</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>2961.54</v>
       </c>
-      <c r="N2" s="1">
+      <c r="P2" s="1">
         <v>2928.94</v>
       </c>
-      <c r="O2" s="1">
+      <c r="Q2" s="1">
         <v>11968</v>
       </c>
-      <c r="P2" s="1">
+      <c r="R2" s="1">
         <v>222.8</v>
       </c>
-      <c r="Q2">
+      <c r="S2">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>254</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" t="s">
         <v>292</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>45</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>2237.6</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>2013.84</v>
       </c>
-      <c r="G3" s="1">
+      <c r="I3" s="1">
         <v>138.96</v>
       </c>
-      <c r="H3" s="2">
+      <c r="J3" s="2">
         <v>6.4548494983277707E-2</v>
       </c>
-      <c r="I3" s="1">
+      <c r="K3" s="1">
         <v>100692</v>
       </c>
-      <c r="J3" s="1">
+      <c r="L3" s="1">
         <v>2152.8000000000002</v>
       </c>
-      <c r="K3" s="1">
+      <c r="M3" s="1">
         <v>2183.5300000000002</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>2185.14</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>2186.16</v>
       </c>
-      <c r="N3" s="1">
+      <c r="P3" s="1">
         <v>2173.39</v>
       </c>
-      <c r="O3" s="1">
+      <c r="Q3" s="1">
         <v>96876</v>
       </c>
-      <c r="P3" s="1">
+      <c r="R3" s="1">
         <v>-3816</v>
       </c>
-      <c r="Q3">
+      <c r="S3">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>139</v>
       </c>
       <c r="B4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C4" t="s">
+        <v>319</v>
+      </c>
+      <c r="E4" t="s">
         <v>292</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>90</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>292.10000000000002</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>262.89</v>
       </c>
-      <c r="G4" s="1">
+      <c r="I4" s="1">
         <v>32.46</v>
       </c>
-      <c r="H4" s="2">
+      <c r="J4" s="2">
         <v>0.1099035043169123</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>26289</v>
       </c>
-      <c r="J4" s="1">
+      <c r="L4" s="1">
         <v>295.35000000000002</v>
       </c>
-      <c r="K4" s="1">
+      <c r="M4" s="1">
         <v>306.04000000000002</v>
       </c>
-      <c r="L4" s="1">
+      <c r="N4" s="1">
         <v>306.10000000000002</v>
       </c>
-      <c r="M4" s="1">
+      <c r="O4" s="1">
         <v>306.07</v>
       </c>
-      <c r="N4" s="1">
+      <c r="P4" s="1">
         <v>304.31</v>
       </c>
-      <c r="O4" s="1">
+      <c r="Q4" s="1">
         <v>26581.5</v>
       </c>
-      <c r="P4" s="1">
+      <c r="R4" s="1">
         <v>292.5</v>
       </c>
-      <c r="Q4">
+      <c r="S4">
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>217</v>
       </c>
       <c r="B5" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" t="s">
+        <v>318</v>
+      </c>
+      <c r="E5" t="s">
         <v>294</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>465</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>161.68</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>145.51</v>
       </c>
-      <c r="G5" s="1">
+      <c r="I5" s="1">
         <v>14.07</v>
       </c>
-      <c r="H5" s="2">
+      <c r="J5" s="2">
         <v>8.8168943476626266E-2</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>75181.2</v>
       </c>
-      <c r="J5" s="1">
+      <c r="L5" s="1">
         <v>159.58000000000001</v>
       </c>
-      <c r="K5" s="1">
+      <c r="M5" s="1">
         <v>167.76</v>
       </c>
-      <c r="L5" s="1">
+      <c r="N5" s="1">
         <v>167.99</v>
       </c>
-      <c r="M5" s="1">
+      <c r="O5" s="1">
         <v>168.13</v>
       </c>
-      <c r="N5" s="1">
+      <c r="P5" s="1">
         <v>167.33</v>
       </c>
-      <c r="O5" s="1">
+      <c r="Q5" s="1">
         <v>74204.7</v>
       </c>
-      <c r="P5" s="1">
+      <c r="R5" s="1">
         <v>-976.5</v>
       </c>
-      <c r="Q5">
+      <c r="S5">
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>236</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" t="s">
         <v>292</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>222</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>453.96</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>408.56</v>
       </c>
-      <c r="G6" s="1">
+      <c r="I6" s="1">
         <v>59.89</v>
       </c>
-      <c r="H6" s="2">
+      <c r="J6" s="2">
         <v>0.12784715551286149</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>100779.12</v>
       </c>
-      <c r="J6" s="1">
+      <c r="L6" s="1">
         <v>468.45</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>450.39</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>449.47</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>448.64</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>442.22</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>103995.9</v>
       </c>
-      <c r="P6" s="1">
+      <c r="R6" s="1">
         <v>3216.78</v>
       </c>
-      <c r="Q6">
+      <c r="S6">
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>130</v>
       </c>
       <c r="B7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C7" t="s">
+        <v>319</v>
+      </c>
+      <c r="E7" t="s">
         <v>293</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>82</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>367.7</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>330.93</v>
       </c>
-      <c r="G7" s="1">
+      <c r="I7" s="1">
         <v>21.82</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>6.1856839121190617E-2</v>
       </c>
-      <c r="I7" s="1">
+      <c r="K7" s="1">
         <v>30151.4</v>
       </c>
-      <c r="J7" s="1">
+      <c r="L7" s="1">
         <v>352.75</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>367.39</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>368.05</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>368.58</v>
       </c>
-      <c r="N7" s="1">
+      <c r="P7" s="1">
         <v>369.89</v>
       </c>
-      <c r="O7" s="1">
+      <c r="Q7" s="1">
         <v>28925.5</v>
       </c>
-      <c r="P7" s="1">
+      <c r="R7" s="1">
         <v>-1225.9000000000001</v>
       </c>
-      <c r="Q7">
+      <c r="S7">
         <v>125</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" t="s">
         <v>293</v>
       </c>
-      <c r="D8">
-        <v>18</v>
-      </c>
-      <c r="E8" s="1">
+      <c r="F8">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1">
         <v>2801.6</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>2521.44</v>
       </c>
-      <c r="G8" s="1">
+      <c r="I8" s="1">
         <v>230.16</v>
       </c>
-      <c r="H8" s="2">
+      <c r="J8" s="2">
         <v>8.3645878761447828E-2</v>
       </c>
-      <c r="I8" s="1">
+      <c r="K8" s="1">
         <v>50428.800000000003</v>
       </c>
-      <c r="J8" s="1">
+      <c r="L8" s="1">
         <v>2751.6</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>2738.6</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>2743.38</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
         <v>2748.12</v>
       </c>
-      <c r="N8" s="1">
+      <c r="P8" s="1">
         <v>2779.22</v>
       </c>
-      <c r="O8" s="1">
+      <c r="Q8" s="1">
         <v>49528.800000000003</v>
       </c>
-      <c r="P8" s="1">
+      <c r="R8" s="1">
         <v>-900</v>
       </c>
-      <c r="Q8">
+      <c r="S8">
         <v>90</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>317</v>
-      </c>
-      <c r="C9" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" t="s">
         <v>296</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>37</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>743.7</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>669.33</v>
       </c>
-      <c r="G9" s="1">
+      <c r="I9" s="1">
         <v>46.12</v>
       </c>
-      <c r="H9" s="2">
+      <c r="J9" s="2">
         <v>6.4462925431546581E-2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>27516.9</v>
       </c>
-      <c r="J9" s="1">
+      <c r="L9" s="1">
         <v>715.45</v>
       </c>
-      <c r="K9" s="1">
+      <c r="M9" s="1">
         <v>707.53</v>
       </c>
-      <c r="L9" s="1">
+      <c r="N9" s="1">
         <v>706.75</v>
       </c>
-      <c r="M9" s="1">
+      <c r="O9" s="1">
         <v>705.78</v>
       </c>
-      <c r="N9" s="1">
+      <c r="P9" s="1">
         <v>691.8</v>
       </c>
-      <c r="O9" s="1">
+      <c r="Q9" s="1">
         <v>26471.65</v>
       </c>
-      <c r="P9" s="1">
+      <c r="R9" s="1">
         <v>-1045.25</v>
       </c>
-      <c r="Q9">
+      <c r="S9">
         <v>174</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>193</v>
       </c>
       <c r="B10" t="s">
-        <v>316</v>
-      </c>
-      <c r="C10" t="s">
+        <v>318</v>
+      </c>
+      <c r="E10" t="s">
         <v>296</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>205</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>423.8</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>381.42</v>
       </c>
-      <c r="G10" s="1">
+      <c r="I10" s="1">
         <v>-300.98</v>
       </c>
-      <c r="H10" s="2">
+      <c r="J10" s="2">
         <v>-3.7416708105420189</v>
       </c>
-      <c r="I10" s="1">
+      <c r="K10" s="1">
         <v>86879</v>
       </c>
-      <c r="J10" s="1">
+      <c r="L10" s="1">
         <v>80.44</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>80.709999999999994</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>80.88</v>
       </c>
-      <c r="M10" s="1">
+      <c r="O10" s="1">
         <v>81.040000000000006</v>
       </c>
-      <c r="N10" s="1">
+      <c r="P10" s="1">
         <v>82.12</v>
       </c>
-      <c r="O10" s="1">
+      <c r="Q10" s="1">
         <v>16490.2</v>
       </c>
-      <c r="P10" s="1">
+      <c r="R10" s="1">
         <v>-70388.800000000003</v>
       </c>
-      <c r="Q10">
+      <c r="S10">
         <v>62</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>316</v>
-      </c>
-      <c r="C11" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" t="s">
         <v>299</v>
       </c>
-      <c r="D11">
+      <c r="F11">
         <v>1172</v>
       </c>
-      <c r="E11" s="1">
+      <c r="G11" s="1">
         <v>256.22000000000003</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>263.82</v>
       </c>
-      <c r="G11" s="1">
+      <c r="I11" s="1">
         <v>22.68</v>
       </c>
-      <c r="H11" s="2">
+      <c r="J11" s="2">
         <v>7.9162303664921496E-2</v>
       </c>
-      <c r="I11" s="1">
+      <c r="K11" s="1">
         <v>300289.84000000003</v>
       </c>
-      <c r="J11" s="1">
+      <c r="L11" s="1">
         <v>286.5</v>
       </c>
-      <c r="K11" s="1">
+      <c r="M11" s="1">
         <v>291.52</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>291.57</v>
       </c>
-      <c r="M11" s="1">
+      <c r="O11" s="1">
         <v>291.55</v>
       </c>
-      <c r="N11" s="1">
+      <c r="P11" s="1">
         <v>289.55</v>
       </c>
-      <c r="O11" s="1">
+      <c r="Q11" s="1">
         <v>335778</v>
       </c>
-      <c r="P11" s="1">
+      <c r="R11" s="1">
         <v>35488.160000000003</v>
       </c>
-      <c r="Q11">
+      <c r="S11">
         <v>125</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>190</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" t="s">
         <v>294</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>362</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>138.75</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>124.88</v>
       </c>
-      <c r="G12" s="1">
+      <c r="I12" s="1">
         <v>10.87</v>
       </c>
-      <c r="H12" s="2">
+      <c r="J12" s="2">
         <v>8.0073664825046076E-2</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>50227.5</v>
       </c>
-      <c r="J12" s="1">
+      <c r="L12" s="1">
         <v>135.75</v>
       </c>
-      <c r="K12" s="1">
+      <c r="M12" s="1">
         <v>139.38</v>
       </c>
-      <c r="L12" s="1">
+      <c r="N12" s="1">
         <v>139.49</v>
       </c>
-      <c r="M12" s="1">
+      <c r="O12" s="1">
         <v>139.55000000000001</v>
       </c>
-      <c r="N12" s="1">
+      <c r="P12" s="1">
         <v>139.16</v>
       </c>
-      <c r="O12" s="1">
+      <c r="Q12" s="1">
         <v>49141.5</v>
       </c>
-      <c r="P12" s="1">
+      <c r="R12" s="1">
         <v>-1086</v>
       </c>
-      <c r="Q12">
+      <c r="S12">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>318</v>
-      </c>
-      <c r="C13" t="s">
+        <v>320</v>
+      </c>
+      <c r="E13" t="s">
         <v>296</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>41</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>589.89</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>530.9</v>
       </c>
-      <c r="G13" s="1">
+      <c r="I13" s="1">
         <v>15.95</v>
       </c>
-      <c r="H13" s="2">
+      <c r="J13" s="2">
         <v>2.916704763646346E-2</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>24185.49</v>
       </c>
-      <c r="J13" s="1">
+      <c r="L13" s="1">
         <v>546.85</v>
       </c>
-      <c r="K13" s="1">
+      <c r="M13" s="1">
         <v>554.23</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>555.4</v>
       </c>
-      <c r="M13" s="1">
+      <c r="O13" s="1">
         <v>556.49</v>
       </c>
-      <c r="N13" s="1">
+      <c r="P13" s="1">
         <v>563.08000000000004</v>
       </c>
-      <c r="O13" s="1">
+      <c r="Q13" s="1">
         <v>22420.85</v>
       </c>
-      <c r="P13" s="1">
+      <c r="R13" s="1">
         <v>-1764.64</v>
       </c>
-      <c r="Q13">
+      <c r="S13">
         <v>180</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>118</v>
       </c>
       <c r="B14" t="s">
-        <v>318</v>
-      </c>
-      <c r="C14" t="s">
+        <v>320</v>
+      </c>
+      <c r="E14" t="s">
         <v>294</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>276</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>278.74</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>250.87</v>
       </c>
-      <c r="G14" s="1">
+      <c r="I14" s="1">
         <v>-3.52</v>
       </c>
-      <c r="H14" s="2">
+      <c r="J14" s="2">
         <v>-1.4230846977966489E-2</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>76932.240000000005</v>
       </c>
-      <c r="J14" s="1">
+      <c r="L14" s="1">
         <v>247.35</v>
       </c>
-      <c r="K14" s="1">
+      <c r="M14" s="1">
         <v>256.63</v>
       </c>
-      <c r="L14" s="1">
+      <c r="N14" s="1">
         <v>257.2</v>
       </c>
-      <c r="M14" s="1">
+      <c r="O14" s="1">
         <v>257.67</v>
       </c>
-      <c r="N14" s="1">
+      <c r="P14" s="1">
         <v>259.11</v>
       </c>
-      <c r="O14" s="1">
+      <c r="Q14" s="1">
         <v>68268.600000000006</v>
       </c>
-      <c r="P14" s="1">
+      <c r="R14" s="1">
         <v>-8663.64</v>
       </c>
-      <c r="Q14">
+      <c r="S14">
         <v>132</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
-      </c>
-      <c r="C15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E15" t="s">
         <v>297</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>226</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>878.42</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>844.15</v>
       </c>
-      <c r="G15" s="1">
+      <c r="I15" s="1">
         <v>-167.25</v>
       </c>
-      <c r="H15" s="2">
+      <c r="J15" s="2">
         <v>-0.2470822868961442</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>198522.92</v>
       </c>
-      <c r="J15" s="1">
+      <c r="L15" s="1">
         <v>676.9</v>
       </c>
-      <c r="K15" s="1">
+      <c r="M15" s="1">
         <v>684.33</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" s="1">
         <v>687.27</v>
       </c>
-      <c r="M15" s="1">
+      <c r="O15" s="1">
         <v>690.15</v>
       </c>
-      <c r="N15" s="1">
+      <c r="P15" s="1">
         <v>715</v>
       </c>
-      <c r="O15" s="1">
+      <c r="Q15" s="1">
         <v>152979.4</v>
       </c>
-      <c r="P15" s="1">
+      <c r="R15" s="1">
         <v>-45543.519999999997</v>
       </c>
-      <c r="Q15">
+      <c r="S15">
         <v>181</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>88</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" t="s">
         <v>299</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>253</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>843.31</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>843.31</v>
       </c>
-      <c r="G16" s="1">
+      <c r="I16" s="1">
         <v>115.59</v>
       </c>
-      <c r="H16" s="2">
+      <c r="J16" s="2">
         <v>0.1205443737616019</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>213357.43</v>
       </c>
-      <c r="J16" s="1">
+      <c r="L16" s="1">
         <v>958.9</v>
       </c>
-      <c r="K16" s="1">
+      <c r="M16" s="1">
         <v>938.87</v>
       </c>
-      <c r="L16" s="1">
+      <c r="N16" s="1">
         <v>938.11</v>
       </c>
-      <c r="M16" s="1">
+      <c r="O16" s="1">
         <v>937.54</v>
       </c>
-      <c r="N16" s="1">
+      <c r="P16" s="1">
         <v>935.46</v>
       </c>
-      <c r="O16" s="1">
+      <c r="Q16" s="1">
         <v>242601.7</v>
       </c>
-      <c r="P16" s="1">
+      <c r="R16" s="1">
         <v>29244.27</v>
       </c>
-      <c r="Q16">
+      <c r="S16">
         <v>153</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>123</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
-      </c>
-      <c r="C17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17" t="s">
         <v>292</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>205</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>483.35</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>435.02</v>
       </c>
-      <c r="G17" s="1">
+      <c r="I17" s="1">
         <v>-30.07</v>
       </c>
-      <c r="H17" s="2">
+      <c r="J17" s="2">
         <v>-7.4256080997654017E-2</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>99086.75</v>
       </c>
-      <c r="J17" s="1">
+      <c r="L17" s="1">
         <v>404.95</v>
       </c>
-      <c r="K17" s="1">
+      <c r="M17" s="1">
         <v>424.12</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>425.57</v>
       </c>
-      <c r="M17" s="1">
+      <c r="O17" s="1">
         <v>426.88</v>
       </c>
-      <c r="N17" s="1">
+      <c r="P17" s="1">
         <v>435.15</v>
       </c>
-      <c r="O17" s="1">
+      <c r="Q17" s="1">
         <v>83014.75</v>
       </c>
-      <c r="P17" s="1">
+      <c r="R17" s="1">
         <v>-16072</v>
       </c>
-      <c r="Q17">
+      <c r="S17">
         <v>125</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>133</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" t="s">
         <v>294</v>
       </c>
-      <c r="D18">
+      <c r="F18">
         <v>386</v>
       </c>
-      <c r="E18" s="1">
+      <c r="G18" s="1">
         <v>181.83</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>163.65</v>
       </c>
-      <c r="G18" s="1">
+      <c r="I18" s="1">
         <v>5.03</v>
       </c>
-      <c r="H18" s="2">
+      <c r="J18" s="2">
         <v>2.9819777092719948E-2</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>70186.38</v>
       </c>
-      <c r="J18" s="1">
+      <c r="L18" s="1">
         <v>168.68</v>
       </c>
-      <c r="K18" s="1">
+      <c r="M18" s="1">
         <v>175.51</v>
       </c>
-      <c r="L18" s="1">
+      <c r="N18" s="1">
         <v>175.7</v>
       </c>
-      <c r="M18" s="1">
+      <c r="O18" s="1">
         <v>175.81</v>
       </c>
-      <c r="N18" s="1">
+      <c r="P18" s="1">
         <v>174.93</v>
       </c>
-      <c r="O18" s="1">
+      <c r="Q18" s="1">
         <v>65110.48</v>
       </c>
-      <c r="P18" s="1">
+      <c r="R18" s="1">
         <v>-5075.8999999999996</v>
       </c>
-      <c r="Q18">
+      <c r="S18">
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>220</v>
       </c>
       <c r="B19" t="s">
-        <v>316</v>
-      </c>
-      <c r="C19" t="s">
+        <v>318</v>
+      </c>
+      <c r="E19" t="s">
         <v>296</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>720</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>70.69</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>63.62</v>
       </c>
-      <c r="G19" s="1">
+      <c r="I19" s="1">
         <v>6.51</v>
       </c>
-      <c r="H19" s="2">
+      <c r="J19" s="2">
         <v>9.2827605874803917E-2</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>50896.800000000003</v>
       </c>
-      <c r="J19" s="1">
+      <c r="L19" s="1">
         <v>70.13</v>
       </c>
-      <c r="K19" s="1">
+      <c r="M19" s="1">
         <v>70.92</v>
       </c>
-      <c r="L19" s="1">
+      <c r="N19" s="1">
         <v>70.81</v>
       </c>
-      <c r="M19" s="1">
+      <c r="O19" s="1">
         <v>70.69</v>
       </c>
-      <c r="N19" s="1">
+      <c r="P19" s="1">
         <v>69.3</v>
       </c>
-      <c r="O19" s="1">
+      <c r="Q19" s="1">
         <v>50493.599999999999</v>
       </c>
-      <c r="P19" s="1">
+      <c r="R19" s="1">
         <v>-403.2</v>
       </c>
-      <c r="Q19">
+      <c r="S19">
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>285</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E20" t="s">
         <v>293</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>121</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>206.6</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>185.94</v>
       </c>
-      <c r="G20" s="1">
+      <c r="I20" s="1">
         <v>20.61</v>
       </c>
-      <c r="H20" s="2">
+      <c r="J20" s="2">
         <v>9.978213507625279E-2</v>
       </c>
-      <c r="I20" s="1">
+      <c r="K20" s="1">
         <v>24998.6</v>
       </c>
-      <c r="J20" s="1">
+      <c r="L20" s="1">
         <v>206.55</v>
       </c>
-      <c r="K20" s="1">
+      <c r="M20" s="1">
         <v>196.16</v>
       </c>
-      <c r="L20" s="1">
+      <c r="N20" s="1">
         <v>195.73</v>
       </c>
-      <c r="M20" s="1">
+      <c r="O20" s="1">
         <v>195.28</v>
       </c>
-      <c r="N20" s="1">
+      <c r="P20" s="1">
         <v>190.07</v>
       </c>
-      <c r="O20" s="1">
+      <c r="Q20" s="1">
         <v>24992.55</v>
       </c>
-      <c r="P20" s="1">
+      <c r="R20" s="1">
         <v>-6.05</v>
       </c>
-      <c r="Q20">
+      <c r="S20">
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>187</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
-      </c>
-      <c r="C21" t="s">
+        <v>318</v>
+      </c>
+      <c r="E21" t="s">
         <v>293</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>300</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>84.49</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>76.040000000000006</v>
       </c>
-      <c r="G21" s="1">
+      <c r="I21" s="1">
         <v>3.75</v>
       </c>
-      <c r="H21" s="2">
+      <c r="J21" s="2">
         <v>4.6998370723148261E-2</v>
       </c>
-      <c r="I21" s="1">
+      <c r="K21" s="1">
         <v>25347</v>
       </c>
-      <c r="J21" s="1">
+      <c r="L21" s="1">
         <v>79.790000000000006</v>
       </c>
-      <c r="K21" s="1">
+      <c r="M21" s="1">
         <v>79.849999999999994</v>
       </c>
-      <c r="L21" s="1">
+      <c r="N21" s="1">
         <v>79.91</v>
       </c>
-      <c r="M21" s="1">
+      <c r="O21" s="1">
         <v>79.959999999999994</v>
       </c>
-      <c r="N21" s="1">
+      <c r="P21" s="1">
         <v>80.09</v>
       </c>
-      <c r="O21" s="1">
+      <c r="Q21" s="1">
         <v>23937</v>
       </c>
-      <c r="P21" s="1">
+      <c r="R21" s="1">
         <v>-1410</v>
       </c>
-      <c r="Q21">
+      <c r="S21">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>317</v>
-      </c>
-      <c r="C22" t="s">
+        <v>319</v>
+      </c>
+      <c r="E22" t="s">
         <v>299</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>38</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>7570.55</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>7570.55</v>
       </c>
-      <c r="G22" s="1">
+      <c r="I22" s="1">
         <v>981.45</v>
       </c>
-      <c r="H22" s="2">
+      <c r="J22" s="2">
         <v>0.1147626286248831</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>287680.90000000002</v>
       </c>
-      <c r="J22" s="1">
+      <c r="L22" s="1">
         <v>8552</v>
       </c>
-      <c r="K22" s="1">
+      <c r="M22" s="1">
         <v>8362.5</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N22" s="1">
         <v>8333.4</v>
       </c>
-      <c r="M22" s="1">
+      <c r="O22" s="1">
         <v>8304.77</v>
       </c>
-      <c r="N22" s="1">
+      <c r="P22" s="1">
         <v>8068.43</v>
       </c>
-      <c r="O22" s="1">
+      <c r="Q22" s="1">
         <v>324976</v>
       </c>
-      <c r="P22" s="1">
+      <c r="R22" s="1">
         <v>37295.1</v>
       </c>
-      <c r="Q22">
+      <c r="S22">
         <v>181</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>81</v>
       </c>
       <c r="B23" t="s">
-        <v>318</v>
-      </c>
-      <c r="C23" t="s">
+        <v>320</v>
+      </c>
+      <c r="E23" t="s">
         <v>292</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>25</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>531.34</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>478.21</v>
       </c>
-      <c r="G23" s="1">
+      <c r="I23" s="1">
         <v>-54.71</v>
       </c>
-      <c r="H23" s="2">
+      <c r="J23" s="2">
         <v>-0.12918536009445089</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>13283.5</v>
       </c>
-      <c r="J23" s="1">
+      <c r="L23" s="1">
         <v>423.5</v>
       </c>
-      <c r="K23" s="1">
+      <c r="M23" s="1">
         <v>443.76</v>
       </c>
-      <c r="L23" s="1">
+      <c r="N23" s="1">
         <v>445.1</v>
       </c>
-      <c r="M23" s="1">
+      <c r="O23" s="1">
         <v>446.2</v>
       </c>
-      <c r="N23" s="1">
+      <c r="P23" s="1">
         <v>450.38</v>
       </c>
-      <c r="O23" s="1">
+      <c r="Q23" s="1">
         <v>10587.5</v>
       </c>
-      <c r="P23" s="1">
+      <c r="R23" s="1">
         <v>-2696</v>
       </c>
-      <c r="Q23">
+      <c r="S23">
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>136</v>
       </c>
       <c r="B24" t="s">
-        <v>317</v>
-      </c>
-      <c r="C24" t="s">
+        <v>319</v>
+      </c>
+      <c r="E24" t="s">
         <v>297</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>208</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>1121.97</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>1078</v>
       </c>
-      <c r="G24" s="1">
+      <c r="I24" s="1">
         <v>65</v>
       </c>
-      <c r="H24" s="2">
+      <c r="J24" s="2">
         <v>5.6867891513560802E-2</v>
       </c>
-      <c r="I24" s="1">
+      <c r="K24" s="1">
         <v>233369.76</v>
       </c>
-      <c r="J24" s="1">
+      <c r="L24" s="1">
         <v>1143</v>
       </c>
-      <c r="K24" s="1">
+      <c r="M24" s="1">
         <v>1180.6199999999999</v>
       </c>
-      <c r="L24" s="1">
+      <c r="N24" s="1">
         <v>1181.21</v>
       </c>
-      <c r="M24" s="1">
+      <c r="O24" s="1">
         <v>1181.26</v>
       </c>
-      <c r="N24" s="1">
+      <c r="P24" s="1">
         <v>1166.47</v>
       </c>
-      <c r="O24" s="1">
+      <c r="Q24" s="1">
         <v>237744</v>
       </c>
-      <c r="P24" s="1">
+      <c r="R24" s="1">
         <v>4374.24</v>
       </c>
-      <c r="Q24">
+      <c r="S24">
         <v>125</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>239</v>
       </c>
       <c r="B25" t="s">
-        <v>318</v>
-      </c>
-      <c r="C25" t="s">
+        <v>320</v>
+      </c>
+      <c r="E25" t="s">
         <v>296</v>
       </c>
-      <c r="D25">
+      <c r="F25">
         <v>34</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>1348.03</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>1213.23</v>
       </c>
-      <c r="G25" s="1">
+      <c r="I25" s="1">
         <v>132.77000000000001</v>
       </c>
-      <c r="H25" s="2">
+      <c r="J25" s="2">
         <v>9.8640416047548279E-2</v>
       </c>
-      <c r="I25" s="1">
+      <c r="K25" s="1">
         <v>45833.02</v>
       </c>
-      <c r="J25" s="1">
+      <c r="L25" s="1">
         <v>1346</v>
       </c>
-      <c r="K25" s="1">
+      <c r="M25" s="1">
         <v>1331.94</v>
       </c>
-      <c r="L25" s="1">
+      <c r="N25" s="1">
         <v>1331.11</v>
       </c>
-      <c r="M25" s="1">
+      <c r="O25" s="1">
         <v>1330.07</v>
       </c>
-      <c r="N25" s="1">
+      <c r="P25" s="1">
         <v>1309.1400000000001</v>
       </c>
-      <c r="O25" s="1">
+      <c r="Q25" s="1">
         <v>45764</v>
       </c>
-      <c r="P25" s="1">
+      <c r="R25" s="1">
         <v>-69.02</v>
       </c>
-      <c r="Q25">
+      <c r="S25">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>273</v>
       </c>
       <c r="B26" t="s">
-        <v>318</v>
-      </c>
-      <c r="C26" t="s">
+        <v>320</v>
+      </c>
+      <c r="E26" t="s">
         <v>293</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>80</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>314.7</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>283.23</v>
       </c>
-      <c r="G26" s="1">
+      <c r="I26" s="1">
         <v>10.42</v>
       </c>
-      <c r="H26" s="2">
+      <c r="J26" s="2">
         <v>3.5484420228162637E-2</v>
       </c>
-      <c r="I26" s="1">
+      <c r="K26" s="1">
         <v>25176</v>
       </c>
-      <c r="J26" s="1">
+      <c r="L26" s="1">
         <v>293.64999999999998</v>
       </c>
-      <c r="K26" s="1">
+      <c r="M26" s="1">
         <v>296.93</v>
       </c>
-      <c r="L26" s="1">
+      <c r="N26" s="1">
         <v>296.52999999999997</v>
       </c>
-      <c r="M26" s="1">
+      <c r="O26" s="1">
         <v>296.01</v>
       </c>
-      <c r="N26" s="1">
+      <c r="P26" s="1">
         <v>289.45</v>
       </c>
-      <c r="O26" s="1">
+      <c r="Q26" s="1">
         <v>23492</v>
       </c>
-      <c r="P26" s="1">
+      <c r="R26" s="1">
         <v>-1684</v>
       </c>
-      <c r="Q26">
+      <c r="S26">
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>258</v>
       </c>
       <c r="B27" t="s">
-        <v>318</v>
-      </c>
-      <c r="C27" t="s">
+        <v>320</v>
+      </c>
+      <c r="E27" t="s">
         <v>294</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>55</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>898.15</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>808.34</v>
       </c>
-      <c r="G27" s="1">
+      <c r="I27" s="1">
         <v>70.41</v>
       </c>
-      <c r="H27" s="2">
+      <c r="J27" s="2">
         <v>8.0125177809388298E-2</v>
       </c>
-      <c r="I27" s="1">
+      <c r="K27" s="1">
         <v>49398.25</v>
       </c>
-      <c r="J27" s="1">
+      <c r="L27" s="1">
         <v>878.75</v>
       </c>
-      <c r="K27" s="1">
+      <c r="M27" s="1">
         <v>880.79</v>
       </c>
-      <c r="L27" s="1">
+      <c r="N27" s="1">
         <v>879.35</v>
       </c>
-      <c r="M27" s="1">
+      <c r="O27" s="1">
         <v>877.62</v>
       </c>
-      <c r="N27" s="1">
+      <c r="P27" s="1">
         <v>852.29</v>
       </c>
-      <c r="O27" s="1">
+      <c r="Q27" s="1">
         <v>48331.25</v>
       </c>
-      <c r="P27" s="1">
+      <c r="R27" s="1">
         <v>-1067</v>
       </c>
-      <c r="Q27">
+      <c r="S27">
         <v>24</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>47</v>
       </c>
       <c r="B28" t="s">
-        <v>316</v>
-      </c>
-      <c r="C28" t="s">
+        <v>318</v>
+      </c>
+      <c r="E28" t="s">
         <v>293</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>37</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>1289.2</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>1160.28</v>
       </c>
-      <c r="G28" s="1">
+      <c r="I28" s="1">
         <v>-38.979999999999997</v>
       </c>
-      <c r="H28" s="2">
+      <c r="J28" s="2">
         <v>-3.4763221261036308E-2</v>
       </c>
-      <c r="I28" s="1">
+      <c r="K28" s="1">
         <v>47700.4</v>
       </c>
-      <c r="J28" s="1">
+      <c r="L28" s="1">
         <v>1121.3</v>
       </c>
-      <c r="K28" s="1">
+      <c r="M28" s="1">
         <v>1157.48</v>
       </c>
-      <c r="L28" s="1">
+      <c r="N28" s="1">
         <v>1160.73</v>
       </c>
-      <c r="M28" s="1">
+      <c r="O28" s="1">
         <v>1163.58</v>
       </c>
-      <c r="N28" s="1">
+      <c r="P28" s="1">
         <v>1180.18</v>
       </c>
-      <c r="O28" s="1">
+      <c r="Q28" s="1">
         <v>41488.1</v>
       </c>
-      <c r="P28" s="1">
+      <c r="R28" s="1">
         <v>-6212.3</v>
       </c>
-      <c r="Q28">
+      <c r="S28">
         <v>180</v>
       </c>
     </row>
@@ -18189,30 +18167,31 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:R51"/>
+  <dimension ref="A1:T51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -18223,205 +18202,205 @@
         <v>301</v>
       </c>
       <c r="D1" t="s">
-        <v>319</v>
+        <v>302</v>
       </c>
       <c r="E1" t="s">
-        <v>320</v>
+        <v>303</v>
       </c>
       <c r="F1" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="G1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
       <c r="I1" t="s">
         <v>323</v>
       </c>
       <c r="J1" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
       <c r="K1" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="L1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="M1" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="N1" t="s">
-        <v>324</v>
+        <v>310</v>
       </c>
       <c r="O1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="P1" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q1" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="R1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+        <v>327</v>
+      </c>
+      <c r="S1" t="s">
+        <v>328</v>
+      </c>
+      <c r="T1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>201</v>
       </c>
       <c r="B2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E2" t="s">
         <v>293</v>
       </c>
-      <c r="D2">
+      <c r="F2">
         <v>4</v>
       </c>
-      <c r="E2" s="1">
+      <c r="G2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="F2" s="1">
+      <c r="H2" s="1">
         <v>2936.3</v>
       </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0</v>
-      </c>
-      <c r="J2">
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>0</v>
+      </c>
+      <c r="L2">
         <v>4</v>
       </c>
-      <c r="K2" s="1">
+      <c r="M2" s="1">
         <v>11745.2</v>
       </c>
-      <c r="L2" s="1">
+      <c r="N2" s="1">
         <v>2992</v>
       </c>
-      <c r="M2" s="1">
+      <c r="O2" s="1">
         <v>11968</v>
       </c>
-      <c r="N2" s="1">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1">
+      <c r="P2" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="1">
         <v>222.8</v>
       </c>
-      <c r="P2" s="1">
+      <c r="R2" s="1">
         <v>222.8</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="S2" s="2">
         <v>1.896945135033886E-2</v>
       </c>
-      <c r="R2">
+      <c r="T2">
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>254</v>
       </c>
       <c r="B3" t="s">
-        <v>316</v>
-      </c>
-      <c r="C3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" t="s">
         <v>292</v>
       </c>
-      <c r="D3">
+      <c r="F3">
         <v>45</v>
       </c>
-      <c r="E3" s="1">
+      <c r="G3" s="1">
         <v>100692.0045</v>
       </c>
-      <c r="F3" s="1">
+      <c r="H3" s="1">
         <v>2237.6</v>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="1">
-        <v>0</v>
-      </c>
-      <c r="I3" s="1">
-        <v>0</v>
-      </c>
-      <c r="J3">
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <v>0</v>
+      </c>
+      <c r="L3">
         <v>45</v>
       </c>
-      <c r="K3" s="1">
+      <c r="M3" s="1">
         <v>100692</v>
       </c>
-      <c r="L3" s="1">
+      <c r="N3" s="1">
         <v>2152.8000000000002</v>
       </c>
-      <c r="M3" s="1">
+      <c r="O3" s="1">
         <v>96876</v>
       </c>
-      <c r="N3" s="1">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1">
+      <c r="P3" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="1">
         <v>-3816</v>
       </c>
-      <c r="P3" s="1">
+      <c r="R3" s="1">
         <v>-3816</v>
       </c>
-      <c r="Q3" s="2">
+      <c r="S3" s="2">
         <v>-3.7897745893021723E-2</v>
       </c>
-      <c r="R3">
+      <c r="T3">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
       <c r="B4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C4" t="s">
+        <v>320</v>
+      </c>
+      <c r="E4" t="s">
         <v>298</v>
       </c>
-      <c r="D4">
+      <c r="F4">
         <v>671</v>
       </c>
-      <c r="E4" s="1">
+      <c r="G4" s="1">
         <v>129693.78</v>
       </c>
-      <c r="F4" s="1">
+      <c r="H4" s="1">
         <v>193.28</v>
       </c>
-      <c r="G4">
+      <c r="I4">
         <v>671</v>
       </c>
-      <c r="H4" s="1">
+      <c r="J4" s="1">
         <v>120337.14</v>
       </c>
-      <c r="I4" s="1">
+      <c r="K4" s="1">
         <v>179.34</v>
       </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>0</v>
-      </c>
-      <c r="L4" s="1">
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="1">
+        <v>0</v>
+      </c>
+      <c r="N4" s="1">
         <v>145.11000000000001</v>
-      </c>
-      <c r="M4" s="1">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1">
-        <v>-9353.74</v>
       </c>
       <c r="O4" s="1">
         <v>0</v>
@@ -18429,55 +18408,55 @@
       <c r="P4" s="1">
         <v>-9353.74</v>
       </c>
-      <c r="Q4" s="2">
+      <c r="Q4" s="1">
+        <v>0</v>
+      </c>
+      <c r="R4" s="1">
+        <v>-9353.74</v>
+      </c>
+      <c r="S4" s="2">
         <v>-7.2121731666699815E-2</v>
       </c>
-      <c r="R4">
+      <c r="T4">
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>98</v>
       </c>
       <c r="B5" t="s">
-        <v>317</v>
-      </c>
-      <c r="C5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" t="s">
         <v>292</v>
       </c>
-      <c r="D5">
+      <c r="F5">
         <v>94</v>
       </c>
-      <c r="E5" s="1">
+      <c r="G5" s="1">
         <v>100072.4</v>
       </c>
-      <c r="F5" s="1">
+      <c r="H5" s="1">
         <v>1064.5999999999999</v>
       </c>
-      <c r="G5">
+      <c r="I5">
         <v>94</v>
       </c>
-      <c r="H5" s="1">
+      <c r="J5" s="1">
         <v>84426.099999999991</v>
       </c>
-      <c r="I5" s="1">
+      <c r="K5" s="1">
         <v>898.15</v>
       </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
         <v>950.2</v>
-      </c>
-      <c r="M5" s="1">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1">
-        <v>-15646.3</v>
       </c>
       <c r="O5" s="1">
         <v>0</v>
@@ -18485,223 +18464,223 @@
       <c r="P5" s="1">
         <v>-15646.3</v>
       </c>
-      <c r="Q5" s="2">
+      <c r="Q5" s="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1">
+        <v>-15646.3</v>
+      </c>
+      <c r="S5" s="2">
         <v>-0.15634980274281421</v>
       </c>
-      <c r="R5">
+      <c r="T5">
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>139</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C6" t="s">
+        <v>319</v>
+      </c>
+      <c r="E6" t="s">
         <v>292</v>
       </c>
-      <c r="D6">
+      <c r="F6">
         <v>260</v>
       </c>
-      <c r="E6" s="1">
+      <c r="G6" s="1">
         <v>75946</v>
       </c>
-      <c r="F6" s="1">
+      <c r="H6" s="1">
         <v>292.10000000000002</v>
       </c>
-      <c r="G6">
+      <c r="I6">
         <v>170</v>
       </c>
-      <c r="H6" s="1">
+      <c r="J6" s="1">
         <v>46165.05</v>
       </c>
-      <c r="I6" s="1">
+      <c r="K6" s="1">
         <v>271.56</v>
       </c>
-      <c r="J6">
+      <c r="L6">
         <v>90</v>
       </c>
-      <c r="K6" s="1">
+      <c r="M6" s="1">
         <v>26289</v>
       </c>
-      <c r="L6" s="1">
+      <c r="N6" s="1">
         <v>295.35000000000002</v>
       </c>
-      <c r="M6" s="1">
+      <c r="O6" s="1">
         <v>26581.5</v>
       </c>
-      <c r="N6" s="1">
+      <c r="P6" s="1">
         <v>-3491.95</v>
       </c>
-      <c r="O6" s="1">
+      <c r="Q6" s="1">
         <v>292.5</v>
       </c>
-      <c r="P6" s="1">
+      <c r="R6" s="1">
         <v>-3199.45</v>
       </c>
-      <c r="Q6" s="2">
+      <c r="S6" s="2">
         <v>-4.2127959339530723E-2</v>
       </c>
-      <c r="R6">
+      <c r="T6">
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>217</v>
       </c>
       <c r="B7" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E7" t="s">
         <v>294</v>
       </c>
-      <c r="D7">
+      <c r="F7">
         <v>465</v>
       </c>
-      <c r="E7" s="1">
+      <c r="G7" s="1">
         <v>75179.430000000008</v>
       </c>
-      <c r="F7" s="1">
+      <c r="H7" s="1">
         <v>161.68</v>
       </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="1">
-        <v>0</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="L7">
         <v>465</v>
       </c>
-      <c r="K7" s="1">
+      <c r="M7" s="1">
         <v>75181.2</v>
       </c>
-      <c r="L7" s="1">
+      <c r="N7" s="1">
         <v>159.58000000000001</v>
       </c>
-      <c r="M7" s="1">
+      <c r="O7" s="1">
         <v>74204.7</v>
       </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
         <v>-976.5</v>
       </c>
-      <c r="P7" s="1">
+      <c r="R7" s="1">
         <v>-976.5</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>-1.2988925295123939E-2</v>
       </c>
-      <c r="R7">
+      <c r="T7">
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>317</v>
-      </c>
-      <c r="C8" t="s">
+        <v>319</v>
+      </c>
+      <c r="E8" t="s">
         <v>292</v>
       </c>
-      <c r="D8">
+      <c r="F8">
         <v>222</v>
       </c>
-      <c r="E8" s="1">
+      <c r="G8" s="1">
         <v>100778.25</v>
       </c>
-      <c r="F8" s="1">
+      <c r="H8" s="1">
         <v>453.96</v>
       </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8" s="1">
-        <v>0</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8">
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="L8">
         <v>222</v>
       </c>
-      <c r="K8" s="1">
+      <c r="M8" s="1">
         <v>100779.12</v>
       </c>
-      <c r="L8" s="1">
+      <c r="N8" s="1">
         <v>468.45</v>
       </c>
-      <c r="M8" s="1">
+      <c r="O8" s="1">
         <v>103995.9</v>
       </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
         <v>3216.78</v>
       </c>
-      <c r="P8" s="1">
+      <c r="R8" s="1">
         <v>3216.78</v>
       </c>
-      <c r="Q8" s="2">
+      <c r="S8" s="2">
         <v>3.1919387367810019E-2</v>
       </c>
-      <c r="R8">
+      <c r="T8">
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>154</v>
       </c>
       <c r="B9" t="s">
-        <v>316</v>
-      </c>
-      <c r="C9" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" t="s">
         <v>293</v>
       </c>
-      <c r="D9">
+      <c r="F9">
         <v>36</v>
       </c>
-      <c r="E9" s="1">
+      <c r="G9" s="1">
         <v>50176.800000000003</v>
       </c>
-      <c r="F9" s="1">
+      <c r="H9" s="1">
         <v>1393.8</v>
       </c>
-      <c r="G9">
+      <c r="I9">
         <v>36</v>
       </c>
-      <c r="H9" s="1">
+      <c r="J9" s="1">
         <v>50997.599999999999</v>
       </c>
-      <c r="I9" s="1">
+      <c r="K9" s="1">
         <v>1416.6</v>
       </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
         <v>1923.9</v>
-      </c>
-      <c r="M9" s="1">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1">
-        <v>820.8</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18709,167 +18688,167 @@
       <c r="P9" s="1">
         <v>820.8</v>
       </c>
-      <c r="Q9" s="2">
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>820.8</v>
+      </c>
+      <c r="S9" s="2">
         <v>1.635815755488592E-2</v>
       </c>
-      <c r="R9">
+      <c r="T9">
         <v>77</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>130</v>
       </c>
       <c r="B10" t="s">
-        <v>317</v>
-      </c>
-      <c r="C10" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" t="s">
         <v>293</v>
       </c>
-      <c r="D10">
+      <c r="F10">
         <v>82</v>
       </c>
-      <c r="E10" s="1">
+      <c r="G10" s="1">
         <v>30151.4</v>
       </c>
-      <c r="F10" s="1">
+      <c r="H10" s="1">
         <v>367.7</v>
       </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>0</v>
+      </c>
+      <c r="L10">
         <v>82</v>
       </c>
-      <c r="K10" s="1">
+      <c r="M10" s="1">
         <v>30151.4</v>
       </c>
-      <c r="L10" s="1">
+      <c r="N10" s="1">
         <v>352.75</v>
       </c>
-      <c r="M10" s="1">
+      <c r="O10" s="1">
         <v>28925.5</v>
       </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
         <v>-1225.9000000000001</v>
       </c>
-      <c r="P10" s="1">
+      <c r="R10" s="1">
         <v>-1225.9000000000001</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="S10" s="2">
         <v>-4.0658145227087307E-2</v>
       </c>
-      <c r="R10">
+      <c r="T10">
         <v>125</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>317</v>
-      </c>
-      <c r="C11" t="s">
+        <v>319</v>
+      </c>
+      <c r="E11" t="s">
         <v>293</v>
       </c>
-      <c r="D11">
-        <v>18</v>
-      </c>
-      <c r="E11" s="1">
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11" s="1">
         <v>50428.801800000001</v>
       </c>
-      <c r="F11" s="1">
+      <c r="H11" s="1">
         <v>2801.6</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>18</v>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
       </c>
       <c r="K11" s="1">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>18</v>
+      </c>
+      <c r="M11" s="1">
         <v>50428.800000000003</v>
       </c>
-      <c r="L11" s="1">
+      <c r="N11" s="1">
         <v>2751.6</v>
       </c>
-      <c r="M11" s="1">
+      <c r="O11" s="1">
         <v>49528.800000000003</v>
       </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
         <v>-900</v>
       </c>
-      <c r="P11" s="1">
+      <c r="R11" s="1">
         <v>-900</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="S11" s="2">
         <v>-1.784694396605711E-2</v>
       </c>
-      <c r="R11">
+      <c r="T11">
         <v>90</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>168</v>
       </c>
       <c r="B12" t="s">
-        <v>318</v>
-      </c>
-      <c r="C12" t="s">
+        <v>320</v>
+      </c>
+      <c r="E12" t="s">
         <v>294</v>
       </c>
-      <c r="D12">
+      <c r="F12">
         <v>228</v>
       </c>
-      <c r="E12" s="1">
+      <c r="G12" s="1">
         <v>99912.15</v>
       </c>
-      <c r="F12" s="1">
+      <c r="H12" s="1">
         <v>438.21</v>
       </c>
-      <c r="G12">
+      <c r="I12">
         <v>228</v>
       </c>
-      <c r="H12" s="1">
+      <c r="J12" s="1">
         <v>90155.400000000009</v>
       </c>
-      <c r="I12" s="1">
+      <c r="K12" s="1">
         <v>395.42</v>
       </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
         <v>371.2</v>
-      </c>
-      <c r="M12" s="1">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1">
-        <v>-9756.48</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18877,223 +18856,223 @@
       <c r="P12" s="1">
         <v>-9756.48</v>
       </c>
-      <c r="Q12" s="2">
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>-9756.48</v>
+      </c>
+      <c r="S12" s="2">
         <v>-9.7650586039835993E-2</v>
       </c>
-      <c r="R12">
+      <c r="T12">
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>317</v>
-      </c>
-      <c r="C13" t="s">
+        <v>319</v>
+      </c>
+      <c r="E13" t="s">
         <v>297</v>
       </c>
-      <c r="D13">
+      <c r="F13">
         <v>2062</v>
       </c>
-      <c r="E13" s="1">
+      <c r="G13" s="1">
         <v>269285.90000000002</v>
       </c>
-      <c r="F13" s="1">
+      <c r="H13" s="1">
         <v>130.59</v>
       </c>
-      <c r="G13">
+      <c r="I13">
         <v>2078</v>
       </c>
-      <c r="H13" s="1">
+      <c r="J13" s="1">
         <v>267524.40000000002</v>
       </c>
-      <c r="I13" s="1">
+      <c r="K13" s="1">
         <v>128.74</v>
       </c>
-      <c r="J13">
+      <c r="L13">
         <v>-16</v>
       </c>
-      <c r="K13" s="1">
+      <c r="M13" s="1">
         <v>-2089.44</v>
       </c>
-      <c r="L13" s="1">
+      <c r="N13" s="1">
         <v>145.97</v>
       </c>
-      <c r="M13" s="1">
+      <c r="O13" s="1">
         <v>-2335.52</v>
       </c>
-      <c r="N13" s="1">
+      <c r="P13" s="1">
         <v>-3841.62</v>
       </c>
-      <c r="O13" s="1">
+      <c r="Q13" s="1">
         <v>-246.08</v>
       </c>
-      <c r="P13" s="1">
+      <c r="R13" s="1">
         <v>-4087.7</v>
       </c>
-      <c r="Q13" s="2">
+      <c r="S13" s="2">
         <v>-1.5179777329596531E-2</v>
       </c>
-      <c r="R13">
+      <c r="T13">
         <v>167</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>53</v>
       </c>
       <c r="B14" t="s">
-        <v>317</v>
-      </c>
-      <c r="C14" t="s">
+        <v>319</v>
+      </c>
+      <c r="E14" t="s">
         <v>296</v>
       </c>
-      <c r="D14">
+      <c r="F14">
         <v>70</v>
       </c>
-      <c r="E14" s="1">
+      <c r="G14" s="1">
         <v>52058.85</v>
       </c>
-      <c r="F14" s="1">
+      <c r="H14" s="1">
         <v>743.7</v>
       </c>
-      <c r="G14">
+      <c r="I14">
         <v>33</v>
       </c>
-      <c r="H14" s="1">
+      <c r="J14" s="1">
         <v>25000.799999999999</v>
       </c>
-      <c r="I14" s="1">
+      <c r="K14" s="1">
         <v>757.6</v>
       </c>
-      <c r="J14">
+      <c r="L14">
         <v>37</v>
       </c>
-      <c r="K14" s="1">
+      <c r="M14" s="1">
         <v>27516.9</v>
       </c>
-      <c r="L14" s="1">
+      <c r="N14" s="1">
         <v>715.45</v>
       </c>
-      <c r="M14" s="1">
+      <c r="O14" s="1">
         <v>26471.65</v>
       </c>
-      <c r="N14" s="1">
+      <c r="P14" s="1">
         <v>458.7</v>
       </c>
-      <c r="O14" s="1">
+      <c r="Q14" s="1">
         <v>-1045.25</v>
       </c>
-      <c r="P14" s="1">
+      <c r="R14" s="1">
         <v>-586.54999999999995</v>
       </c>
-      <c r="Q14" s="2">
+      <c r="S14" s="2">
         <v>-1.126705641788092E-2</v>
       </c>
-      <c r="R14">
+      <c r="T14">
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>127</v>
       </c>
       <c r="B15" t="s">
-        <v>318</v>
-      </c>
-      <c r="C15" t="s">
+        <v>320</v>
+      </c>
+      <c r="E15" t="s">
         <v>293</v>
       </c>
-      <c r="D15">
+      <c r="F15">
         <v>42</v>
       </c>
-      <c r="E15" s="1">
+      <c r="G15" s="1">
         <v>40147.050000000003</v>
       </c>
-      <c r="F15" s="1">
+      <c r="H15" s="1">
         <v>955.88</v>
       </c>
-      <c r="G15">
+      <c r="I15">
         <v>52</v>
       </c>
-      <c r="H15" s="1">
+      <c r="J15" s="1">
         <v>42377.3</v>
       </c>
-      <c r="I15" s="1">
+      <c r="K15" s="1">
         <v>814.95</v>
       </c>
-      <c r="J15">
+      <c r="L15">
         <v>-10</v>
       </c>
-      <c r="K15" s="1">
+      <c r="M15" s="1">
         <v>-9558.7999999999993</v>
       </c>
-      <c r="L15" s="1">
+      <c r="N15" s="1">
         <v>1007.5</v>
       </c>
-      <c r="M15" s="1">
+      <c r="O15" s="1">
         <v>-10075</v>
       </c>
-      <c r="N15" s="1">
+      <c r="P15" s="1">
         <v>-7328.46</v>
       </c>
-      <c r="O15" s="1">
+      <c r="Q15" s="1">
         <v>-516.20000000000005</v>
       </c>
-      <c r="P15" s="1">
+      <c r="R15" s="1">
         <v>-7844.66</v>
       </c>
-      <c r="Q15" s="2">
+      <c r="S15" s="2">
         <v>-0.19539816748677671</v>
       </c>
-      <c r="R15">
+      <c r="T15">
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
-      </c>
-      <c r="C16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E16" t="s">
         <v>292</v>
       </c>
-      <c r="D16">
+      <c r="F16">
         <v>64</v>
       </c>
-      <c r="E16" s="1">
+      <c r="G16" s="1">
         <v>99129.600000000006</v>
       </c>
-      <c r="F16" s="1">
+      <c r="H16" s="1">
         <v>1548.9</v>
       </c>
-      <c r="G16">
+      <c r="I16">
         <v>64</v>
       </c>
-      <c r="H16" s="1">
+      <c r="J16" s="1">
         <v>83161.600000000006</v>
       </c>
-      <c r="I16" s="1">
+      <c r="K16" s="1">
         <v>1299.4000000000001</v>
       </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
         <v>1321.2</v>
-      </c>
-      <c r="M16" s="1">
-        <v>0</v>
-      </c>
-      <c r="N16" s="1">
-        <v>-15968</v>
       </c>
       <c r="O16" s="1">
         <v>0</v>
@@ -19101,111 +19080,111 @@
       <c r="P16" s="1">
         <v>-15968</v>
       </c>
-      <c r="Q16" s="2">
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>-15968</v>
+      </c>
+      <c r="S16" s="2">
         <v>-0.16108205823487631</v>
       </c>
-      <c r="R16">
+      <c r="T16">
         <v>147</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>193</v>
       </c>
       <c r="B17" t="s">
-        <v>316</v>
-      </c>
-      <c r="C17" t="s">
+        <v>318</v>
+      </c>
+      <c r="E17" t="s">
         <v>296</v>
       </c>
-      <c r="D17">
+      <c r="F17">
         <v>338</v>
       </c>
-      <c r="E17" s="1">
+      <c r="G17" s="1">
         <v>143246</v>
       </c>
-      <c r="F17" s="1">
+      <c r="H17" s="1">
         <v>423.8</v>
       </c>
-      <c r="G17">
+      <c r="I17">
         <v>133</v>
       </c>
-      <c r="H17" s="1">
+      <c r="J17" s="1">
         <v>48531.7</v>
       </c>
-      <c r="I17" s="1">
+      <c r="K17" s="1">
         <v>364.9</v>
       </c>
-      <c r="J17">
+      <c r="L17">
         <v>205</v>
       </c>
-      <c r="K17" s="1">
+      <c r="M17" s="1">
         <v>86879</v>
       </c>
-      <c r="L17" s="1">
+      <c r="N17" s="1">
         <v>80.44</v>
       </c>
-      <c r="M17" s="1">
+      <c r="O17" s="1">
         <v>16490.2</v>
       </c>
-      <c r="N17" s="1">
+      <c r="P17" s="1">
         <v>-7833.7</v>
       </c>
-      <c r="O17" s="1">
+      <c r="Q17" s="1">
         <v>-70388.800000000003</v>
       </c>
-      <c r="P17" s="1">
+      <c r="R17" s="1">
         <v>-78222.5</v>
       </c>
-      <c r="Q17" s="2">
+      <c r="S17" s="2">
         <v>-0.54607109448082325</v>
       </c>
-      <c r="R17">
+      <c r="T17">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>317</v>
-      </c>
-      <c r="C18" t="s">
+        <v>319</v>
+      </c>
+      <c r="E18" t="s">
         <v>292</v>
       </c>
-      <c r="D18">
-        <v>19</v>
-      </c>
-      <c r="E18" s="1">
+      <c r="F18">
+        <v>19</v>
+      </c>
+      <c r="G18" s="1">
         <v>89756.600600000005</v>
       </c>
-      <c r="F18" s="1">
+      <c r="H18" s="1">
         <v>4724.03</v>
       </c>
-      <c r="G18">
-        <v>19</v>
-      </c>
-      <c r="H18" s="1">
+      <c r="I18">
+        <v>19</v>
+      </c>
+      <c r="J18" s="1">
         <v>77079.199999999997</v>
       </c>
-      <c r="I18" s="1">
+      <c r="K18" s="1">
         <v>4056.8</v>
       </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <v>0</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
         <v>3875.8</v>
-      </c>
-      <c r="M18" s="1">
-        <v>0</v>
-      </c>
-      <c r="N18" s="1">
-        <v>-12677.37</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -19213,55 +19192,55 @@
       <c r="P18" s="1">
         <v>-12677.37</v>
       </c>
-      <c r="Q18" s="2">
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>-12677.37</v>
+      </c>
+      <c r="S18" s="2">
         <v>-0.14124164590966029</v>
       </c>
-      <c r="R18">
+      <c r="T18">
         <v>64</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>108</v>
       </c>
       <c r="B19" t="s">
-        <v>317</v>
-      </c>
-      <c r="C19" t="s">
+        <v>319</v>
+      </c>
+      <c r="E19" t="s">
         <v>293</v>
       </c>
-      <c r="D19">
+      <c r="F19">
         <v>75</v>
       </c>
-      <c r="E19" s="1">
+      <c r="G19" s="1">
         <v>25440</v>
       </c>
-      <c r="F19" s="1">
+      <c r="H19" s="1">
         <v>339.2</v>
       </c>
-      <c r="G19">
+      <c r="I19">
         <v>75</v>
       </c>
-      <c r="H19" s="1">
+      <c r="J19" s="1">
         <v>22856.25</v>
       </c>
-      <c r="I19" s="1">
+      <c r="K19" s="1">
         <v>304.75</v>
       </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
         <v>232.57</v>
-      </c>
-      <c r="M19" s="1">
-        <v>0</v>
-      </c>
-      <c r="N19" s="1">
-        <v>-2583.75</v>
       </c>
       <c r="O19" s="1">
         <v>0</v>
@@ -19269,223 +19248,223 @@
       <c r="P19" s="1">
         <v>-2583.75</v>
       </c>
-      <c r="Q19" s="2">
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>-2583.75</v>
+      </c>
+      <c r="S19" s="2">
         <v>-0.1015625</v>
       </c>
-      <c r="R19">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T19">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>142</v>
       </c>
       <c r="B20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C20" t="s">
+        <v>318</v>
+      </c>
+      <c r="E20" t="s">
         <v>299</v>
       </c>
-      <c r="D20">
+      <c r="F20">
         <v>1172</v>
       </c>
-      <c r="E20" s="1">
+      <c r="G20" s="1">
         <v>300285.28000000003</v>
       </c>
-      <c r="F20" s="1">
+      <c r="H20" s="1">
         <v>256.22000000000003</v>
       </c>
-      <c r="G20">
-        <v>0</v>
-      </c>
-      <c r="H20" s="1">
-        <v>0</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <v>0</v>
+      </c>
+      <c r="L20">
         <v>1172</v>
       </c>
-      <c r="K20" s="1">
+      <c r="M20" s="1">
         <v>300289.84000000003</v>
       </c>
-      <c r="L20" s="1">
+      <c r="N20" s="1">
         <v>286.5</v>
       </c>
-      <c r="M20" s="1">
+      <c r="O20" s="1">
         <v>335778</v>
       </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="1">
         <v>35488.160000000003</v>
       </c>
-      <c r="P20" s="1">
+      <c r="R20" s="1">
         <v>35488.160000000003</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="S20" s="2">
         <v>0.1181814839541918</v>
       </c>
-      <c r="R20">
+      <c r="T20">
         <v>125</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>190</v>
       </c>
       <c r="B21" t="s">
-        <v>318</v>
-      </c>
-      <c r="C21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E21" t="s">
         <v>294</v>
       </c>
-      <c r="D21">
+      <c r="F21">
         <v>362</v>
       </c>
-      <c r="E21" s="1">
+      <c r="G21" s="1">
         <v>50229.29</v>
       </c>
-      <c r="F21" s="1">
+      <c r="H21" s="1">
         <v>138.75</v>
       </c>
-      <c r="G21">
-        <v>0</v>
-      </c>
-      <c r="H21" s="1">
-        <v>0</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21">
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1">
+        <v>0</v>
+      </c>
+      <c r="L21">
         <v>362</v>
       </c>
-      <c r="K21" s="1">
+      <c r="M21" s="1">
         <v>50227.5</v>
       </c>
-      <c r="L21" s="1">
+      <c r="N21" s="1">
         <v>135.75</v>
       </c>
-      <c r="M21" s="1">
+      <c r="O21" s="1">
         <v>49141.5</v>
       </c>
-      <c r="N21" s="1">
-        <v>0</v>
-      </c>
-      <c r="O21" s="1">
+      <c r="P21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="1">
         <v>-1086</v>
       </c>
-      <c r="P21" s="1">
+      <c r="R21" s="1">
         <v>-1086</v>
       </c>
-      <c r="Q21" s="2">
+      <c r="S21" s="2">
         <v>-2.1620851101020942E-2</v>
       </c>
-      <c r="R21">
+      <c r="T21">
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>318</v>
-      </c>
-      <c r="C22" t="s">
+        <v>320</v>
+      </c>
+      <c r="E22" t="s">
         <v>296</v>
       </c>
-      <c r="D22">
+      <c r="F22">
         <v>339</v>
       </c>
-      <c r="E22" s="1">
+      <c r="G22" s="1">
         <v>199971.65</v>
       </c>
-      <c r="F22" s="1">
+      <c r="H22" s="1">
         <v>589.89</v>
       </c>
-      <c r="G22">
+      <c r="I22">
         <v>298</v>
       </c>
-      <c r="H22" s="1">
+      <c r="J22" s="1">
         <v>175804.15</v>
       </c>
-      <c r="I22" s="1">
+      <c r="K22" s="1">
         <v>589.95000000000005</v>
       </c>
-      <c r="J22">
+      <c r="L22">
         <v>41</v>
       </c>
-      <c r="K22" s="1">
+      <c r="M22" s="1">
         <v>24185.49</v>
       </c>
-      <c r="L22" s="1">
+      <c r="N22" s="1">
         <v>546.85</v>
       </c>
-      <c r="M22" s="1">
+      <c r="O22" s="1">
         <v>22420.85</v>
       </c>
-      <c r="N22" s="1">
+      <c r="P22" s="1">
         <v>16.93</v>
       </c>
-      <c r="O22" s="1">
+      <c r="Q22" s="1">
         <v>-1764.64</v>
       </c>
-      <c r="P22" s="1">
+      <c r="R22" s="1">
         <v>-1747.71</v>
       </c>
-      <c r="Q22" s="2">
+      <c r="S22" s="2">
         <v>-8.7397888650716238E-3</v>
       </c>
-      <c r="R22">
+      <c r="T22">
         <v>180</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>165</v>
       </c>
       <c r="B23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C23" t="s">
+        <v>318</v>
+      </c>
+      <c r="E23" t="s">
         <v>292</v>
       </c>
-      <c r="D23">
+      <c r="F23">
         <v>920</v>
       </c>
-      <c r="E23" s="1">
+      <c r="G23" s="1">
         <v>99801.600000000006</v>
       </c>
-      <c r="F23" s="1">
+      <c r="H23" s="1">
         <v>108.48</v>
       </c>
-      <c r="G23">
+      <c r="I23">
         <v>920</v>
       </c>
-      <c r="H23" s="1">
+      <c r="J23" s="1">
         <v>82570</v>
       </c>
-      <c r="I23" s="1">
+      <c r="K23" s="1">
         <v>89.75</v>
       </c>
-      <c r="J23">
-        <v>0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>0</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
         <v>95.06</v>
-      </c>
-      <c r="M23" s="1">
-        <v>0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>-17231.599999999999</v>
       </c>
       <c r="O23" s="1">
         <v>0</v>
@@ -19493,335 +19472,335 @@
       <c r="P23" s="1">
         <v>-17231.599999999999</v>
       </c>
-      <c r="Q23" s="2">
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>-17231.599999999999</v>
+      </c>
+      <c r="S23" s="2">
         <v>-0.17265855457227139</v>
       </c>
-      <c r="R23">
+      <c r="T23">
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>118</v>
       </c>
       <c r="B24" t="s">
-        <v>318</v>
-      </c>
-      <c r="C24" t="s">
+        <v>320</v>
+      </c>
+      <c r="E24" t="s">
         <v>294</v>
       </c>
-      <c r="D24">
+      <c r="F24">
         <v>276</v>
       </c>
-      <c r="E24" s="1">
+      <c r="G24" s="1">
         <v>76932.53</v>
       </c>
-      <c r="F24" s="1">
+      <c r="H24" s="1">
         <v>278.74</v>
       </c>
-      <c r="G24">
-        <v>0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24">
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24" s="1">
+        <v>0</v>
+      </c>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24">
         <v>276</v>
       </c>
-      <c r="K24" s="1">
+      <c r="M24" s="1">
         <v>76932.240000000005</v>
       </c>
-      <c r="L24" s="1">
+      <c r="N24" s="1">
         <v>247.35</v>
       </c>
-      <c r="M24" s="1">
+      <c r="O24" s="1">
         <v>68268.600000000006</v>
       </c>
-      <c r="N24" s="1">
-        <v>0</v>
-      </c>
-      <c r="O24" s="1">
+      <c r="P24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="1">
         <v>-8663.64</v>
       </c>
-      <c r="P24" s="1">
+      <c r="R24" s="1">
         <v>-8663.64</v>
       </c>
-      <c r="Q24" s="2">
+      <c r="S24" s="2">
         <v>-0.1126134809293286</v>
       </c>
-      <c r="R24">
+      <c r="T24">
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>318</v>
-      </c>
-      <c r="C25" t="s">
+        <v>320</v>
+      </c>
+      <c r="E25" t="s">
         <v>297</v>
       </c>
-      <c r="D25">
+      <c r="F25">
         <v>226</v>
       </c>
-      <c r="E25" s="1">
+      <c r="G25" s="1">
         <v>198521.9</v>
       </c>
-      <c r="F25" s="1">
+      <c r="H25" s="1">
         <v>878.42</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25">
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25">
         <v>226</v>
       </c>
-      <c r="K25" s="1">
+      <c r="M25" s="1">
         <v>198522.92</v>
       </c>
-      <c r="L25" s="1">
+      <c r="N25" s="1">
         <v>676.9</v>
       </c>
-      <c r="M25" s="1">
+      <c r="O25" s="1">
         <v>152979.4</v>
       </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
+      <c r="P25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="1">
         <v>-45543.519999999997</v>
       </c>
-      <c r="P25" s="1">
+      <c r="R25" s="1">
         <v>-45543.519999999997</v>
       </c>
-      <c r="Q25" s="2">
+      <c r="S25" s="2">
         <v>-0.2294130773481414</v>
       </c>
-      <c r="R25">
+      <c r="T25">
         <v>181</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>88</v>
       </c>
       <c r="B26" t="s">
-        <v>317</v>
-      </c>
-      <c r="C26" t="s">
+        <v>319</v>
+      </c>
+      <c r="E26" t="s">
         <v>299</v>
       </c>
-      <c r="D26">
+      <c r="F26">
         <v>356</v>
       </c>
-      <c r="E26" s="1">
+      <c r="G26" s="1">
         <v>300219.3</v>
       </c>
-      <c r="F26" s="1">
+      <c r="H26" s="1">
         <v>843.31</v>
       </c>
-      <c r="G26">
+      <c r="I26">
         <v>103</v>
       </c>
-      <c r="H26" s="1">
+      <c r="J26" s="1">
         <v>99714.349999999991</v>
       </c>
-      <c r="I26" s="1">
+      <c r="K26" s="1">
         <v>968.1</v>
       </c>
-      <c r="J26">
+      <c r="L26">
         <v>253</v>
       </c>
-      <c r="K26" s="1">
+      <c r="M26" s="1">
         <v>213357.43</v>
       </c>
-      <c r="L26" s="1">
+      <c r="N26" s="1">
         <v>958.9</v>
       </c>
-      <c r="M26" s="1">
+      <c r="O26" s="1">
         <v>242601.7</v>
       </c>
-      <c r="N26" s="1">
+      <c r="P26" s="1">
         <v>12853.42</v>
       </c>
-      <c r="O26" s="1">
+      <c r="Q26" s="1">
         <v>29244.27</v>
       </c>
-      <c r="P26" s="1">
+      <c r="R26" s="1">
         <v>42097.69</v>
       </c>
-      <c r="Q26" s="2">
+      <c r="S26" s="2">
         <v>0.14022313022513869</v>
       </c>
-      <c r="R26">
+      <c r="T26">
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>123</v>
       </c>
       <c r="B27" t="s">
-        <v>316</v>
-      </c>
-      <c r="C27" t="s">
+        <v>318</v>
+      </c>
+      <c r="E27" t="s">
         <v>292</v>
       </c>
-      <c r="D27">
+      <c r="F27">
         <v>205</v>
       </c>
-      <c r="E27" s="1">
+      <c r="G27" s="1">
         <v>99086.75</v>
       </c>
-      <c r="F27" s="1">
+      <c r="H27" s="1">
         <v>483.35</v>
       </c>
-      <c r="G27">
-        <v>0</v>
-      </c>
-      <c r="H27" s="1">
-        <v>0</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27">
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>0</v>
+      </c>
+      <c r="L27">
         <v>205</v>
       </c>
-      <c r="K27" s="1">
+      <c r="M27" s="1">
         <v>99086.75</v>
       </c>
-      <c r="L27" s="1">
+      <c r="N27" s="1">
         <v>404.95</v>
       </c>
-      <c r="M27" s="1">
+      <c r="O27" s="1">
         <v>83014.75</v>
       </c>
-      <c r="N27" s="1">
-        <v>0</v>
-      </c>
-      <c r="O27" s="1">
+      <c r="P27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="1">
         <v>-16072</v>
       </c>
-      <c r="P27" s="1">
+      <c r="R27" s="1">
         <v>-16072</v>
       </c>
-      <c r="Q27" s="2">
+      <c r="S27" s="2">
         <v>-0.16220130340333089</v>
       </c>
-      <c r="R27">
+      <c r="T27">
         <v>125</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>133</v>
       </c>
       <c r="B28" t="s">
-        <v>317</v>
-      </c>
-      <c r="C28" t="s">
+        <v>319</v>
+      </c>
+      <c r="E28" t="s">
         <v>294</v>
       </c>
-      <c r="D28">
+      <c r="F28">
         <v>386</v>
       </c>
-      <c r="E28" s="1">
+      <c r="G28" s="1">
         <v>70186.3</v>
       </c>
-      <c r="F28" s="1">
+      <c r="H28" s="1">
         <v>181.83</v>
       </c>
-      <c r="G28">
-        <v>0</v>
-      </c>
-      <c r="H28" s="1">
-        <v>0</v>
-      </c>
-      <c r="I28" s="1">
-        <v>0</v>
-      </c>
-      <c r="J28">
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28" s="1">
+        <v>0</v>
+      </c>
+      <c r="K28" s="1">
+        <v>0</v>
+      </c>
+      <c r="L28">
         <v>386</v>
       </c>
-      <c r="K28" s="1">
+      <c r="M28" s="1">
         <v>70186.38</v>
       </c>
-      <c r="L28" s="1">
+      <c r="N28" s="1">
         <v>168.68</v>
       </c>
-      <c r="M28" s="1">
+      <c r="O28" s="1">
         <v>65110.48</v>
       </c>
-      <c r="N28" s="1">
-        <v>0</v>
-      </c>
-      <c r="O28" s="1">
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
         <v>-5075.8999999999996</v>
       </c>
-      <c r="P28" s="1">
+      <c r="R28" s="1">
         <v>-5075.8999999999996</v>
       </c>
-      <c r="Q28" s="2">
+      <c r="S28" s="2">
         <v>-7.2320381612935844E-2</v>
       </c>
-      <c r="R28">
+      <c r="T28">
         <v>125</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>318</v>
-      </c>
-      <c r="C29" t="s">
+        <v>320</v>
+      </c>
+      <c r="E29" t="s">
         <v>293</v>
       </c>
-      <c r="D29">
+      <c r="F29">
         <v>35</v>
       </c>
-      <c r="E29" s="1">
+      <c r="G29" s="1">
         <v>25089.75</v>
       </c>
-      <c r="F29" s="1">
+      <c r="H29" s="1">
         <v>716.85</v>
       </c>
-      <c r="G29">
+      <c r="I29">
         <v>35</v>
       </c>
-      <c r="H29" s="1">
+      <c r="J29" s="1">
         <v>22651.75</v>
       </c>
-      <c r="I29" s="1">
+      <c r="K29" s="1">
         <v>647.19000000000005</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" s="1">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
         <v>521.9</v>
-      </c>
-      <c r="M29" s="1">
-        <v>0</v>
-      </c>
-      <c r="N29" s="1">
-        <v>-2438</v>
       </c>
       <c r="O29" s="1">
         <v>0</v>
@@ -19829,55 +19808,55 @@
       <c r="P29" s="1">
         <v>-2438</v>
       </c>
-      <c r="Q29" s="2">
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>-2438</v>
+      </c>
+      <c r="S29" s="2">
         <v>-9.7171155551569868E-2</v>
       </c>
-      <c r="R29">
+      <c r="T29">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>318</v>
-      </c>
-      <c r="C30" t="s">
+        <v>320</v>
+      </c>
+      <c r="E30" t="s">
         <v>294</v>
       </c>
-      <c r="D30">
+      <c r="F30">
         <v>196</v>
       </c>
-      <c r="E30" s="1">
+      <c r="G30" s="1">
         <v>100079.5</v>
       </c>
-      <c r="F30" s="1">
+      <c r="H30" s="1">
         <v>510.61</v>
       </c>
-      <c r="G30">
+      <c r="I30">
         <v>196</v>
       </c>
-      <c r="H30" s="1">
+      <c r="J30" s="1">
         <v>82398.399999999994</v>
       </c>
-      <c r="I30" s="1">
+      <c r="K30" s="1">
         <v>420.4</v>
       </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
-      <c r="K30" s="1">
-        <v>0</v>
-      </c>
-      <c r="L30" s="1">
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30" s="1">
+        <v>0</v>
+      </c>
+      <c r="N30" s="1">
         <v>452.55</v>
-      </c>
-      <c r="M30" s="1">
-        <v>0</v>
-      </c>
-      <c r="N30" s="1">
-        <v>-17681.16</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -19885,55 +19864,55 @@
       <c r="P30" s="1">
         <v>-17681.16</v>
       </c>
-      <c r="Q30" s="2">
+      <c r="Q30" s="1">
+        <v>0</v>
+      </c>
+      <c r="R30" s="1">
+        <v>-17681.16</v>
+      </c>
+      <c r="S30" s="2">
         <v>-0.17667114643858131</v>
       </c>
-      <c r="R30">
+      <c r="T30">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>179</v>
       </c>
       <c r="B31" t="s">
-        <v>318</v>
-      </c>
-      <c r="C31" t="s">
+        <v>320</v>
+      </c>
+      <c r="E31" t="s">
         <v>293</v>
       </c>
-      <c r="D31">
-        <v>19</v>
-      </c>
-      <c r="E31" s="1">
+      <c r="F31">
+        <v>19</v>
+      </c>
+      <c r="G31" s="1">
         <v>24977.4</v>
       </c>
-      <c r="F31" s="1">
+      <c r="H31" s="1">
         <v>1314.6</v>
       </c>
-      <c r="G31">
-        <v>19</v>
-      </c>
-      <c r="H31" s="1">
+      <c r="I31">
+        <v>19</v>
+      </c>
+      <c r="J31" s="1">
         <v>21475.7</v>
       </c>
-      <c r="I31" s="1">
+      <c r="K31" s="1">
         <v>1130.3</v>
       </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31" s="1">
+        <v>0</v>
+      </c>
+      <c r="N31" s="1">
         <v>1510.5</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>-3501.7</v>
       </c>
       <c r="O31" s="1">
         <v>0</v>
@@ -19941,111 +19920,111 @@
       <c r="P31" s="1">
         <v>-3501.7</v>
       </c>
-      <c r="Q31" s="2">
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>-3501.7</v>
+      </c>
+      <c r="S31" s="2">
         <v>-0.14019473604138141</v>
       </c>
-      <c r="R31">
+      <c r="T31">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>220</v>
       </c>
       <c r="B32" t="s">
-        <v>316</v>
-      </c>
-      <c r="C32" t="s">
+        <v>318</v>
+      </c>
+      <c r="E32" t="s">
         <v>296</v>
       </c>
-      <c r="D32">
+      <c r="F32">
         <v>720</v>
       </c>
-      <c r="E32" s="1">
+      <c r="G32" s="1">
         <v>50899.69</v>
       </c>
-      <c r="F32" s="1">
+      <c r="H32" s="1">
         <v>70.69</v>
       </c>
-      <c r="G32">
-        <v>0</v>
-      </c>
-      <c r="H32" s="1">
-        <v>0</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32">
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32" s="1">
+        <v>0</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32">
         <v>720</v>
       </c>
-      <c r="K32" s="1">
+      <c r="M32" s="1">
         <v>50896.800000000003</v>
       </c>
-      <c r="L32" s="1">
+      <c r="N32" s="1">
         <v>70.13</v>
       </c>
-      <c r="M32" s="1">
+      <c r="O32" s="1">
         <v>50493.599999999999</v>
       </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="O32" s="1">
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
         <v>-403.2</v>
       </c>
-      <c r="P32" s="1">
+      <c r="R32" s="1">
         <v>-403.2</v>
       </c>
-      <c r="Q32" s="2">
+      <c r="S32" s="2">
         <v>-7.9214627829756919E-3</v>
       </c>
-      <c r="R32">
+      <c r="T32">
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>318</v>
-      </c>
-      <c r="C33" t="s">
+        <v>320</v>
+      </c>
+      <c r="E33" t="s">
         <v>292</v>
       </c>
-      <c r="D33">
+      <c r="F33">
         <v>42</v>
       </c>
-      <c r="E33" s="1">
+      <c r="G33" s="1">
         <v>91224</v>
       </c>
-      <c r="F33" s="1">
+      <c r="H33" s="1">
         <v>2172</v>
       </c>
-      <c r="G33">
+      <c r="I33">
         <v>42</v>
       </c>
-      <c r="H33" s="1">
+      <c r="J33" s="1">
         <v>81102.5</v>
       </c>
-      <c r="I33" s="1">
+      <c r="K33" s="1">
         <v>1931.01</v>
       </c>
-      <c r="J33">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="1">
+        <v>0</v>
+      </c>
+      <c r="N33" s="1">
         <v>1790.2</v>
-      </c>
-      <c r="M33" s="1">
-        <v>0</v>
-      </c>
-      <c r="N33" s="1">
-        <v>-10121.5</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -20053,223 +20032,223 @@
       <c r="P33" s="1">
         <v>-10121.5</v>
       </c>
-      <c r="Q33" s="2">
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>-10121.5</v>
+      </c>
+      <c r="S33" s="2">
         <v>-0.1109521617118302</v>
       </c>
-      <c r="R33">
+      <c r="T33">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>285</v>
       </c>
       <c r="B34" t="s">
-        <v>316</v>
-      </c>
-      <c r="C34" t="s">
+        <v>318</v>
+      </c>
+      <c r="E34" t="s">
         <v>293</v>
       </c>
-      <c r="D34">
+      <c r="F34">
         <v>121</v>
       </c>
-      <c r="E34" s="1">
+      <c r="G34" s="1">
         <v>24998.6</v>
       </c>
-      <c r="F34" s="1">
+      <c r="H34" s="1">
         <v>206.6</v>
       </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34">
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34" s="1">
+        <v>0</v>
+      </c>
+      <c r="K34" s="1">
+        <v>0</v>
+      </c>
+      <c r="L34">
         <v>121</v>
       </c>
-      <c r="K34" s="1">
+      <c r="M34" s="1">
         <v>24998.6</v>
       </c>
-      <c r="L34" s="1">
+      <c r="N34" s="1">
         <v>206.55</v>
       </c>
-      <c r="M34" s="1">
+      <c r="O34" s="1">
         <v>24992.55</v>
       </c>
-      <c r="N34" s="1">
-        <v>0</v>
-      </c>
-      <c r="O34" s="1">
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
         <v>-6.05</v>
       </c>
-      <c r="P34" s="1">
+      <c r="R34" s="1">
         <v>-6.05</v>
       </c>
-      <c r="Q34" s="2">
+      <c r="S34" s="2">
         <v>-2.4201355275895451E-4</v>
       </c>
-      <c r="R34">
+      <c r="T34">
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>187</v>
       </c>
       <c r="B35" t="s">
-        <v>316</v>
-      </c>
-      <c r="C35" t="s">
+        <v>318</v>
+      </c>
+      <c r="E35" t="s">
         <v>293</v>
       </c>
-      <c r="D35">
+      <c r="F35">
         <v>300</v>
       </c>
-      <c r="E35" s="1">
+      <c r="G35" s="1">
         <v>25347</v>
       </c>
-      <c r="F35" s="1">
+      <c r="H35" s="1">
         <v>84.49</v>
       </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" s="1">
-        <v>0</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35">
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35" s="1">
+        <v>0</v>
+      </c>
+      <c r="K35" s="1">
+        <v>0</v>
+      </c>
+      <c r="L35">
         <v>300</v>
       </c>
-      <c r="K35" s="1">
+      <c r="M35" s="1">
         <v>25347</v>
       </c>
-      <c r="L35" s="1">
+      <c r="N35" s="1">
         <v>79.790000000000006</v>
       </c>
-      <c r="M35" s="1">
+      <c r="O35" s="1">
         <v>23937</v>
       </c>
-      <c r="N35" s="1">
-        <v>0</v>
-      </c>
-      <c r="O35" s="1">
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
         <v>-1410</v>
       </c>
-      <c r="P35" s="1">
+      <c r="R35" s="1">
         <v>-1410</v>
       </c>
-      <c r="Q35" s="2">
+      <c r="S35" s="2">
         <v>-5.5627884956799621E-2</v>
       </c>
-      <c r="R35">
+      <c r="T35">
         <v>65</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>50</v>
       </c>
       <c r="B36" t="s">
-        <v>317</v>
-      </c>
-      <c r="C36" t="s">
+        <v>319</v>
+      </c>
+      <c r="E36" t="s">
         <v>292</v>
       </c>
-      <c r="D36">
+      <c r="F36">
         <v>30</v>
       </c>
-      <c r="E36" s="1">
+      <c r="G36" s="1">
         <v>93744</v>
       </c>
-      <c r="F36" s="1">
+      <c r="H36" s="1">
         <v>3124.8</v>
       </c>
-      <c r="G36">
+      <c r="I36">
         <v>52</v>
       </c>
-      <c r="H36" s="1">
+      <c r="J36" s="1">
         <v>76804.7</v>
       </c>
-      <c r="I36" s="1">
+      <c r="K36" s="1">
         <v>1477.01</v>
       </c>
-      <c r="J36">
+      <c r="L36">
         <v>-22</v>
       </c>
-      <c r="K36" s="1">
+      <c r="M36" s="1">
         <v>-68745.600000000006</v>
       </c>
-      <c r="L36" s="1">
+      <c r="N36" s="1">
         <v>1433.8</v>
       </c>
-      <c r="M36" s="1">
+      <c r="O36" s="1">
         <v>-31543.599999999999</v>
       </c>
-      <c r="N36" s="1">
+      <c r="P36" s="1">
         <v>-85684.9</v>
       </c>
-      <c r="O36" s="1">
+      <c r="Q36" s="1">
         <v>37202</v>
       </c>
-      <c r="P36" s="1">
+      <c r="R36" s="1">
         <v>-48482.9</v>
       </c>
-      <c r="Q36" s="2">
+      <c r="S36" s="2">
         <v>-0.51718403311145245</v>
       </c>
-      <c r="R36">
+      <c r="T36">
         <v>180</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>317</v>
-      </c>
-      <c r="C37" t="s">
+        <v>319</v>
+      </c>
+      <c r="E37" t="s">
         <v>294</v>
       </c>
-      <c r="D37">
+      <c r="F37">
         <v>200</v>
       </c>
-      <c r="E37" s="1">
+      <c r="G37" s="1">
         <v>25540.1</v>
       </c>
-      <c r="F37" s="1">
+      <c r="H37" s="1">
         <v>127.7</v>
       </c>
-      <c r="G37">
+      <c r="I37">
         <v>200</v>
       </c>
-      <c r="H37" s="1">
+      <c r="J37" s="1">
         <v>23912</v>
       </c>
-      <c r="I37" s="1">
+      <c r="K37" s="1">
         <v>119.56</v>
       </c>
-      <c r="J37">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
-      </c>
-      <c r="L37" s="1">
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37" s="1">
+        <v>0</v>
+      </c>
+      <c r="N37" s="1">
         <v>119.31</v>
-      </c>
-      <c r="M37" s="1">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1">
-        <v>-1628</v>
       </c>
       <c r="O37" s="1">
         <v>0</v>
@@ -20277,223 +20256,223 @@
       <c r="P37" s="1">
         <v>-1628</v>
       </c>
-      <c r="Q37" s="2">
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>-1628</v>
+      </c>
+      <c r="S37" s="2">
         <v>-6.3742898422480723E-2</v>
       </c>
-      <c r="R37">
+      <c r="T37">
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>15</v>
       </c>
       <c r="B38" t="s">
-        <v>317</v>
-      </c>
-      <c r="C38" t="s">
+        <v>319</v>
+      </c>
+      <c r="E38" t="s">
         <v>299</v>
       </c>
-      <c r="D38">
+      <c r="F38">
         <v>38</v>
       </c>
-      <c r="E38" s="1">
+      <c r="G38" s="1">
         <v>287681</v>
       </c>
-      <c r="F38" s="1">
+      <c r="H38" s="1">
         <v>7570.55</v>
       </c>
-      <c r="G38">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1">
-        <v>0</v>
-      </c>
-      <c r="I38" s="1">
-        <v>0</v>
-      </c>
-      <c r="J38">
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" s="1">
+        <v>0</v>
+      </c>
+      <c r="K38" s="1">
+        <v>0</v>
+      </c>
+      <c r="L38">
         <v>38</v>
       </c>
-      <c r="K38" s="1">
+      <c r="M38" s="1">
         <v>287680.90000000002</v>
       </c>
-      <c r="L38" s="1">
+      <c r="N38" s="1">
         <v>8552</v>
       </c>
-      <c r="M38" s="1">
+      <c r="O38" s="1">
         <v>324976</v>
       </c>
-      <c r="N38" s="1">
-        <v>0</v>
-      </c>
-      <c r="O38" s="1">
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
         <v>37295.1</v>
       </c>
-      <c r="P38" s="1">
+      <c r="R38" s="1">
         <v>37295.1</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>0.12964046982595301</v>
       </c>
-      <c r="R38">
+      <c r="T38">
         <v>181</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>318</v>
-      </c>
-      <c r="C39" t="s">
+        <v>320</v>
+      </c>
+      <c r="E39" t="s">
         <v>292</v>
       </c>
-      <c r="D39">
+      <c r="F39">
         <v>188</v>
       </c>
-      <c r="E39" s="1">
+      <c r="G39" s="1">
         <v>99892.650000000009</v>
       </c>
-      <c r="F39" s="1">
+      <c r="H39" s="1">
         <v>531.34</v>
       </c>
-      <c r="G39">
+      <c r="I39">
         <v>163</v>
       </c>
-      <c r="H39" s="1">
+      <c r="J39" s="1">
         <v>78567.95</v>
       </c>
-      <c r="I39" s="1">
+      <c r="K39" s="1">
         <v>482.01</v>
       </c>
-      <c r="J39">
+      <c r="L39">
         <v>25</v>
       </c>
-      <c r="K39" s="1">
+      <c r="M39" s="1">
         <v>13283.5</v>
       </c>
-      <c r="L39" s="1">
+      <c r="N39" s="1">
         <v>423.5</v>
       </c>
-      <c r="M39" s="1">
+      <c r="O39" s="1">
         <v>10587.5</v>
       </c>
-      <c r="N39" s="1">
+      <c r="P39" s="1">
         <v>-8040.47</v>
       </c>
-      <c r="O39" s="1">
+      <c r="Q39" s="1">
         <v>-2696</v>
       </c>
-      <c r="P39" s="1">
+      <c r="R39" s="1">
         <v>-10736.47</v>
       </c>
-      <c r="Q39" s="2">
+      <c r="S39" s="2">
         <v>-0.10748007986573591</v>
       </c>
-      <c r="R39">
+      <c r="T39">
         <v>153</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>318</v>
-      </c>
-      <c r="C40" t="s">
+        <v>320</v>
+      </c>
+      <c r="E40" t="s">
         <v>294</v>
       </c>
-      <c r="D40">
+      <c r="F40">
         <v>204</v>
       </c>
-      <c r="E40" s="1">
+      <c r="G40" s="1">
         <v>48757.69</v>
       </c>
-      <c r="F40" s="1">
+      <c r="H40" s="1">
         <v>239.01</v>
       </c>
-      <c r="G40">
+      <c r="I40">
         <v>220</v>
       </c>
-      <c r="H40" s="1">
+      <c r="J40" s="1">
         <v>54098</v>
       </c>
-      <c r="I40" s="1">
+      <c r="K40" s="1">
         <v>245.9</v>
       </c>
-      <c r="J40">
+      <c r="L40">
         <v>-16</v>
       </c>
-      <c r="K40" s="1">
+      <c r="M40" s="1">
         <v>-3824.16</v>
       </c>
-      <c r="L40" s="1">
+      <c r="N40" s="1">
         <v>333.45</v>
       </c>
-      <c r="M40" s="1">
+      <c r="O40" s="1">
         <v>-5335.2</v>
       </c>
-      <c r="N40" s="1">
+      <c r="P40" s="1">
         <v>1515.8</v>
       </c>
-      <c r="O40" s="1">
+      <c r="Q40" s="1">
         <v>-1511.04</v>
       </c>
-      <c r="P40" s="1">
+      <c r="R40" s="1">
         <v>4.76</v>
       </c>
-      <c r="Q40" s="2">
+      <c r="S40" s="2">
         <v>9.7625625824357127E-5</v>
       </c>
-      <c r="R40">
+      <c r="T40">
         <v>153</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>263</v>
       </c>
       <c r="B41" t="s">
-        <v>318</v>
-      </c>
-      <c r="C41" t="s">
+        <v>320</v>
+      </c>
+      <c r="E41" t="s">
         <v>293</v>
       </c>
-      <c r="D41">
+      <c r="F41">
         <v>10</v>
       </c>
-      <c r="E41" s="1">
+      <c r="G41" s="1">
         <v>4835.5</v>
       </c>
-      <c r="F41" s="1">
+      <c r="H41" s="1">
         <v>483.55</v>
       </c>
-      <c r="G41">
+      <c r="I41">
         <v>10</v>
       </c>
-      <c r="H41" s="1">
+      <c r="J41" s="1">
         <v>4193</v>
       </c>
-      <c r="I41" s="1">
+      <c r="K41" s="1">
         <v>419.3</v>
       </c>
-      <c r="J41">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
-      </c>
-      <c r="L41" s="1">
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41" s="1">
+        <v>0</v>
+      </c>
+      <c r="N41" s="1">
         <v>395.8</v>
-      </c>
-      <c r="M41" s="1">
-        <v>0</v>
-      </c>
-      <c r="N41" s="1">
-        <v>-642.5</v>
       </c>
       <c r="O41" s="1">
         <v>0</v>
@@ -20501,167 +20480,167 @@
       <c r="P41" s="1">
         <v>-642.5</v>
       </c>
-      <c r="Q41" s="2">
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>-642.5</v>
+      </c>
+      <c r="S41" s="2">
         <v>-0.1328714714093682</v>
       </c>
-      <c r="R41">
+      <c r="T41">
         <v>15</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>136</v>
       </c>
       <c r="B42" t="s">
-        <v>317</v>
-      </c>
-      <c r="C42" t="s">
+        <v>319</v>
+      </c>
+      <c r="E42" t="s">
         <v>297</v>
       </c>
-      <c r="D42">
+      <c r="F42">
         <v>208</v>
       </c>
-      <c r="E42" s="1">
+      <c r="G42" s="1">
         <v>233369.9</v>
       </c>
-      <c r="F42" s="1">
+      <c r="H42" s="1">
         <v>1121.97</v>
       </c>
-      <c r="G42">
-        <v>0</v>
-      </c>
-      <c r="H42" s="1">
-        <v>0</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42">
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42" s="1">
+        <v>0</v>
+      </c>
+      <c r="K42" s="1">
+        <v>0</v>
+      </c>
+      <c r="L42">
         <v>208</v>
       </c>
-      <c r="K42" s="1">
+      <c r="M42" s="1">
         <v>233369.76</v>
       </c>
-      <c r="L42" s="1">
+      <c r="N42" s="1">
         <v>1143</v>
       </c>
-      <c r="M42" s="1">
+      <c r="O42" s="1">
         <v>237744</v>
       </c>
-      <c r="N42" s="1">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1">
+      <c r="P42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="1">
         <v>4374.24</v>
       </c>
-      <c r="P42" s="1">
+      <c r="R42" s="1">
         <v>4374.24</v>
       </c>
-      <c r="Q42" s="2">
+      <c r="S42" s="2">
         <v>1.874380543506253E-2</v>
       </c>
-      <c r="R42">
+      <c r="T42">
         <v>125</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>239</v>
       </c>
       <c r="B43" t="s">
-        <v>318</v>
-      </c>
-      <c r="C43" t="s">
+        <v>320</v>
+      </c>
+      <c r="E43" t="s">
         <v>296</v>
       </c>
-      <c r="D43">
+      <c r="F43">
         <v>34</v>
       </c>
-      <c r="E43" s="1">
+      <c r="G43" s="1">
         <v>45832.9</v>
       </c>
-      <c r="F43" s="1">
+      <c r="H43" s="1">
         <v>1348.03</v>
       </c>
-      <c r="G43">
-        <v>0</v>
-      </c>
-      <c r="H43" s="1">
-        <v>0</v>
-      </c>
-      <c r="I43" s="1">
-        <v>0</v>
-      </c>
-      <c r="J43">
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43" s="1">
+        <v>0</v>
+      </c>
+      <c r="K43" s="1">
+        <v>0</v>
+      </c>
+      <c r="L43">
         <v>34</v>
       </c>
-      <c r="K43" s="1">
+      <c r="M43" s="1">
         <v>45833.02</v>
       </c>
-      <c r="L43" s="1">
+      <c r="N43" s="1">
         <v>1346</v>
       </c>
-      <c r="M43" s="1">
+      <c r="O43" s="1">
         <v>45764</v>
       </c>
-      <c r="N43" s="1">
-        <v>0</v>
-      </c>
-      <c r="O43" s="1">
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
         <v>-69.02</v>
       </c>
-      <c r="P43" s="1">
+      <c r="R43" s="1">
         <v>-69.02</v>
       </c>
-      <c r="Q43" s="2">
+      <c r="S43" s="2">
         <v>-1.5059051467395689E-3</v>
       </c>
-      <c r="R43">
+      <c r="T43">
         <v>37</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>211</v>
       </c>
       <c r="B44" t="s">
-        <v>318</v>
-      </c>
-      <c r="C44" t="s">
+        <v>320</v>
+      </c>
+      <c r="E44" t="s">
         <v>293</v>
       </c>
-      <c r="D44">
+      <c r="F44">
         <v>600</v>
       </c>
-      <c r="E44" s="1">
+      <c r="G44" s="1">
         <v>26682</v>
       </c>
-      <c r="F44" s="1">
+      <c r="H44" s="1">
         <v>44.47</v>
       </c>
-      <c r="G44">
+      <c r="I44">
         <v>600</v>
       </c>
-      <c r="H44" s="1">
+      <c r="J44" s="1">
         <v>22532.01</v>
       </c>
-      <c r="I44" s="1">
+      <c r="K44" s="1">
         <v>37.549999999999997</v>
       </c>
-      <c r="J44">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
-      </c>
-      <c r="L44" s="1">
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44" s="1">
+        <v>0</v>
+      </c>
+      <c r="N44" s="1">
         <v>39.81</v>
-      </c>
-      <c r="M44" s="1">
-        <v>0</v>
-      </c>
-      <c r="N44" s="1">
-        <v>-4149.99</v>
       </c>
       <c r="O44" s="1">
         <v>0</v>
@@ -20669,55 +20648,55 @@
       <c r="P44" s="1">
         <v>-4149.99</v>
       </c>
-      <c r="Q44" s="2">
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>-4149.99</v>
+      </c>
+      <c r="S44" s="2">
         <v>-0.1555351922644479</v>
       </c>
-      <c r="R44">
+      <c r="T44">
         <v>14</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>67</v>
       </c>
       <c r="B45" t="s">
-        <v>318</v>
-      </c>
-      <c r="C45" t="s">
+        <v>320</v>
+      </c>
+      <c r="E45" t="s">
         <v>293</v>
       </c>
-      <c r="D45">
+      <c r="F45">
         <v>57</v>
       </c>
-      <c r="E45" s="1">
+      <c r="G45" s="1">
         <v>50160</v>
       </c>
-      <c r="F45" s="1">
+      <c r="H45" s="1">
         <v>880</v>
       </c>
-      <c r="G45">
+      <c r="I45">
         <v>57</v>
       </c>
-      <c r="H45" s="1">
+      <c r="J45" s="1">
         <v>44850.6</v>
       </c>
-      <c r="I45" s="1">
+      <c r="K45" s="1">
         <v>786.85</v>
       </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
-      </c>
-      <c r="L45" s="1">
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45" s="1">
+        <v>0</v>
+      </c>
+      <c r="N45" s="1">
         <v>669.2</v>
-      </c>
-      <c r="M45" s="1">
-        <v>0</v>
-      </c>
-      <c r="N45" s="1">
-        <v>-5309.4</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -20725,55 +20704,55 @@
       <c r="P45" s="1">
         <v>-5309.4</v>
       </c>
-      <c r="Q45" s="2">
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>-5309.4</v>
+      </c>
+      <c r="S45" s="2">
         <v>-0.10584928229665071</v>
       </c>
-      <c r="R45">
+      <c r="T45">
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>316</v>
-      </c>
-      <c r="C46" t="s">
+        <v>318</v>
+      </c>
+      <c r="E46" t="s">
         <v>292</v>
       </c>
-      <c r="D46">
-        <v>20</v>
-      </c>
-      <c r="E46" s="1">
+      <c r="F46">
+        <v>20</v>
+      </c>
+      <c r="G46" s="1">
         <v>90180</v>
       </c>
-      <c r="F46" s="1">
+      <c r="H46" s="1">
         <v>4509</v>
       </c>
-      <c r="G46">
-        <v>20</v>
-      </c>
-      <c r="H46" s="1">
+      <c r="I46">
+        <v>20</v>
+      </c>
+      <c r="J46" s="1">
         <v>83602.900399999999</v>
       </c>
-      <c r="I46" s="1">
+      <c r="K46" s="1">
         <v>4180.1499999999996</v>
       </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0</v>
-      </c>
-      <c r="L46" s="1">
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46" s="1">
+        <v>0</v>
+      </c>
+      <c r="N46" s="1">
         <v>3947.7</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>-6577.1</v>
       </c>
       <c r="O46" s="1">
         <v>0</v>
@@ -20781,167 +20760,167 @@
       <c r="P46" s="1">
         <v>-6577.1</v>
       </c>
-      <c r="Q46" s="2">
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>-6577.1</v>
+      </c>
+      <c r="S46" s="2">
         <v>-7.2933022843202494E-2</v>
       </c>
-      <c r="R46">
+      <c r="T46">
         <v>25</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>273</v>
       </c>
       <c r="B47" t="s">
-        <v>318</v>
-      </c>
-      <c r="C47" t="s">
+        <v>320</v>
+      </c>
+      <c r="E47" t="s">
         <v>293</v>
       </c>
-      <c r="D47">
+      <c r="F47">
         <v>80</v>
       </c>
-      <c r="E47" s="1">
+      <c r="G47" s="1">
         <v>25175.98</v>
       </c>
-      <c r="F47" s="1">
+      <c r="H47" s="1">
         <v>314.7</v>
       </c>
-      <c r="G47">
-        <v>0</v>
-      </c>
-      <c r="H47" s="1">
-        <v>0</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47">
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47" s="1">
+        <v>0</v>
+      </c>
+      <c r="K47" s="1">
+        <v>0</v>
+      </c>
+      <c r="L47">
         <v>80</v>
       </c>
-      <c r="K47" s="1">
+      <c r="M47" s="1">
         <v>25176</v>
       </c>
-      <c r="L47" s="1">
+      <c r="N47" s="1">
         <v>293.64999999999998</v>
       </c>
-      <c r="M47" s="1">
+      <c r="O47" s="1">
         <v>23492</v>
       </c>
-      <c r="N47" s="1">
-        <v>0</v>
-      </c>
-      <c r="O47" s="1">
+      <c r="P47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="1">
         <v>-1684</v>
       </c>
-      <c r="P47" s="1">
+      <c r="R47" s="1">
         <v>-1684</v>
       </c>
-      <c r="Q47" s="2">
+      <c r="S47" s="2">
         <v>-6.688915386809173E-2</v>
       </c>
-      <c r="R47">
+      <c r="T47">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>258</v>
       </c>
       <c r="B48" t="s">
-        <v>318</v>
-      </c>
-      <c r="C48" t="s">
+        <v>320</v>
+      </c>
+      <c r="E48" t="s">
         <v>294</v>
       </c>
-      <c r="D48">
+      <c r="F48">
         <v>55</v>
       </c>
-      <c r="E48" s="1">
+      <c r="G48" s="1">
         <v>49398.5</v>
       </c>
-      <c r="F48" s="1">
+      <c r="H48" s="1">
         <v>898.15</v>
       </c>
-      <c r="G48">
-        <v>0</v>
-      </c>
-      <c r="H48" s="1">
-        <v>0</v>
-      </c>
-      <c r="I48" s="1">
-        <v>0</v>
-      </c>
-      <c r="J48">
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48" s="1">
+        <v>0</v>
+      </c>
+      <c r="K48" s="1">
+        <v>0</v>
+      </c>
+      <c r="L48">
         <v>55</v>
       </c>
-      <c r="K48" s="1">
+      <c r="M48" s="1">
         <v>49398.25</v>
       </c>
-      <c r="L48" s="1">
+      <c r="N48" s="1">
         <v>878.75</v>
       </c>
-      <c r="M48" s="1">
+      <c r="O48" s="1">
         <v>48331.25</v>
       </c>
-      <c r="N48" s="1">
-        <v>0</v>
-      </c>
-      <c r="O48" s="1">
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
         <v>-1067</v>
       </c>
-      <c r="P48" s="1">
+      <c r="R48" s="1">
         <v>-1067</v>
       </c>
-      <c r="Q48" s="2">
+      <c r="S48" s="2">
         <v>-2.1599846149174571E-2</v>
       </c>
-      <c r="R48">
+      <c r="T48">
         <v>24</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>31</v>
       </c>
       <c r="B49" t="s">
-        <v>317</v>
-      </c>
-      <c r="C49" t="s">
+        <v>319</v>
+      </c>
+      <c r="E49" t="s">
         <v>292</v>
       </c>
-      <c r="D49">
+      <c r="F49">
         <v>25</v>
       </c>
-      <c r="E49" s="1">
+      <c r="G49" s="1">
         <v>91567.5</v>
       </c>
-      <c r="F49" s="1">
+      <c r="H49" s="1">
         <v>3662.7</v>
       </c>
-      <c r="G49">
+      <c r="I49">
         <v>25</v>
       </c>
-      <c r="H49" s="1">
+      <c r="J49" s="1">
         <v>84762.5</v>
       </c>
-      <c r="I49" s="1">
+      <c r="K49" s="1">
         <v>3390.5</v>
       </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
-      </c>
-      <c r="L49" s="1">
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49" s="1">
+        <v>0</v>
+      </c>
+      <c r="N49" s="1">
         <v>4244.6000000000004</v>
-      </c>
-      <c r="M49" s="1">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1">
-        <v>-6805</v>
       </c>
       <c r="O49" s="1">
         <v>0</v>
@@ -20949,55 +20928,55 @@
       <c r="P49" s="1">
         <v>-6805</v>
       </c>
-      <c r="Q49" s="2">
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>-6805</v>
+      </c>
+      <c r="S49" s="2">
         <v>-7.431676085947525E-2</v>
       </c>
-      <c r="R49">
+      <c r="T49">
         <v>25</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>157</v>
       </c>
       <c r="B50" t="s">
-        <v>318</v>
-      </c>
-      <c r="C50" t="s">
+        <v>320</v>
+      </c>
+      <c r="E50" t="s">
         <v>294</v>
       </c>
-      <c r="D50">
+      <c r="F50">
         <v>22</v>
       </c>
-      <c r="E50" s="1">
+      <c r="G50" s="1">
         <v>101483.5</v>
       </c>
-      <c r="F50" s="1">
+      <c r="H50" s="1">
         <v>4612.8900000000003</v>
       </c>
-      <c r="G50">
+      <c r="I50">
         <v>22</v>
       </c>
-      <c r="H50" s="1">
+      <c r="J50" s="1">
         <v>88669.197999999989</v>
       </c>
-      <c r="I50" s="1">
+      <c r="K50" s="1">
         <v>4030.42</v>
       </c>
-      <c r="J50">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1">
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50" s="1">
+        <v>0</v>
+      </c>
+      <c r="N50" s="1">
         <v>3700.9</v>
-      </c>
-      <c r="M50" s="1">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1">
-        <v>-12814.38</v>
       </c>
       <c r="O50" s="1">
         <v>0</v>
@@ -21005,66 +20984,72 @@
       <c r="P50" s="1">
         <v>-12814.38</v>
       </c>
-      <c r="Q50" s="2">
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>-12814.38</v>
+      </c>
+      <c r="S50" s="2">
         <v>-0.1262705760049663</v>
       </c>
-      <c r="R50">
+      <c r="T50">
         <v>60</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>316</v>
-      </c>
-      <c r="C51" t="s">
+        <v>318</v>
+      </c>
+      <c r="E51" t="s">
         <v>293</v>
       </c>
-      <c r="D51">
+      <c r="F51">
         <v>37</v>
       </c>
-      <c r="E51" s="1">
+      <c r="G51" s="1">
         <v>47700.4</v>
       </c>
-      <c r="F51" s="1">
+      <c r="H51" s="1">
         <v>1289.2</v>
       </c>
-      <c r="G51">
-        <v>0</v>
-      </c>
-      <c r="H51" s="1">
-        <v>0</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
-      <c r="J51">
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0</v>
+      </c>
+      <c r="K51" s="1">
+        <v>0</v>
+      </c>
+      <c r="L51">
         <v>37</v>
       </c>
-      <c r="K51" s="1">
+      <c r="M51" s="1">
         <v>47700.4</v>
       </c>
-      <c r="L51" s="1">
+      <c r="N51" s="1">
         <v>1121.3</v>
       </c>
-      <c r="M51" s="1">
+      <c r="O51" s="1">
         <v>41488.1</v>
       </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="O51" s="1">
+      <c r="P51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="1">
         <v>-6212.3</v>
       </c>
-      <c r="P51" s="1">
+      <c r="R51" s="1">
         <v>-6212.3</v>
       </c>
-      <c r="Q51" s="2">
+      <c r="S51" s="2">
         <v>-0.13023580515048089</v>
       </c>
-      <c r="R51">
+      <c r="T51">
         <v>180</v>
       </c>
     </row>

--- a/Transformed_Tradebook.xlsx
+++ b/Transformed_Tradebook.xlsx
@@ -32512,7 +32512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V30"/>
+  <dimension ref="A1:W30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="27" min="1" max="1"/>
@@ -32527,16 +32527,17 @@
     <col width="27" customWidth="1" style="27" min="10" max="10"/>
     <col width="16" customWidth="1" style="27" min="11" max="11"/>
     <col width="14" customWidth="1" style="27" min="12" max="12"/>
-    <col width="17" customWidth="1" style="27" min="13" max="13"/>
-    <col width="15" customWidth="1" style="27" min="14" max="14"/>
+    <col width="16" customWidth="1" style="27" min="13" max="13"/>
+    <col width="17" customWidth="1" style="27" min="14" max="14"/>
     <col width="15" customWidth="1" style="27" min="15" max="15"/>
-    <col width="14" customWidth="1" style="27" min="16" max="16"/>
-    <col width="15" customWidth="1" style="27" min="17" max="17"/>
-    <col width="16" customWidth="1" style="27" min="18" max="18"/>
+    <col width="15" customWidth="1" style="27" min="16" max="16"/>
+    <col width="14" customWidth="1" style="27" min="17" max="17"/>
+    <col width="15" customWidth="1" style="27" min="18" max="18"/>
     <col width="16" customWidth="1" style="27" min="19" max="19"/>
     <col width="16" customWidth="1" style="27" min="20" max="20"/>
-    <col width="25" customWidth="1" style="27" min="21" max="21"/>
-    <col width="14" customWidth="1" style="27" min="22" max="22"/>
+    <col width="16" customWidth="1" style="27" min="21" max="21"/>
+    <col width="25" customWidth="1" style="27" min="22" max="22"/>
+    <col width="14" customWidth="1" style="27" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -32602,50 +32603,55 @@
       </c>
       <c r="M1" s="48" t="inlineStr">
         <is>
+          <t>Prev_Day_Close</t>
+        </is>
+      </c>
+      <c r="N1" s="48" t="inlineStr">
+        <is>
           <t>Prev_Week_Close</t>
         </is>
       </c>
-      <c r="N1" s="48" t="inlineStr">
+      <c r="O1" s="48" t="inlineStr">
         <is>
           <t>EMA9</t>
         </is>
       </c>
-      <c r="O1" s="48" t="inlineStr">
+      <c r="P1" s="48" t="inlineStr">
         <is>
           <t>EMA10</t>
         </is>
       </c>
-      <c r="P1" s="48" t="inlineStr">
+      <c r="Q1" s="48" t="inlineStr">
         <is>
           <t>EMA11</t>
         </is>
       </c>
-      <c r="Q1" s="48" t="inlineStr">
+      <c r="R1" s="48" t="inlineStr">
         <is>
           <t>EMA21</t>
         </is>
       </c>
-      <c r="R1" s="48" t="inlineStr">
+      <c r="S1" s="48" t="inlineStr">
         <is>
           <t>Current_Value</t>
         </is>
       </c>
-      <c r="S1" s="48" t="inlineStr">
+      <c r="T1" s="48" t="inlineStr">
         <is>
           <t>Unrealized_PnL</t>
         </is>
       </c>
-      <c r="T1" s="48" t="inlineStr">
+      <c r="U1" s="48" t="inlineStr">
         <is>
           <t>Holding_Period</t>
         </is>
       </c>
-      <c r="U1" s="48" t="inlineStr">
+      <c r="V1" s="48" t="inlineStr">
         <is>
           <t>Split_Info</t>
         </is>
       </c>
-      <c r="V1" s="48" t="inlineStr">
+      <c r="W1" s="48" t="inlineStr">
         <is>
           <t>Adj_Required</t>
         </is>
@@ -32699,31 +32705,34 @@
         <v>2886.5</v>
       </c>
       <c r="M2" s="51" t="n">
+        <v>2799.1</v>
+      </c>
+      <c r="N2" s="51" t="n">
         <v>2731</v>
       </c>
-      <c r="N2" s="51" t="n">
+      <c r="O2" s="51" t="n">
         <v>2763.25</v>
       </c>
-      <c r="O2" s="51" t="n">
+      <c r="P2" s="51" t="n">
         <v>2752.93</v>
       </c>
-      <c r="P2" s="51" t="n">
+      <c r="Q2" s="51" t="n">
         <v>2742.62</v>
       </c>
-      <c r="Q2" s="51" t="n">
+      <c r="R2" s="51" t="n">
         <v>2648.69</v>
       </c>
-      <c r="R2" s="51" t="n">
+      <c r="S2" s="51" t="n">
         <v>51957</v>
       </c>
-      <c r="S2" s="51" t="n">
+      <c r="T2" s="51" t="n">
         <v>2817</v>
       </c>
-      <c r="T2" s="49" t="n">
+      <c r="U2" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="U2" s="49" t="inlineStr"/>
-      <c r="V2" s="49" t="inlineStr">
+      <c r="V2" s="49" t="inlineStr"/>
+      <c r="W2" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -32777,31 +32786,34 @@
         <v>2725</v>
       </c>
       <c r="M3" s="51" t="n">
+        <v>2689.8</v>
+      </c>
+      <c r="N3" s="51" t="n">
         <v>2716</v>
       </c>
-      <c r="N3" s="51" t="n">
+      <c r="O3" s="51" t="n">
         <v>2404.44</v>
       </c>
-      <c r="O3" s="51" t="n">
+      <c r="P3" s="51" t="n">
         <v>2381.91</v>
       </c>
-      <c r="P3" s="51" t="n">
+      <c r="Q3" s="51" t="n">
         <v>2362.91</v>
       </c>
-      <c r="Q3" s="51" t="n">
+      <c r="R3" s="51" t="n">
         <v>2282.12</v>
       </c>
-      <c r="R3" s="51" t="n">
+      <c r="S3" s="51" t="n">
         <v>51775</v>
       </c>
-      <c r="S3" s="51" t="n">
+      <c r="T3" s="51" t="n">
         <v>-41.8</v>
       </c>
-      <c r="T3" s="49" t="n">
+      <c r="U3" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="U3" s="49" t="inlineStr"/>
-      <c r="V3" s="49" t="inlineStr">
+      <c r="V3" s="49" t="inlineStr"/>
+      <c r="W3" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -32855,31 +32867,34 @@
         <v>3248.2</v>
       </c>
       <c r="M4" s="51" t="n">
+        <v>3214.1</v>
+      </c>
+      <c r="N4" s="51" t="n">
         <v>3177.2</v>
       </c>
-      <c r="N4" s="51" t="n">
+      <c r="O4" s="51" t="n">
         <v>2993.13</v>
       </c>
-      <c r="O4" s="51" t="n">
+      <c r="P4" s="51" t="n">
         <v>2980.46</v>
       </c>
-      <c r="P4" s="51" t="n">
+      <c r="Q4" s="51" t="n">
         <v>2969.06</v>
       </c>
-      <c r="Q4" s="51" t="n">
+      <c r="R4" s="51" t="n">
         <v>2885.09</v>
       </c>
-      <c r="R4" s="51" t="n">
+      <c r="S4" s="51" t="n">
         <v>45474.8</v>
       </c>
-      <c r="S4" s="51" t="n">
+      <c r="T4" s="51" t="n">
         <v>1589.56</v>
       </c>
-      <c r="T4" s="49" t="n">
+      <c r="U4" s="49" t="n">
         <v>134</v>
       </c>
-      <c r="U4" s="49" t="inlineStr"/>
-      <c r="V4" s="49" t="inlineStr">
+      <c r="V4" s="49" t="inlineStr"/>
+      <c r="W4" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -32933,31 +32948,34 @@
         <v>1864.5</v>
       </c>
       <c r="M5" s="51" t="n">
+        <v>1876</v>
+      </c>
+      <c r="N5" s="51" t="n">
         <v>1890.2</v>
       </c>
-      <c r="N5" s="51" t="n">
+      <c r="O5" s="51" t="n">
         <v>1896.42</v>
       </c>
-      <c r="O5" s="51" t="n">
+      <c r="P5" s="51" t="n">
         <v>1899.74</v>
       </c>
-      <c r="P5" s="51" t="n">
+      <c r="Q5" s="51" t="n">
         <v>1903</v>
       </c>
-      <c r="Q5" s="51" t="n">
+      <c r="R5" s="51" t="n">
         <v>1930.85</v>
       </c>
-      <c r="R5" s="51" t="n">
+      <c r="S5" s="51" t="n">
         <v>178992</v>
       </c>
-      <c r="S5" s="51" t="n">
+      <c r="T5" s="51" t="n">
         <v>-22684.8</v>
       </c>
-      <c r="T5" s="49" t="n">
+      <c r="U5" s="49" t="n">
         <v>99</v>
       </c>
-      <c r="U5" s="49" t="inlineStr"/>
-      <c r="V5" s="49" t="inlineStr">
+      <c r="V5" s="49" t="inlineStr"/>
+      <c r="W5" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33011,31 +33029,34 @@
         <v>340.7</v>
       </c>
       <c r="M6" s="51" t="n">
+        <v>311</v>
+      </c>
+      <c r="N6" s="51" t="n">
         <v>294.55</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="O6" s="51" t="n">
         <v>286.26</v>
       </c>
-      <c r="O6" s="51" t="n">
+      <c r="P6" s="51" t="n">
         <v>282.74</v>
       </c>
-      <c r="P6" s="51" t="n">
+      <c r="Q6" s="51" t="n">
         <v>279.71</v>
       </c>
-      <c r="Q6" s="51" t="n">
+      <c r="R6" s="51" t="n">
         <v>263.78</v>
       </c>
-      <c r="R6" s="51" t="n">
+      <c r="S6" s="51" t="n">
         <v>58259.7</v>
       </c>
-      <c r="S6" s="51" t="n">
+      <c r="T6" s="51" t="n">
         <v>8011.35</v>
       </c>
-      <c r="T6" s="49" t="n">
+      <c r="U6" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="U6" s="49" t="inlineStr"/>
-      <c r="V6" s="49" t="inlineStr">
+      <c r="V6" s="49" t="inlineStr"/>
+      <c r="W6" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33089,31 +33110,34 @@
         <v>1092.7</v>
       </c>
       <c r="M7" s="51" t="n">
+        <v>1087.2</v>
+      </c>
+      <c r="N7" s="51" t="n">
         <v>1106.6</v>
       </c>
-      <c r="N7" s="51" t="n">
+      <c r="O7" s="51" t="n">
         <v>1071.35</v>
       </c>
-      <c r="O7" s="51" t="n">
+      <c r="P7" s="51" t="n">
         <v>1065.35</v>
       </c>
-      <c r="P7" s="51" t="n">
+      <c r="Q7" s="51" t="n">
         <v>1059.84</v>
       </c>
-      <c r="Q7" s="51" t="n">
+      <c r="R7" s="51" t="n">
         <v>1026.04</v>
       </c>
-      <c r="R7" s="51" t="n">
+      <c r="S7" s="51" t="n">
         <v>48078.8</v>
       </c>
-      <c r="S7" s="51" t="n">
+      <c r="T7" s="51" t="n">
         <v>-2149.4</v>
       </c>
-      <c r="T7" s="49" t="n">
+      <c r="U7" s="49" t="n">
         <v>22</v>
       </c>
-      <c r="U7" s="49" t="inlineStr"/>
-      <c r="V7" s="49" t="inlineStr">
+      <c r="V7" s="49" t="inlineStr"/>
+      <c r="W7" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33167,31 +33191,34 @@
         <v>1512.8</v>
       </c>
       <c r="M8" s="51" t="n">
+        <v>1500.5</v>
+      </c>
+      <c r="N8" s="51" t="n">
         <v>1511.8</v>
       </c>
-      <c r="N8" s="51" t="n">
+      <c r="O8" s="51" t="n">
         <v>1419.55</v>
       </c>
-      <c r="O8" s="51" t="n">
+      <c r="P8" s="51" t="n">
         <v>1409.4</v>
       </c>
-      <c r="P8" s="51" t="n">
+      <c r="Q8" s="51" t="n">
         <v>1399.88</v>
       </c>
-      <c r="Q8" s="51" t="n">
+      <c r="R8" s="51" t="n">
         <v>1330.54</v>
       </c>
-      <c r="R8" s="51" t="n">
+      <c r="S8" s="51" t="n">
         <v>49922.4</v>
       </c>
-      <c r="S8" s="51" t="n">
+      <c r="T8" s="51" t="n">
         <v>237.6</v>
       </c>
-      <c r="T8" s="49" t="n">
+      <c r="U8" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="U8" s="49" t="inlineStr"/>
-      <c r="V8" s="49" t="inlineStr">
+      <c r="V8" s="49" t="inlineStr"/>
+      <c r="W8" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33245,31 +33272,34 @@
         <v>1708.8</v>
       </c>
       <c r="M9" s="51" t="n">
+        <v>1763</v>
+      </c>
+      <c r="N9" s="51" t="n">
         <v>1706.2</v>
       </c>
-      <c r="N9" s="51" t="n">
+      <c r="O9" s="51" t="n">
         <v>1399.94</v>
       </c>
-      <c r="O9" s="51" t="n">
+      <c r="P9" s="51" t="n">
         <v>1379.1</v>
       </c>
-      <c r="P9" s="51" t="n">
+      <c r="Q9" s="51" t="n">
         <v>1361.36</v>
       </c>
-      <c r="Q9" s="51" t="n">
+      <c r="R9" s="51" t="n">
         <v>1282.54</v>
       </c>
-      <c r="R9" s="51" t="n">
+      <c r="S9" s="51" t="n">
         <v>49555.2</v>
       </c>
-      <c r="S9" s="51" t="n">
+      <c r="T9" s="51" t="n">
         <v>-133.98</v>
       </c>
-      <c r="T9" s="49" t="n">
+      <c r="U9" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="U9" s="49" t="inlineStr"/>
-      <c r="V9" s="49" t="inlineStr">
+      <c r="V9" s="49" t="inlineStr"/>
+      <c r="W9" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33323,31 +33353,34 @@
         <v>4190.8</v>
       </c>
       <c r="M10" s="51" t="n">
+        <v>4120.7</v>
+      </c>
+      <c r="N10" s="51" t="n">
         <v>4000.6</v>
       </c>
-      <c r="N10" s="51" t="n">
+      <c r="O10" s="51" t="n">
         <v>3623.33</v>
       </c>
-      <c r="O10" s="51" t="n">
+      <c r="P10" s="51" t="n">
         <v>3575.74</v>
       </c>
-      <c r="P10" s="51" t="n">
+      <c r="Q10" s="51" t="n">
         <v>3532.3</v>
       </c>
-      <c r="Q10" s="51" t="n">
+      <c r="R10" s="51" t="n">
         <v>3236.77</v>
       </c>
-      <c r="R10" s="51" t="n">
+      <c r="S10" s="51" t="n">
         <v>75434.39999999999</v>
       </c>
-      <c r="S10" s="51" t="n">
+      <c r="T10" s="51" t="n">
         <v>25005.6</v>
       </c>
-      <c r="T10" s="49" t="n">
+      <c r="U10" s="49" t="n">
         <v>162</v>
       </c>
-      <c r="U10" s="49" t="inlineStr"/>
-      <c r="V10" s="49" t="inlineStr">
+      <c r="V10" s="49" t="inlineStr"/>
+      <c r="W10" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33401,31 +33434,34 @@
         <v>1089.4</v>
       </c>
       <c r="M11" s="51" t="n">
+        <v>1090.4</v>
+      </c>
+      <c r="N11" s="51" t="n">
         <v>1116.3</v>
       </c>
-      <c r="N11" s="51" t="n">
+      <c r="O11" s="51" t="n">
         <v>1111.93</v>
       </c>
-      <c r="O11" s="51" t="n">
+      <c r="P11" s="51" t="n">
         <v>1113.34</v>
       </c>
-      <c r="P11" s="51" t="n">
+      <c r="Q11" s="51" t="n">
         <v>1114.44</v>
       </c>
-      <c r="Q11" s="51" t="n">
+      <c r="R11" s="51" t="n">
         <v>1115.26</v>
       </c>
-      <c r="R11" s="51" t="n">
+      <c r="S11" s="51" t="n">
         <v>53380.6</v>
       </c>
-      <c r="S11" s="51" t="n">
+      <c r="T11" s="51" t="n">
         <v>2755.76</v>
       </c>
-      <c r="T11" s="49" t="n">
+      <c r="U11" s="49" t="n">
         <v>71</v>
       </c>
-      <c r="U11" s="49" t="inlineStr"/>
-      <c r="V11" s="49" t="inlineStr">
+      <c r="V11" s="49" t="inlineStr"/>
+      <c r="W11" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33479,31 +33515,34 @@
         <v>819.4</v>
       </c>
       <c r="M12" s="51" t="n">
+        <v>808.75</v>
+      </c>
+      <c r="N12" s="51" t="n">
         <v>838.2</v>
       </c>
-      <c r="N12" s="51" t="n">
+      <c r="O12" s="51" t="n">
         <v>792.23</v>
       </c>
-      <c r="O12" s="51" t="n">
+      <c r="P12" s="51" t="n">
         <v>786.23</v>
       </c>
-      <c r="P12" s="51" t="n">
+      <c r="Q12" s="51" t="n">
         <v>780.66</v>
       </c>
-      <c r="Q12" s="51" t="n">
+      <c r="R12" s="51" t="n">
         <v>744.23</v>
       </c>
-      <c r="R12" s="51" t="n">
+      <c r="S12" s="51" t="n">
         <v>77023.60000000001</v>
       </c>
-      <c r="S12" s="51" t="n">
+      <c r="T12" s="51" t="n">
         <v>1747.46</v>
       </c>
-      <c r="T12" s="49" t="n">
+      <c r="U12" s="49" t="n">
         <v>246</v>
       </c>
-      <c r="U12" s="49" t="inlineStr"/>
-      <c r="V12" s="49" t="inlineStr">
+      <c r="V12" s="49" t="inlineStr"/>
+      <c r="W12" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33557,35 +33596,38 @@
         <v>114.34</v>
       </c>
       <c r="M13" s="51" t="n">
+        <v>120.84</v>
+      </c>
+      <c r="N13" s="51" t="n">
         <v>120.36</v>
       </c>
-      <c r="N13" s="51" t="n">
+      <c r="O13" s="51" t="n">
         <v>109.72</v>
       </c>
-      <c r="O13" s="51" t="n">
+      <c r="P13" s="51" t="n">
         <v>108.25</v>
       </c>
-      <c r="P13" s="51" t="n">
+      <c r="Q13" s="51" t="n">
         <v>106.86</v>
       </c>
-      <c r="Q13" s="51" t="n">
+      <c r="R13" s="51" t="n">
         <v>95.33</v>
       </c>
-      <c r="R13" s="51" t="n">
+      <c r="S13" s="51" t="n">
         <v>164192.24</v>
       </c>
-      <c r="S13" s="51" t="n">
+      <c r="T13" s="51" t="n">
         <v>32094.6</v>
       </c>
-      <c r="T13" s="49" t="n">
+      <c r="U13" s="49" t="n">
         <v>134</v>
       </c>
-      <c r="U13" s="49" t="inlineStr">
+      <c r="V13" s="49" t="inlineStr">
         <is>
           <t>5:1 Split on 2026-03-09</t>
         </is>
       </c>
-      <c r="V13" s="49" t="inlineStr">
+      <c r="W13" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33639,31 +33681,34 @@
         <v>286.6</v>
       </c>
       <c r="M14" s="51" t="n">
+        <v>283.95</v>
+      </c>
+      <c r="N14" s="51" t="n">
         <v>281.3</v>
       </c>
-      <c r="N14" s="51" t="n">
+      <c r="O14" s="51" t="n">
         <v>285.62</v>
       </c>
-      <c r="O14" s="51" t="n">
+      <c r="P14" s="51" t="n">
         <v>285.13</v>
       </c>
-      <c r="P14" s="51" t="n">
+      <c r="Q14" s="51" t="n">
         <v>284.58</v>
       </c>
-      <c r="Q14" s="51" t="n">
+      <c r="R14" s="51" t="n">
         <v>276.81</v>
       </c>
-      <c r="R14" s="51" t="n">
+      <c r="S14" s="51" t="n">
         <v>335895.2</v>
       </c>
-      <c r="S14" s="51" t="n">
+      <c r="T14" s="51" t="n">
         <v>35605.36</v>
       </c>
-      <c r="T14" s="49" t="n">
+      <c r="U14" s="49" t="n">
         <v>197</v>
       </c>
-      <c r="U14" s="49" t="inlineStr"/>
-      <c r="V14" s="49" t="inlineStr">
+      <c r="V14" s="49" t="inlineStr"/>
+      <c r="W14" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33717,31 +33762,34 @@
         <v>161.12</v>
       </c>
       <c r="M15" s="51" t="n">
+        <v>161.98</v>
+      </c>
+      <c r="N15" s="51" t="n">
         <v>162.79</v>
       </c>
-      <c r="N15" s="51" t="n">
+      <c r="O15" s="51" t="n">
         <v>154.07</v>
       </c>
-      <c r="O15" s="51" t="n">
+      <c r="P15" s="51" t="n">
         <v>153.01</v>
       </c>
-      <c r="P15" s="51" t="n">
+      <c r="Q15" s="51" t="n">
         <v>152</v>
       </c>
-      <c r="Q15" s="51" t="n">
+      <c r="R15" s="51" t="n">
         <v>143.69</v>
       </c>
-      <c r="R15" s="51" t="n">
+      <c r="S15" s="51" t="n">
         <v>58325.44</v>
       </c>
-      <c r="S15" s="51" t="n">
+      <c r="T15" s="51" t="n">
         <v>8097.94</v>
       </c>
-      <c r="T15" s="49" t="n">
+      <c r="U15" s="49" t="n">
         <v>137</v>
       </c>
-      <c r="U15" s="49" t="inlineStr"/>
-      <c r="V15" s="49" t="inlineStr">
+      <c r="V15" s="49" t="inlineStr"/>
+      <c r="W15" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33795,31 +33843,34 @@
         <v>643.85</v>
       </c>
       <c r="M16" s="51" t="n">
+        <v>632.8</v>
+      </c>
+      <c r="N16" s="51" t="n">
         <v>652.6</v>
       </c>
-      <c r="N16" s="51" t="n">
+      <c r="O16" s="51" t="n">
         <v>649.59</v>
       </c>
-      <c r="O16" s="51" t="n">
+      <c r="P16" s="51" t="n">
         <v>646.04</v>
       </c>
-      <c r="P16" s="51" t="n">
+      <c r="Q16" s="51" t="n">
         <v>642.55</v>
       </c>
-      <c r="Q16" s="51" t="n">
+      <c r="R16" s="51" t="n">
         <v>612.38</v>
       </c>
-      <c r="R16" s="51" t="n">
+      <c r="S16" s="51" t="n">
         <v>26397.85</v>
       </c>
-      <c r="S16" s="51" t="n">
+      <c r="T16" s="51" t="n">
         <v>2212.36</v>
       </c>
-      <c r="T16" s="49" t="n">
+      <c r="U16" s="49" t="n">
         <v>252</v>
       </c>
-      <c r="U16" s="49" t="inlineStr"/>
-      <c r="V16" s="49" t="inlineStr">
+      <c r="V16" s="49" t="inlineStr"/>
+      <c r="W16" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33873,31 +33924,34 @@
         <v>290.55</v>
       </c>
       <c r="M17" s="51" t="n">
+        <v>283.3</v>
+      </c>
+      <c r="N17" s="51" t="n">
         <v>287.9</v>
       </c>
-      <c r="N17" s="51" t="n">
+      <c r="O17" s="51" t="n">
         <v>286.24</v>
       </c>
-      <c r="O17" s="51" t="n">
+      <c r="P17" s="51" t="n">
         <v>285.06</v>
       </c>
-      <c r="P17" s="51" t="n">
+      <c r="Q17" s="51" t="n">
         <v>283.9</v>
       </c>
-      <c r="Q17" s="51" t="n">
+      <c r="R17" s="51" t="n">
         <v>273.59</v>
       </c>
-      <c r="R17" s="51" t="n">
+      <c r="S17" s="51" t="n">
         <v>80191.8</v>
       </c>
-      <c r="S17" s="51" t="n">
+      <c r="T17" s="51" t="n">
         <v>3259.56</v>
       </c>
-      <c r="T17" s="49" t="n">
+      <c r="U17" s="49" t="n">
         <v>204</v>
       </c>
-      <c r="U17" s="49" t="inlineStr"/>
-      <c r="V17" s="49" t="inlineStr">
+      <c r="V17" s="49" t="inlineStr"/>
+      <c r="W17" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -33951,31 +34005,34 @@
         <v>4385.3</v>
       </c>
       <c r="M18" s="51" t="n">
+        <v>4426.8</v>
+      </c>
+      <c r="N18" s="51" t="n">
         <v>4342.6</v>
       </c>
-      <c r="N18" s="51" t="n">
+      <c r="O18" s="51" t="n">
         <v>4410.37</v>
       </c>
-      <c r="O18" s="51" t="n">
+      <c r="P18" s="51" t="n">
         <v>4412.63</v>
       </c>
-      <c r="P18" s="51" t="n">
+      <c r="Q18" s="51" t="n">
         <v>4413.55</v>
       </c>
-      <c r="Q18" s="51" t="n">
+      <c r="R18" s="51" t="n">
         <v>4369.81</v>
       </c>
-      <c r="R18" s="51" t="n">
+      <c r="S18" s="51" t="n">
         <v>214879.7</v>
       </c>
-      <c r="S18" s="51" t="n">
+      <c r="T18" s="51" t="n">
         <v>14555.94</v>
       </c>
-      <c r="T18" s="49" t="n">
+      <c r="U18" s="49" t="n">
         <v>71</v>
       </c>
-      <c r="U18" s="49" t="inlineStr"/>
-      <c r="V18" s="49" t="inlineStr">
+      <c r="V18" s="49" t="inlineStr"/>
+      <c r="W18" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34029,31 +34086,34 @@
         <v>1048.3</v>
       </c>
       <c r="M19" s="51" t="n">
+        <v>1053.1</v>
+      </c>
+      <c r="N19" s="51" t="n">
         <v>1067.5</v>
       </c>
-      <c r="N19" s="51" t="n">
+      <c r="O19" s="51" t="n">
         <v>1016.47</v>
       </c>
-      <c r="O19" s="51" t="n">
+      <c r="P19" s="51" t="n">
         <v>1010.99</v>
       </c>
-      <c r="P19" s="51" t="n">
+      <c r="Q19" s="51" t="n">
         <v>1005.73</v>
       </c>
-      <c r="Q19" s="51" t="n">
+      <c r="R19" s="51" t="n">
         <v>960.29</v>
       </c>
-      <c r="R19" s="51" t="n">
+      <c r="S19" s="51" t="n">
         <v>265219.9</v>
       </c>
-      <c r="S19" s="51" t="n">
+      <c r="T19" s="51" t="n">
         <v>51862.47</v>
       </c>
-      <c r="T19" s="49" t="n">
+      <c r="U19" s="49" t="n">
         <v>225</v>
       </c>
-      <c r="U19" s="49" t="inlineStr"/>
-      <c r="V19" s="49" t="inlineStr">
+      <c r="V19" s="49" t="inlineStr"/>
+      <c r="W19" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34107,31 +34167,34 @@
         <v>1344.9</v>
       </c>
       <c r="M20" s="51" t="n">
+        <v>1327.3</v>
+      </c>
+      <c r="N20" s="51" t="n">
         <v>1323.6</v>
       </c>
-      <c r="N20" s="51" t="n">
+      <c r="O20" s="51" t="n">
         <v>1187.13</v>
       </c>
-      <c r="O20" s="51" t="n">
+      <c r="P20" s="51" t="n">
         <v>1176.36</v>
       </c>
-      <c r="P20" s="51" t="n">
+      <c r="Q20" s="51" t="n">
         <v>1166.73</v>
       </c>
-      <c r="Q20" s="51" t="n">
+      <c r="R20" s="51" t="n">
         <v>1100.72</v>
       </c>
-      <c r="R20" s="51" t="n">
+      <c r="S20" s="51" t="n">
         <v>51106.2</v>
       </c>
-      <c r="S20" s="51" t="n">
+      <c r="T20" s="51" t="n">
         <v>737.2</v>
       </c>
-      <c r="T20" s="49" t="n">
+      <c r="U20" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="U20" s="49" t="inlineStr"/>
-      <c r="V20" s="49" t="inlineStr">
+      <c r="V20" s="49" t="inlineStr"/>
+      <c r="W20" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34185,31 +34248,34 @@
         <v>3092.3</v>
       </c>
       <c r="M21" s="51" t="n">
+        <v>3083.7</v>
+      </c>
+      <c r="N21" s="51" t="n">
         <v>3123.1</v>
       </c>
-      <c r="N21" s="51" t="n">
+      <c r="O21" s="51" t="n">
         <v>3147.77</v>
       </c>
-      <c r="O21" s="51" t="n">
+      <c r="P21" s="51" t="n">
         <v>3151.04</v>
       </c>
-      <c r="P21" s="51" t="n">
+      <c r="Q21" s="51" t="n">
         <v>3153.58</v>
       </c>
-      <c r="Q21" s="51" t="n">
+      <c r="R21" s="51" t="n">
         <v>3162.32</v>
       </c>
-      <c r="R21" s="51" t="n">
+      <c r="S21" s="51" t="n">
         <v>49476.8</v>
       </c>
-      <c r="S21" s="51" t="n">
+      <c r="T21" s="51" t="n">
         <v>-555.2</v>
       </c>
-      <c r="T21" s="49" t="n">
+      <c r="U21" s="49" t="n">
         <v>4</v>
       </c>
-      <c r="U21" s="49" t="inlineStr"/>
-      <c r="V21" s="49" t="inlineStr">
+      <c r="V21" s="49" t="inlineStr"/>
+      <c r="W21" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34263,31 +34329,34 @@
         <v>78.34</v>
       </c>
       <c r="M22" s="51" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="N22" s="51" t="n">
         <v>78.02</v>
       </c>
-      <c r="N22" s="51" t="n">
+      <c r="O22" s="51" t="n">
         <v>75.51000000000001</v>
       </c>
-      <c r="O22" s="51" t="n">
+      <c r="P22" s="51" t="n">
         <v>74.97</v>
       </c>
-      <c r="P22" s="51" t="n">
+      <c r="Q22" s="51" t="n">
         <v>74.45999999999999</v>
       </c>
-      <c r="Q22" s="51" t="n">
+      <c r="R22" s="51" t="n">
         <v>70.31999999999999</v>
       </c>
-      <c r="R22" s="51" t="n">
+      <c r="S22" s="51" t="n">
         <v>56404.8</v>
       </c>
-      <c r="S22" s="51" t="n">
+      <c r="T22" s="51" t="n">
         <v>1152</v>
       </c>
-      <c r="T22" s="49" t="n">
+      <c r="U22" s="49" t="n">
         <v>123</v>
       </c>
-      <c r="U22" s="49" t="inlineStr"/>
-      <c r="V22" s="49" t="inlineStr">
+      <c r="V22" s="49" t="inlineStr"/>
+      <c r="W22" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34337,31 +34406,34 @@
         <v>267.61</v>
       </c>
       <c r="M23" s="51" t="n">
+        <v>267.58</v>
+      </c>
+      <c r="N23" s="51" t="n">
         <v>267.3</v>
       </c>
-      <c r="N23" s="51" t="n">
+      <c r="O23" s="51" t="n">
         <v>270.54</v>
       </c>
-      <c r="O23" s="51" t="n">
+      <c r="P23" s="51" t="n">
         <v>270.92</v>
       </c>
-      <c r="P23" s="51" t="n">
+      <c r="Q23" s="51" t="n">
         <v>271.32</v>
       </c>
-      <c r="Q23" s="51" t="n">
+      <c r="R23" s="51" t="n">
         <v>275.06</v>
       </c>
-      <c r="R23" s="51" t="n">
+      <c r="S23" s="51" t="n">
         <v>24620.12</v>
       </c>
-      <c r="S23" s="51" t="n">
+      <c r="T23" s="51" t="n">
         <v>-458.16</v>
       </c>
-      <c r="T23" s="49" t="n">
+      <c r="U23" s="49" t="n">
         <v>71</v>
       </c>
-      <c r="U23" s="49" t="inlineStr"/>
-      <c r="V23" s="49" t="inlineStr">
+      <c r="V23" s="49" t="inlineStr"/>
+      <c r="W23" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34415,31 +34487,34 @@
         <v>89.02</v>
       </c>
       <c r="M24" s="51" t="n">
+        <v>90.14</v>
+      </c>
+      <c r="N24" s="51" t="n">
         <v>91.41</v>
       </c>
-      <c r="N24" s="51" t="n">
+      <c r="O24" s="51" t="n">
         <v>87.22</v>
       </c>
-      <c r="O24" s="51" t="n">
+      <c r="P24" s="51" t="n">
         <v>86.81</v>
       </c>
-      <c r="P24" s="51" t="n">
+      <c r="Q24" s="51" t="n">
         <v>86.41</v>
       </c>
-      <c r="Q24" s="51" t="n">
+      <c r="R24" s="51" t="n">
         <v>83.20999999999999</v>
       </c>
-      <c r="R24" s="51" t="n">
+      <c r="S24" s="51" t="n">
         <v>26706</v>
       </c>
-      <c r="S24" s="51" t="n">
+      <c r="T24" s="51" t="n">
         <v>1359</v>
       </c>
-      <c r="T24" s="49" t="n">
+      <c r="U24" s="49" t="n">
         <v>137</v>
       </c>
-      <c r="U24" s="49" t="inlineStr"/>
-      <c r="V24" s="49" t="inlineStr">
+      <c r="V24" s="49" t="inlineStr"/>
+      <c r="W24" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34493,31 +34568,34 @@
         <v>1529.8</v>
       </c>
       <c r="M25" s="51" t="n">
+        <v>1537.5</v>
+      </c>
+      <c r="N25" s="51" t="n">
         <v>1544.8</v>
       </c>
-      <c r="N25" s="51" t="n">
+      <c r="O25" s="51" t="n">
         <v>1355.76</v>
       </c>
-      <c r="O25" s="51" t="n">
+      <c r="P25" s="51" t="n">
         <v>1343.42</v>
       </c>
-      <c r="P25" s="51" t="n">
+      <c r="Q25" s="51" t="n">
         <v>1333.09</v>
       </c>
-      <c r="Q25" s="51" t="n">
+      <c r="R25" s="51" t="n">
         <v>1280.92</v>
       </c>
-      <c r="R25" s="51" t="n">
+      <c r="S25" s="51" t="n">
         <v>107086</v>
       </c>
-      <c r="S25" s="51" t="n">
+      <c r="T25" s="51" t="n">
         <v>7503.3</v>
       </c>
-      <c r="T25" s="49" t="n">
+      <c r="U25" s="49" t="n">
         <v>15</v>
       </c>
-      <c r="U25" s="49" t="inlineStr"/>
-      <c r="V25" s="49" t="inlineStr">
+      <c r="V25" s="49" t="inlineStr"/>
+      <c r="W25" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34571,31 +34649,34 @@
         <v>9162.5</v>
       </c>
       <c r="M26" s="51" t="n">
+        <v>9151</v>
+      </c>
+      <c r="N26" s="51" t="n">
         <v>9152.5</v>
       </c>
-      <c r="N26" s="51" t="n">
+      <c r="O26" s="51" t="n">
         <v>8992.02</v>
       </c>
-      <c r="O26" s="51" t="n">
+      <c r="P26" s="51" t="n">
         <v>8959.18</v>
       </c>
-      <c r="P26" s="51" t="n">
+      <c r="Q26" s="51" t="n">
         <v>8926.209999999999</v>
       </c>
-      <c r="Q26" s="51" t="n">
+      <c r="R26" s="51" t="n">
         <v>8630.76</v>
       </c>
-      <c r="R26" s="51" t="n">
+      <c r="S26" s="51" t="n">
         <v>458125</v>
       </c>
-      <c r="S26" s="51" t="n">
+      <c r="T26" s="51" t="n">
         <v>71678</v>
       </c>
-      <c r="T26" s="49" t="n">
+      <c r="U26" s="49" t="n">
         <v>253</v>
       </c>
-      <c r="U26" s="49" t="inlineStr"/>
-      <c r="V26" s="49" t="inlineStr">
+      <c r="V26" s="49" t="inlineStr"/>
+      <c r="W26" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34649,31 +34730,34 @@
         <v>1561.6</v>
       </c>
       <c r="M27" s="51" t="n">
+        <v>1492.1</v>
+      </c>
+      <c r="N27" s="51" t="n">
         <v>1517.8</v>
       </c>
-      <c r="N27" s="51" t="n">
+      <c r="O27" s="51" t="n">
         <v>1499.56</v>
       </c>
-      <c r="O27" s="51" t="n">
+      <c r="P27" s="51" t="n">
         <v>1489.44</v>
       </c>
-      <c r="P27" s="51" t="n">
+      <c r="Q27" s="51" t="n">
         <v>1478.96</v>
       </c>
-      <c r="Q27" s="51" t="n">
+      <c r="R27" s="51" t="n">
         <v>1375.13</v>
       </c>
-      <c r="R27" s="51" t="n">
+      <c r="S27" s="51" t="n">
         <v>65587.2</v>
       </c>
-      <c r="S27" s="51" t="n">
+      <c r="T27" s="51" t="n">
         <v>8724.66</v>
       </c>
-      <c r="T27" s="49" t="n">
+      <c r="U27" s="49" t="n">
         <v>109</v>
       </c>
-      <c r="U27" s="49" t="inlineStr"/>
-      <c r="V27" s="49" t="inlineStr">
+      <c r="V27" s="49" t="inlineStr"/>
+      <c r="W27" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34727,31 +34811,34 @@
         <v>18116</v>
       </c>
       <c r="M28" s="51" t="n">
+        <v>18019</v>
+      </c>
+      <c r="N28" s="51" t="n">
         <v>17314</v>
       </c>
-      <c r="N28" s="51" t="n">
+      <c r="O28" s="51" t="n">
         <v>16880.24</v>
       </c>
-      <c r="O28" s="51" t="n">
+      <c r="P28" s="51" t="n">
         <v>16786.32</v>
       </c>
-      <c r="P28" s="51" t="n">
+      <c r="Q28" s="51" t="n">
         <v>16699.8</v>
       </c>
-      <c r="Q28" s="51" t="n">
+      <c r="R28" s="51" t="n">
         <v>16053.77</v>
       </c>
-      <c r="R28" s="51" t="n">
+      <c r="S28" s="51" t="n">
         <v>36232</v>
       </c>
-      <c r="S28" s="51" t="n">
+      <c r="T28" s="51" t="n">
         <v>10190</v>
       </c>
-      <c r="T28" s="49" t="n">
+      <c r="U28" s="49" t="n">
         <v>60</v>
       </c>
-      <c r="U28" s="49" t="inlineStr"/>
-      <c r="V28" s="49" t="inlineStr">
+      <c r="V28" s="49" t="inlineStr"/>
+      <c r="W28" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34805,31 +34892,34 @@
         <v>1882.3</v>
       </c>
       <c r="M29" s="51" t="n">
+        <v>1905.8</v>
+      </c>
+      <c r="N29" s="51" t="n">
         <v>1878.2</v>
       </c>
-      <c r="N29" s="51" t="n">
+      <c r="O29" s="51" t="n">
         <v>1793.32</v>
       </c>
-      <c r="O29" s="51" t="n">
+      <c r="P29" s="51" t="n">
         <v>1787.71</v>
       </c>
-      <c r="P29" s="51" t="n">
+      <c r="Q29" s="51" t="n">
         <v>1782.81</v>
       </c>
-      <c r="Q29" s="51" t="n">
+      <c r="R29" s="51" t="n">
         <v>1753.02</v>
       </c>
-      <c r="R29" s="51" t="n">
+      <c r="S29" s="51" t="n">
         <v>48939.8</v>
       </c>
-      <c r="S29" s="51" t="n">
+      <c r="T29" s="51" t="n">
         <v>-439.4</v>
       </c>
-      <c r="T29" s="49" t="n">
+      <c r="U29" s="49" t="n">
         <v>1</v>
       </c>
-      <c r="U29" s="49" t="inlineStr"/>
-      <c r="V29" s="49" t="inlineStr">
+      <c r="V29" s="49" t="inlineStr"/>
+      <c r="W29" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -34883,31 +34973,34 @@
         <v>1256.3</v>
       </c>
       <c r="M30" s="51" t="n">
+        <v>1328</v>
+      </c>
+      <c r="N30" s="51" t="n">
         <v>1311.3</v>
       </c>
-      <c r="N30" s="51" t="n">
+      <c r="O30" s="51" t="n">
         <v>1232.7</v>
       </c>
-      <c r="O30" s="51" t="n">
+      <c r="P30" s="51" t="n">
         <v>1226.66</v>
       </c>
-      <c r="P30" s="51" t="n">
+      <c r="Q30" s="51" t="n">
         <v>1220.66</v>
       </c>
-      <c r="Q30" s="51" t="n">
+      <c r="R30" s="51" t="n">
         <v>1162.77</v>
       </c>
-      <c r="R30" s="51" t="n">
+      <c r="S30" s="51" t="n">
         <v>371864.8</v>
       </c>
-      <c r="S30" s="51" t="n">
+      <c r="T30" s="51" t="n">
         <v>97090.96000000001</v>
       </c>
-      <c r="T30" s="49" t="n">
+      <c r="U30" s="49" t="n">
         <v>96</v>
       </c>
-      <c r="U30" s="49" t="inlineStr"/>
-      <c r="V30" s="49" t="inlineStr">
+      <c r="V30" s="49" t="inlineStr"/>
+      <c r="W30" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>

--- a/Transformed_Tradebook.xlsx
+++ b/Transformed_Tradebook.xlsx
@@ -127,7 +127,7 @@
       <color rgb="00C00000"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -144,6 +144,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="002F5496"/>
         <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -239,7 +251,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -310,6 +322,8 @@
     <xf numFmtId="167" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -32704,10 +32718,10 @@
       <c r="L2" s="51" t="n">
         <v>2886.5</v>
       </c>
-      <c r="M2" s="51" t="n">
+      <c r="M2" s="54" t="n">
         <v>2799.1</v>
       </c>
-      <c r="N2" s="51" t="n">
+      <c r="N2" s="54" t="n">
         <v>2731</v>
       </c>
       <c r="O2" s="51" t="n">
@@ -32785,10 +32799,10 @@
       <c r="L3" s="51" t="n">
         <v>2725</v>
       </c>
-      <c r="M3" s="51" t="n">
+      <c r="M3" s="54" t="n">
         <v>2689.8</v>
       </c>
-      <c r="N3" s="51" t="n">
+      <c r="N3" s="54" t="n">
         <v>2716</v>
       </c>
       <c r="O3" s="51" t="n">
@@ -32866,10 +32880,10 @@
       <c r="L4" s="51" t="n">
         <v>3248.2</v>
       </c>
-      <c r="M4" s="51" t="n">
+      <c r="M4" s="54" t="n">
         <v>3214.1</v>
       </c>
-      <c r="N4" s="51" t="n">
+      <c r="N4" s="54" t="n">
         <v>3177.2</v>
       </c>
       <c r="O4" s="51" t="n">
@@ -32947,10 +32961,10 @@
       <c r="L5" s="51" t="n">
         <v>1864.5</v>
       </c>
-      <c r="M5" s="51" t="n">
+      <c r="M5" s="55" t="n">
         <v>1876</v>
       </c>
-      <c r="N5" s="51" t="n">
+      <c r="N5" s="55" t="n">
         <v>1890.2</v>
       </c>
       <c r="O5" s="51" t="n">
@@ -33028,10 +33042,10 @@
       <c r="L6" s="51" t="n">
         <v>340.7</v>
       </c>
-      <c r="M6" s="51" t="n">
+      <c r="M6" s="54" t="n">
         <v>311</v>
       </c>
-      <c r="N6" s="51" t="n">
+      <c r="N6" s="54" t="n">
         <v>294.55</v>
       </c>
       <c r="O6" s="51" t="n">
@@ -33109,10 +33123,10 @@
       <c r="L7" s="51" t="n">
         <v>1092.7</v>
       </c>
-      <c r="M7" s="51" t="n">
+      <c r="M7" s="54" t="n">
         <v>1087.2</v>
       </c>
-      <c r="N7" s="51" t="n">
+      <c r="N7" s="55" t="n">
         <v>1106.6</v>
       </c>
       <c r="O7" s="51" t="n">
@@ -33190,10 +33204,10 @@
       <c r="L8" s="51" t="n">
         <v>1512.8</v>
       </c>
-      <c r="M8" s="51" t="n">
+      <c r="M8" s="54" t="n">
         <v>1500.5</v>
       </c>
-      <c r="N8" s="51" t="n">
+      <c r="N8" s="54" t="n">
         <v>1511.8</v>
       </c>
       <c r="O8" s="51" t="n">
@@ -33271,10 +33285,10 @@
       <c r="L9" s="51" t="n">
         <v>1708.8</v>
       </c>
-      <c r="M9" s="51" t="n">
+      <c r="M9" s="55" t="n">
         <v>1763</v>
       </c>
-      <c r="N9" s="51" t="n">
+      <c r="N9" s="54" t="n">
         <v>1706.2</v>
       </c>
       <c r="O9" s="51" t="n">
@@ -33352,10 +33366,10 @@
       <c r="L10" s="51" t="n">
         <v>4190.8</v>
       </c>
-      <c r="M10" s="51" t="n">
+      <c r="M10" s="54" t="n">
         <v>4120.7</v>
       </c>
-      <c r="N10" s="51" t="n">
+      <c r="N10" s="54" t="n">
         <v>4000.6</v>
       </c>
       <c r="O10" s="51" t="n">
@@ -33433,10 +33447,10 @@
       <c r="L11" s="51" t="n">
         <v>1089.4</v>
       </c>
-      <c r="M11" s="51" t="n">
+      <c r="M11" s="55" t="n">
         <v>1090.4</v>
       </c>
-      <c r="N11" s="51" t="n">
+      <c r="N11" s="55" t="n">
         <v>1116.3</v>
       </c>
       <c r="O11" s="51" t="n">
@@ -33514,10 +33528,10 @@
       <c r="L12" s="51" t="n">
         <v>819.4</v>
       </c>
-      <c r="M12" s="51" t="n">
+      <c r="M12" s="54" t="n">
         <v>808.75</v>
       </c>
-      <c r="N12" s="51" t="n">
+      <c r="N12" s="55" t="n">
         <v>838.2</v>
       </c>
       <c r="O12" s="51" t="n">
@@ -33595,10 +33609,10 @@
       <c r="L13" s="51" t="n">
         <v>114.34</v>
       </c>
-      <c r="M13" s="51" t="n">
+      <c r="M13" s="55" t="n">
         <v>120.84</v>
       </c>
-      <c r="N13" s="51" t="n">
+      <c r="N13" s="55" t="n">
         <v>120.36</v>
       </c>
       <c r="O13" s="51" t="n">
@@ -33680,10 +33694,10 @@
       <c r="L14" s="51" t="n">
         <v>286.6</v>
       </c>
-      <c r="M14" s="51" t="n">
+      <c r="M14" s="54" t="n">
         <v>283.95</v>
       </c>
-      <c r="N14" s="51" t="n">
+      <c r="N14" s="54" t="n">
         <v>281.3</v>
       </c>
       <c r="O14" s="51" t="n">
@@ -33761,10 +33775,10 @@
       <c r="L15" s="51" t="n">
         <v>161.12</v>
       </c>
-      <c r="M15" s="51" t="n">
+      <c r="M15" s="55" t="n">
         <v>161.98</v>
       </c>
-      <c r="N15" s="51" t="n">
+      <c r="N15" s="55" t="n">
         <v>162.79</v>
       </c>
       <c r="O15" s="51" t="n">
@@ -33842,10 +33856,10 @@
       <c r="L16" s="51" t="n">
         <v>643.85</v>
       </c>
-      <c r="M16" s="51" t="n">
+      <c r="M16" s="54" t="n">
         <v>632.8</v>
       </c>
-      <c r="N16" s="51" t="n">
+      <c r="N16" s="55" t="n">
         <v>652.6</v>
       </c>
       <c r="O16" s="51" t="n">
@@ -33923,10 +33937,10 @@
       <c r="L17" s="51" t="n">
         <v>290.55</v>
       </c>
-      <c r="M17" s="51" t="n">
+      <c r="M17" s="54" t="n">
         <v>283.3</v>
       </c>
-      <c r="N17" s="51" t="n">
+      <c r="N17" s="54" t="n">
         <v>287.9</v>
       </c>
       <c r="O17" s="51" t="n">
@@ -34004,10 +34018,10 @@
       <c r="L18" s="51" t="n">
         <v>4385.3</v>
       </c>
-      <c r="M18" s="51" t="n">
+      <c r="M18" s="55" t="n">
         <v>4426.8</v>
       </c>
-      <c r="N18" s="51" t="n">
+      <c r="N18" s="54" t="n">
         <v>4342.6</v>
       </c>
       <c r="O18" s="51" t="n">
@@ -34085,10 +34099,10 @@
       <c r="L19" s="51" t="n">
         <v>1048.3</v>
       </c>
-      <c r="M19" s="51" t="n">
+      <c r="M19" s="55" t="n">
         <v>1053.1</v>
       </c>
-      <c r="N19" s="51" t="n">
+      <c r="N19" s="55" t="n">
         <v>1067.5</v>
       </c>
       <c r="O19" s="51" t="n">
@@ -34166,10 +34180,10 @@
       <c r="L20" s="51" t="n">
         <v>1344.9</v>
       </c>
-      <c r="M20" s="51" t="n">
+      <c r="M20" s="54" t="n">
         <v>1327.3</v>
       </c>
-      <c r="N20" s="51" t="n">
+      <c r="N20" s="54" t="n">
         <v>1323.6</v>
       </c>
       <c r="O20" s="51" t="n">
@@ -34247,10 +34261,10 @@
       <c r="L21" s="51" t="n">
         <v>3092.3</v>
       </c>
-      <c r="M21" s="51" t="n">
+      <c r="M21" s="54" t="n">
         <v>3083.7</v>
       </c>
-      <c r="N21" s="51" t="n">
+      <c r="N21" s="55" t="n">
         <v>3123.1</v>
       </c>
       <c r="O21" s="51" t="n">
@@ -34328,10 +34342,10 @@
       <c r="L22" s="51" t="n">
         <v>78.34</v>
       </c>
-      <c r="M22" s="51" t="n">
+      <c r="M22" s="54" t="n">
         <v>77.8</v>
       </c>
-      <c r="N22" s="51" t="n">
+      <c r="N22" s="54" t="n">
         <v>78.02</v>
       </c>
       <c r="O22" s="51" t="n">
@@ -34405,10 +34419,10 @@
       <c r="L23" s="51" t="n">
         <v>267.61</v>
       </c>
-      <c r="M23" s="51" t="n">
+      <c r="M23" s="54" t="n">
         <v>267.58</v>
       </c>
-      <c r="N23" s="51" t="n">
+      <c r="N23" s="54" t="n">
         <v>267.3</v>
       </c>
       <c r="O23" s="51" t="n">
@@ -34486,10 +34500,10 @@
       <c r="L24" s="51" t="n">
         <v>89.02</v>
       </c>
-      <c r="M24" s="51" t="n">
+      <c r="M24" s="55" t="n">
         <v>90.14</v>
       </c>
-      <c r="N24" s="51" t="n">
+      <c r="N24" s="55" t="n">
         <v>91.41</v>
       </c>
       <c r="O24" s="51" t="n">
@@ -34567,10 +34581,10 @@
       <c r="L25" s="51" t="n">
         <v>1529.8</v>
       </c>
-      <c r="M25" s="51" t="n">
+      <c r="M25" s="55" t="n">
         <v>1537.5</v>
       </c>
-      <c r="N25" s="51" t="n">
+      <c r="N25" s="55" t="n">
         <v>1544.8</v>
       </c>
       <c r="O25" s="51" t="n">
@@ -34648,10 +34662,10 @@
       <c r="L26" s="51" t="n">
         <v>9162.5</v>
       </c>
-      <c r="M26" s="51" t="n">
+      <c r="M26" s="54" t="n">
         <v>9151</v>
       </c>
-      <c r="N26" s="51" t="n">
+      <c r="N26" s="54" t="n">
         <v>9152.5</v>
       </c>
       <c r="O26" s="51" t="n">
@@ -34729,10 +34743,10 @@
       <c r="L27" s="51" t="n">
         <v>1561.6</v>
       </c>
-      <c r="M27" s="51" t="n">
+      <c r="M27" s="54" t="n">
         <v>1492.1</v>
       </c>
-      <c r="N27" s="51" t="n">
+      <c r="N27" s="54" t="n">
         <v>1517.8</v>
       </c>
       <c r="O27" s="51" t="n">
@@ -34810,10 +34824,10 @@
       <c r="L28" s="51" t="n">
         <v>18116</v>
       </c>
-      <c r="M28" s="51" t="n">
+      <c r="M28" s="54" t="n">
         <v>18019</v>
       </c>
-      <c r="N28" s="51" t="n">
+      <c r="N28" s="54" t="n">
         <v>17314</v>
       </c>
       <c r="O28" s="51" t="n">
@@ -34891,10 +34905,10 @@
       <c r="L29" s="51" t="n">
         <v>1882.3</v>
       </c>
-      <c r="M29" s="51" t="n">
+      <c r="M29" s="55" t="n">
         <v>1905.8</v>
       </c>
-      <c r="N29" s="51" t="n">
+      <c r="N29" s="54" t="n">
         <v>1878.2</v>
       </c>
       <c r="O29" s="51" t="n">
@@ -34972,10 +34986,10 @@
       <c r="L30" s="51" t="n">
         <v>1256.3</v>
       </c>
-      <c r="M30" s="51" t="n">
+      <c r="M30" s="55" t="n">
         <v>1328</v>
       </c>
-      <c r="N30" s="51" t="n">
+      <c r="N30" s="55" t="n">
         <v>1311.3</v>
       </c>
       <c r="O30" s="51" t="n">
